--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A5/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1609" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88C36B4D-0A0E-4C21-9DAA-6C68967C4EAB}"/>
+  <xr:revisionPtr revIDLastSave="1666" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C871719-7412-4024-B898-59048F494210}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="11388" windowHeight="9240" tabRatio="461" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="48" yWindow="1356" windowWidth="10788" windowHeight="10812" tabRatio="461" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="42">
   <si>
     <t>BUY</t>
   </si>
@@ -208,7 +208,7 @@
     <numFmt numFmtId="171" formatCode="&quot;฿&quot;#,##0.00"/>
     <numFmt numFmtId="172" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -333,12 +333,6 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF92D050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -360,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -455,7 +449,6 @@
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
@@ -476,6 +469,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7317,7 +7314,7 @@
     <col min="7" max="7" width="6.6640625" style="20" customWidth="1"/>
     <col min="8" max="8" width="5.77734375" style="20" customWidth="1"/>
     <col min="9" max="9" width="7.21875" style="20" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" style="20" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" style="97" customWidth="1"/>
     <col min="11" max="11" width="12.77734375" style="20" customWidth="1"/>
     <col min="12" max="12" width="8.88671875" style="20"/>
     <col min="13" max="13" width="8.88671875" style="23"/>
@@ -7362,7 +7359,7 @@
         <f>(F2+G2+H2)*0.07</f>
         <v>20.604780000000005</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="24">
         <f>E2+F2+I2+G2+H2</f>
         <v>142514.95877999999</v>
       </c>
@@ -7403,7 +7400,7 @@
         <f>(F3+G3+H3)*0.07</f>
         <v>5.3033400000000004</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="24">
         <f>E3+F3+I3+G3+H3</f>
         <v>36681.065340000001</v>
       </c>
@@ -7442,7 +7439,7 @@
         <f t="shared" si="0"/>
         <v>25.908120000000004</v>
       </c>
-      <c r="J4" s="15">
+      <c r="J4" s="24">
         <f t="shared" si="0"/>
         <v>179196.02411999999</v>
       </c>
@@ -7480,7 +7477,7 @@
         <f>(F5+G5+H5)*0.07</f>
         <v>6.6074400000000013</v>
       </c>
-      <c r="J5" s="17">
+      <c r="J5" s="24">
         <f>E5+F5+I5+G5+H5</f>
         <v>45700.999439999992</v>
       </c>
@@ -7519,87 +7516,34 @@
         <f t="shared" si="1"/>
         <v>32.515560000000008</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="24">
         <f t="shared" si="1"/>
         <v>224897.02355999997</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" s="52">
-        <v>45182</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9">
-        <v>3200</v>
-      </c>
-      <c r="D7" s="43">
-        <v>8</v>
-      </c>
-      <c r="E7" s="19">
-        <f>C7*D7</f>
-        <v>25600</v>
-      </c>
-      <c r="F7" s="19">
-        <f>E7*0.002</f>
-        <v>51.2</v>
-      </c>
-      <c r="G7" s="19">
-        <f>E7*0.00006</f>
-        <v>1.536</v>
-      </c>
-      <c r="H7" s="19">
-        <f>E7*0.00001</f>
-        <v>0.25600000000000001</v>
-      </c>
-      <c r="I7" s="19">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>3.7094400000000007</v>
-      </c>
-      <c r="J7" s="19">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>25656.701440000001</v>
-      </c>
+      <c r="A7" s="52"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+      <c r="J7" s="32"/>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="52"/>
-      <c r="B8" s="11">
-        <f>(D7-D6)/D6</f>
-        <v>-0.75757575757575757</v>
-      </c>
-      <c r="C8" s="9">
-        <f>SUM(C6:C7)</f>
-        <v>10000</v>
-      </c>
-      <c r="D8" s="60">
-        <f>E8/C8</f>
-        <v>25</v>
-      </c>
-      <c r="E8" s="9">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>250000</v>
-      </c>
-      <c r="F8" s="9">
-        <f t="shared" si="2"/>
-        <v>500</v>
-      </c>
-      <c r="G8" s="9">
-        <f t="shared" si="2"/>
-        <v>15</v>
-      </c>
-      <c r="H8" s="9">
-        <f t="shared" si="2"/>
-        <v>2.5</v>
-      </c>
-      <c r="I8" s="9">
-        <f t="shared" si="2"/>
-        <v>36.225000000000009</v>
-      </c>
-      <c r="J8" s="9">
-        <f t="shared" si="2"/>
-        <v>250553.72499999998</v>
-      </c>
+      <c r="B8" s="11"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="9"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="32"/>
     </row>
     <row r="10" spans="1:13" s="12" customFormat="1">
       <c r="A10" s="13">
@@ -7629,7 +7573,7 @@
       <c r="I10" s="17">
         <v>8.8678800000000013</v>
       </c>
-      <c r="J10" s="17">
+      <c r="J10" s="24">
         <v>61335.551879999999</v>
       </c>
     </row>
@@ -7692,7 +7636,7 @@
       <c r="G12" s="17"/>
       <c r="H12" s="17"/>
       <c r="I12" s="17"/>
-      <c r="J12" s="17">
+      <c r="J12" s="24">
         <f>J11-J10</f>
         <v>4397.9665752000001</v>
       </c>
@@ -7731,7 +7675,7 @@
         <f>(F14+G14+H14)*0.07</f>
         <v>3.4080480000000004</v>
       </c>
-      <c r="J14" s="17">
+      <c r="J14" s="24">
         <f>E14+F14+I14+G14+H14</f>
         <v>23572.094448</v>
       </c>
@@ -7795,7 +7739,7 @@
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
       <c r="I16" s="17"/>
-      <c r="J16" s="17">
+      <c r="J16" s="24">
         <f>J15-J14</f>
         <v>1092.9416207999966</v>
       </c>
@@ -7834,7 +7778,7 @@
         <f>(F18+G18+H18)*0.07</f>
         <v>4.0687920000000011</v>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="24">
         <f>E18+F18+I18+G18+H18</f>
         <v>28142.194391999998</v>
       </c>
@@ -7898,7 +7842,7 @@
       <c r="G20" s="17"/>
       <c r="H20" s="17"/>
       <c r="I20" s="17"/>
-      <c r="J20" s="17">
+      <c r="J20" s="24">
         <f>J19-J18</f>
         <v>1312.1690688000017</v>
       </c>
@@ -7937,7 +7881,7 @@
         <f>(F22+G22+H22)*0.07</f>
         <v>4.0861799999999997</v>
       </c>
-      <c r="J22" s="17">
+      <c r="J22" s="24">
         <f>E22+F22+I22+G22+H22</f>
         <v>28262.460179999998</v>
       </c>
@@ -8001,7 +7945,7 @@
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
       <c r="I24" s="17"/>
-      <c r="J24" s="17">
+      <c r="J24" s="24">
         <f>J23-J22</f>
         <v>1311.6364656000042</v>
       </c>
@@ -8040,7 +7984,7 @@
         <f>(F26+G26+H26)*0.07</f>
         <v>6.5494800000000009</v>
       </c>
-      <c r="J26" s="17">
+      <c r="J26" s="24">
         <f>E26+F26+I26+G26+H26</f>
         <v>45300.11348</v>
       </c>
@@ -8104,7 +8048,7 @@
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="17"/>
-      <c r="J28" s="17">
+      <c r="J28" s="24">
         <f>J27-J26</f>
         <v>2792.7157479999951</v>
       </c>
@@ -8143,7 +8087,7 @@
         <f>(F30+G30+H30)*0.07</f>
         <v>4.2890400000000009</v>
       </c>
-      <c r="J30" s="17">
+      <c r="J30" s="24">
         <f>E30+F30+I30+G30+H30</f>
         <v>29665.561040000001</v>
       </c>
@@ -8206,7 +8150,7 @@
       <c r="G32" s="19"/>
       <c r="H32" s="19"/>
       <c r="I32" s="19"/>
-      <c r="J32" s="19">
+      <c r="J32" s="32">
         <f>J31-J30</f>
         <v>347.55728319999616</v>
       </c>
@@ -8220,34 +8164,34 @@
         <v>0</v>
       </c>
       <c r="C34" s="9">
-        <v>5000</v>
+        <v>6800</v>
       </c>
       <c r="D34" s="43">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E34" s="19">
         <f>C34*D34</f>
-        <v>45000</v>
+        <v>40800</v>
       </c>
       <c r="F34" s="19">
         <f>E34*0.002</f>
-        <v>90</v>
+        <v>81.600000000000009</v>
       </c>
       <c r="G34" s="19">
         <f>E34*0.00006</f>
-        <v>2.7</v>
+        <v>2.448</v>
       </c>
       <c r="H34" s="19">
         <f>E34*0.00001</f>
-        <v>0.45</v>
+        <v>0.40800000000000003</v>
       </c>
       <c r="I34" s="19">
         <f>(F34+G34+H34)*0.07</f>
-        <v>6.5205000000000011</v>
-      </c>
-      <c r="J34" s="19">
+        <v>5.9119200000000012</v>
+      </c>
+      <c r="J34" s="32">
         <f>E34+F34+I34+G34+H34</f>
-        <v>45099.670499999993</v>
+        <v>40890.367919999997</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -8258,34 +8202,35 @@
         <v>2</v>
       </c>
       <c r="C35" s="9">
-        <v>5000</v>
+        <f>C34</f>
+        <v>6800</v>
       </c>
       <c r="D35" s="32">
-        <v>9.1999999999999993</v>
+        <v>8.3000000000000007</v>
       </c>
       <c r="E35" s="10">
         <f>C35*D35</f>
-        <v>46000</v>
+        <v>56440.000000000007</v>
       </c>
       <c r="F35" s="33">
         <f>E35*0.002</f>
-        <v>92</v>
+        <v>112.88000000000002</v>
       </c>
       <c r="G35" s="32">
         <f>E35*0.000068</f>
-        <v>3.1280000000000001</v>
+        <v>3.8379200000000004</v>
       </c>
       <c r="H35" s="32">
         <f>E35*0.00001</f>
-        <v>0.46</v>
+        <v>0.56440000000000012</v>
       </c>
       <c r="I35" s="32">
         <f>(F35+G35+H35)*0.07</f>
-        <v>6.69116</v>
+        <v>8.2097624000000025</v>
       </c>
       <c r="J35" s="32">
         <f>E35-F35-G35-H35-I35</f>
-        <v>45897.720840000002</v>
+        <v>56314.507917600007</v>
       </c>
       <c r="M35" s="20"/>
     </row>
@@ -8296,21 +8241,21 @@
       </c>
       <c r="B36" s="11">
         <f>(D35-D34)/D34</f>
-        <v>2.2222222222222143E-2</v>
+        <v>0.38333333333333347</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="10"/>
       <c r="E36" s="19">
         <f>E35-E34</f>
-        <v>1000</v>
+        <v>15640.000000000007</v>
       </c>
       <c r="F36" s="19"/>
       <c r="G36" s="19"/>
       <c r="H36" s="19"/>
       <c r="I36" s="19"/>
-      <c r="J36" s="19">
+      <c r="J36" s="32">
         <f>J35-J34</f>
-        <v>798.05034000000887</v>
+        <v>15424.13999760001</v>
       </c>
       <c r="M36" s="20"/>
     </row>
@@ -9816,12 +9761,12 @@
     <col min="1" max="1" width="10.109375" style="41" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.44140625" style="20" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5546875" style="98" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="98" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" style="98" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="5.5546875" style="98" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.5546875" style="98" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" style="98" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="97" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8" style="97" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="5.5546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.5546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" style="97" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.88671875" style="20"/>
   </cols>
   <sheetData>
@@ -10054,11 +9999,11 @@
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="E8" s="98">
+      <c r="E8" s="97">
         <f>E7-E6</f>
         <v>89200</v>
       </c>
-      <c r="J8" s="98">
+      <c r="J8" s="97">
         <f>J7-J6</f>
         <v>86618.118248000159</v>
       </c>
@@ -11318,31 +11263,31 @@
         <f>SUM(C38:C44)</f>
         <v>80000</v>
       </c>
-      <c r="D45" s="98">
+      <c r="D45" s="97">
         <f>E45/C45</f>
         <v>17.399999999999999</v>
       </c>
-      <c r="E45" s="98">
+      <c r="E45" s="97">
         <f t="shared" ref="E45:J45" si="14">SUM(E38:E44)</f>
         <v>1392000</v>
       </c>
-      <c r="F45" s="98">
+      <c r="F45" s="97">
         <f t="shared" si="14"/>
         <v>2784</v>
       </c>
-      <c r="G45" s="98">
+      <c r="G45" s="97">
         <f t="shared" si="14"/>
         <v>94.655999999999992</v>
       </c>
-      <c r="H45" s="98">
+      <c r="H45" s="97">
         <f t="shared" si="14"/>
         <v>13.920000000000002</v>
       </c>
-      <c r="I45" s="98">
+      <c r="I45" s="97">
         <f t="shared" si="14"/>
         <v>202.48032000000001</v>
       </c>
-      <c r="J45" s="98">
+      <c r="J45" s="97">
         <f t="shared" si="14"/>
         <v>1395095.05632</v>
       </c>
@@ -11735,31 +11680,31 @@
         <f>SUM(C55:C56)</f>
         <v>81000</v>
       </c>
-      <c r="D57" s="98">
+      <c r="D57" s="97">
         <f>E57/C57</f>
         <v>14.8</v>
       </c>
-      <c r="E57" s="98">
+      <c r="E57" s="97">
         <f t="shared" ref="E57:J57" si="17">SUM(E55:E56)</f>
         <v>1198800</v>
       </c>
-      <c r="F57" s="98">
+      <c r="F57" s="97">
         <f t="shared" si="17"/>
         <v>2397.6</v>
       </c>
-      <c r="G57" s="98">
+      <c r="G57" s="97">
         <f t="shared" si="17"/>
         <v>81.5184</v>
       </c>
-      <c r="H57" s="98">
+      <c r="H57" s="97">
         <f t="shared" si="17"/>
         <v>11.988000000000001</v>
       </c>
-      <c r="I57" s="98">
+      <c r="I57" s="97">
         <f t="shared" si="17"/>
         <v>174.37744800000002</v>
       </c>
-      <c r="J57" s="98">
+      <c r="J57" s="97">
         <f t="shared" si="17"/>
         <v>1201465.4838479999</v>
       </c>
@@ -11879,31 +11824,31 @@
         <f>SUM(C59:C60)</f>
         <v>80000</v>
       </c>
-      <c r="D61" s="98">
+      <c r="D61" s="97">
         <f>E61/C61</f>
         <v>14.855</v>
       </c>
-      <c r="E61" s="98">
+      <c r="E61" s="97">
         <f t="shared" ref="E61:J61" si="18">SUM(E59:E60)</f>
         <v>1188400</v>
       </c>
-      <c r="F61" s="98">
+      <c r="F61" s="97">
         <f t="shared" si="18"/>
         <v>80</v>
       </c>
-      <c r="G61" s="98">
+      <c r="G61" s="97">
         <f t="shared" si="18"/>
         <v>2.72</v>
       </c>
-      <c r="H61" s="98">
+      <c r="H61" s="97">
         <f t="shared" si="18"/>
         <v>0.4</v>
       </c>
-      <c r="I61" s="98">
+      <c r="I61" s="97">
         <f t="shared" si="18"/>
         <v>5.8184000000000005</v>
       </c>
-      <c r="J61" s="98">
+      <c r="J61" s="97">
         <f t="shared" si="18"/>
         <v>-1111088.6078319999</v>
       </c>
@@ -12313,7 +12258,7 @@
       </c>
     </row>
     <row r="76" spans="1:10">
-      <c r="E76" s="98">
+      <c r="E76" s="97">
         <f>E55+E72</f>
         <v>1198800</v>
       </c>
@@ -13365,7 +13310,7 @@
         <f>SUM(C6:C7)</f>
         <v>50000</v>
       </c>
-      <c r="D8" s="96">
+      <c r="D8" s="95">
         <f>E8/C8</f>
         <v>10.4</v>
       </c>
@@ -13452,7 +13397,7 @@
         <f>C8+C9</f>
         <v>60000</v>
       </c>
-      <c r="D10" s="95">
+      <c r="D10" s="94">
         <f>E10/C10</f>
         <v>9</v>
       </c>
@@ -21251,31 +21196,31 @@
         <v>2500</v>
       </c>
       <c r="D22" s="10">
-        <v>11.2</v>
+        <v>9.6</v>
       </c>
       <c r="E22" s="19">
         <f>C22*D22</f>
-        <v>28000</v>
+        <v>24000</v>
       </c>
       <c r="F22" s="19">
         <f>E22*0.002</f>
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G22" s="19">
         <f>E22*0.000068</f>
-        <v>1.9039999999999999</v>
+        <v>1.6319999999999999</v>
       </c>
       <c r="H22" s="19">
         <f>E22*0.00001</f>
-        <v>0.28000000000000003</v>
+        <v>0.24000000000000002</v>
       </c>
       <c r="I22" s="19">
         <f>(F22+G22+H22)*0.07</f>
-        <v>4.0728800000000005</v>
+        <v>3.4910400000000004</v>
       </c>
       <c r="J22" s="19">
         <f>E22+F22+I22+G22+H22</f>
-        <v>28062.256879999997</v>
+        <v>24053.363040000004</v>
       </c>
       <c r="M22" s="20"/>
     </row>
@@ -21283,7 +21228,7 @@
       <c r="A23" s="41"/>
       <c r="B23" s="23">
         <f>(D22-D21)/D21</f>
-        <v>-0.5757575757575758</v>
+        <v>-0.63636363636363624</v>
       </c>
       <c r="C23" s="21">
         <f>SUM(C21:C22)</f>
@@ -21291,38 +21236,38 @@
       </c>
       <c r="D23" s="61">
         <f>E23/C23</f>
-        <v>24.5</v>
+        <v>24.3</v>
       </c>
       <c r="E23" s="21">
         <f t="shared" ref="E23:J23" si="11">SUM(E21:E22)</f>
-        <v>490000</v>
+        <v>486000</v>
       </c>
       <c r="F23" s="21">
         <f t="shared" si="11"/>
-        <v>980</v>
+        <v>972</v>
       </c>
       <c r="G23" s="21">
         <f t="shared" si="11"/>
-        <v>33.319999999999993</v>
+        <v>33.047999999999995</v>
       </c>
       <c r="H23" s="21">
         <f t="shared" si="11"/>
-        <v>4.9000000000000004</v>
+        <v>4.8600000000000003</v>
       </c>
       <c r="I23" s="21">
         <f t="shared" si="11"/>
-        <v>71.275400000000005</v>
+        <v>70.693560000000005</v>
       </c>
       <c r="J23" s="21">
         <f t="shared" si="11"/>
-        <v>491089.49540000001</v>
+        <v>487080.60156000004</v>
       </c>
       <c r="K23" s="22"/>
       <c r="L23" s="23"/>
       <c r="M23" s="20"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="C24" s="97" t="s">
+      <c r="C24" s="96" t="s">
         <v>35</v>
       </c>
     </row>
@@ -22005,80 +21950,80 @@
       <c r="K4" s="23"/>
     </row>
     <row r="5" spans="1:11" s="20" customFormat="1">
-      <c r="A5" s="7">
-        <v>45875</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="A5" s="13">
+        <v>46085</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="15">
         <v>5000</v>
       </c>
-      <c r="D5" s="43">
-        <v>6</v>
-      </c>
-      <c r="E5" s="19">
+      <c r="D5" s="38">
+        <v>6.5</v>
+      </c>
+      <c r="E5" s="17">
         <f>C5*D5</f>
-        <v>30000</v>
-      </c>
-      <c r="F5" s="19">
+        <v>32500</v>
+      </c>
+      <c r="F5" s="17">
         <f>E5*0.002</f>
-        <v>60</v>
-      </c>
-      <c r="G5" s="19">
+        <v>65</v>
+      </c>
+      <c r="G5" s="17">
         <f>E5*0.000068</f>
-        <v>2.04</v>
-      </c>
-      <c r="H5" s="19">
+        <v>2.21</v>
+      </c>
+      <c r="H5" s="17">
         <f>E5*0.00001</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="I5" s="19">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="I5" s="17">
         <f>(F5+G5+H5)*0.07</f>
-        <v>4.3638000000000003</v>
-      </c>
-      <c r="J5" s="19">
+        <v>4.7274500000000002</v>
+      </c>
+      <c r="J5" s="17">
         <f>E5+F5+I5+G5+H5</f>
-        <v>30066.703799999999</v>
+        <v>32572.262449999998</v>
       </c>
     </row>
     <row r="6" spans="1:11" s="20" customFormat="1">
-      <c r="A6" s="41"/>
-      <c r="B6" s="23">
+      <c r="A6" s="39"/>
+      <c r="B6" s="6">
         <f>(D5-D4)/D4</f>
-        <v>-0.2</v>
-      </c>
-      <c r="C6" s="21">
+        <v>-0.13333333333333333</v>
+      </c>
+      <c r="C6" s="5">
         <f>SUM(C4:C5)</f>
         <v>25000</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="34">
         <f>E6/C6</f>
-        <v>7.2</v>
-      </c>
-      <c r="E6" s="21">
+        <v>7.3</v>
+      </c>
+      <c r="E6" s="5">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>180000</v>
-      </c>
-      <c r="F6" s="21">
+        <v>182500</v>
+      </c>
+      <c r="F6" s="5">
         <f t="shared" si="1"/>
-        <v>360</v>
-      </c>
-      <c r="G6" s="21">
+        <v>365</v>
+      </c>
+      <c r="G6" s="5">
         <f t="shared" si="1"/>
-        <v>11.635999999999999</v>
-      </c>
-      <c r="H6" s="21">
+        <v>11.806000000000001</v>
+      </c>
+      <c r="H6" s="5">
         <f t="shared" si="1"/>
-        <v>1.8000000000000003</v>
-      </c>
-      <c r="I6" s="21">
+        <v>1.8250000000000002</v>
+      </c>
+      <c r="I6" s="5">
         <f t="shared" si="1"/>
-        <v>26.140520000000006</v>
-      </c>
-      <c r="J6" s="21">
+        <v>26.504170000000006</v>
+      </c>
+      <c r="J6" s="5">
         <f t="shared" si="1"/>
-        <v>180399.57651999997</v>
+        <v>182905.13516999999</v>
       </c>
       <c r="K6" s="23"/>
     </row>
@@ -22093,38 +22038,38 @@
         <v>5000</v>
       </c>
       <c r="D7" s="43">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="E7" s="19">
         <f>C7*D7</f>
-        <v>30000</v>
+        <v>30500</v>
       </c>
       <c r="F7" s="19">
         <f>E7*0.002</f>
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="19">
         <f>E7*0.000068</f>
-        <v>2.04</v>
+        <v>2.0739999999999998</v>
       </c>
       <c r="H7" s="19">
         <f>E7*0.00001</f>
-        <v>0.30000000000000004</v>
+        <v>0.30500000000000005</v>
       </c>
       <c r="I7" s="19">
         <f>(F7+G7+H7)*0.07</f>
-        <v>4.3638000000000003</v>
+        <v>4.4365300000000003</v>
       </c>
       <c r="J7" s="19">
         <f>E7+F7+I7+G7+H7</f>
-        <v>30066.703799999999</v>
+        <v>30567.81553</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="20" customFormat="1">
       <c r="A8" s="41"/>
       <c r="B8" s="23">
         <f>(D7-D6)/D6</f>
-        <v>-0.16666666666666669</v>
+        <v>-0.16438356164383564</v>
       </c>
       <c r="C8" s="21">
         <f>SUM(C6:C7)</f>
@@ -22132,31 +22077,31 @@
       </c>
       <c r="D8" s="31">
         <f>E8/C8</f>
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="E8" s="21">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>210000</v>
+        <v>213000</v>
       </c>
       <c r="F8" s="21">
         <f t="shared" si="2"/>
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="G8" s="21">
         <f t="shared" si="2"/>
-        <v>13.675999999999998</v>
+        <v>13.88</v>
       </c>
       <c r="H8" s="21">
         <f t="shared" si="2"/>
-        <v>2.1000000000000005</v>
+        <v>2.1300000000000003</v>
       </c>
       <c r="I8" s="21">
         <f t="shared" si="2"/>
-        <v>30.504320000000007</v>
+        <v>30.940700000000007</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="2"/>
-        <v>210466.28031999996</v>
+        <v>213472.95069999999</v>
       </c>
       <c r="K8" s="23"/>
     </row>
@@ -25192,31 +25137,31 @@
         <v>5000</v>
       </c>
       <c r="D5" s="43">
-        <v>9.3000000000000007</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="E5" s="19">
         <f>C5*D5</f>
-        <v>46500</v>
+        <v>49000</v>
       </c>
       <c r="F5" s="19">
         <f>E5*0.002</f>
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G5" s="19">
         <f>E5*0.000068</f>
-        <v>3.1619999999999999</v>
+        <v>3.3319999999999999</v>
       </c>
       <c r="H5" s="19">
         <f>E5*0.00001</f>
-        <v>0.46500000000000002</v>
+        <v>0.49000000000000005</v>
       </c>
       <c r="I5" s="19">
         <f>(F5+G5+H5)*0.07</f>
-        <v>6.7638900000000017</v>
+        <v>7.1275399999999998</v>
       </c>
       <c r="J5" s="19">
         <f>E5+F5+I5+G5+H5</f>
-        <v>46603.390889999995</v>
+        <v>49108.949540000001</v>
       </c>
       <c r="M5" s="20"/>
     </row>
@@ -25232,31 +25177,31 @@
       </c>
       <c r="D6" s="31">
         <f>E6/C6</f>
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="E6" s="21">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>292500</v>
+        <v>295000</v>
       </c>
       <c r="F6" s="21">
         <f t="shared" si="1"/>
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="G6" s="21">
         <f t="shared" si="1"/>
-        <v>18.89</v>
+        <v>19.059999999999999</v>
       </c>
       <c r="H6" s="21">
         <f t="shared" si="1"/>
-        <v>2.9249999999999998</v>
+        <v>2.95</v>
       </c>
       <c r="I6" s="21">
         <f t="shared" si="1"/>
-        <v>42.477050000000006</v>
+        <v>42.840699999999998</v>
       </c>
       <c r="J6" s="21">
         <f t="shared" si="1"/>
-        <v>293149.29204999999</v>
+        <v>295654.85070000001</v>
       </c>
       <c r="K6" s="23"/>
       <c r="L6" s="20"/>
@@ -25945,7 +25890,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05574364-77F0-49AB-A1F4-209718CEC5C7}">
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="47" customWidth="1"/>
@@ -26259,93 +26204,70 @@
       <c r="M8" s="58"/>
       <c r="N8" s="58"/>
     </row>
-    <row r="9" spans="1:14" s="59" customFormat="1" ht="21">
-      <c r="A9" s="63">
-        <v>45882</v>
+    <row r="9" spans="1:14" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A9" s="52">
+        <v>45525</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C9" s="9">
-        <v>2500</v>
-      </c>
-      <c r="D9" s="10">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="E9" s="19">
+        <f>C8</f>
+        <v>17500</v>
+      </c>
+      <c r="D9" s="32">
+        <v>11.1</v>
+      </c>
+      <c r="E9" s="10">
         <f>C9*D9</f>
-        <v>24500</v>
-      </c>
-      <c r="F9" s="19">
+        <v>194250</v>
+      </c>
+      <c r="F9" s="33">
         <f>E9*0.002</f>
-        <v>49</v>
-      </c>
-      <c r="G9" s="19">
-        <f>E9*0.00006</f>
-        <v>1.47</v>
-      </c>
-      <c r="H9" s="19">
+        <v>388.5</v>
+      </c>
+      <c r="G9" s="32">
+        <f>E9*0.000068</f>
+        <v>13.209</v>
+      </c>
+      <c r="H9" s="32">
         <f>E9*0.00001</f>
-        <v>0.24500000000000002</v>
-      </c>
-      <c r="I9" s="19">
+        <v>1.9425000000000001</v>
+      </c>
+      <c r="I9" s="32">
         <f>(F9+G9+H9)*0.07</f>
-        <v>3.5500500000000001</v>
-      </c>
-      <c r="J9" s="19">
-        <f>E9+F9+I9+G9+H9</f>
-        <v>24554.265050000002</v>
-      </c>
-      <c r="K9" s="30"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="11"/>
-      <c r="N9" s="12"/>
-    </row>
-    <row r="10" spans="1:14" s="18" customFormat="1" ht="21">
+        <v>28.255605000000003</v>
+      </c>
+      <c r="J9" s="32">
+        <f>E9-F9-G9-H9-I9</f>
+        <v>193818.09289499998</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="52"/>
-      <c r="B10" s="72">
-        <f>(D9-D8)/D8</f>
-        <v>-7.5471698113207447E-2</v>
-      </c>
-      <c r="C10" s="9">
-        <f>SUM(C8:C9)</f>
-        <v>20000</v>
-      </c>
-      <c r="D10" s="60">
-        <f>E10/C10</f>
-        <v>10.5</v>
-      </c>
-      <c r="E10" s="9">
-        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
-        <v>210000</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="3"/>
-        <v>420</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="3"/>
-        <v>12.600000000000001</v>
-      </c>
-      <c r="H10" s="9">
-        <f t="shared" si="3"/>
-        <v>2.1</v>
-      </c>
-      <c r="I10" s="9">
-        <f t="shared" si="3"/>
-        <v>30.428999999999998</v>
-      </c>
-      <c r="J10" s="9">
-        <f t="shared" si="3"/>
-        <v>210465.12900000002</v>
-      </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="12"/>
-      <c r="M10" s="58"/>
-      <c r="N10" s="58"/>
-    </row>
-    <row r="11" spans="1:14" s="12" customFormat="1">
-      <c r="A11" s="63"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="10">
+        <f>E9-E8</f>
+        <v>8750</v>
+      </c>
+      <c r="F10" s="33"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="10">
+        <f>J9-J8</f>
+        <v>7907.2289449999516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="52"/>
+      <c r="B11" s="12"/>
       <c r="C11" s="9"/>
       <c r="D11" s="10"/>
       <c r="E11" s="19"/>
@@ -26354,163 +26276,9 @@
       <c r="H11" s="19"/>
       <c r="I11" s="19"/>
       <c r="J11" s="19"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="11"/>
-    </row>
-    <row r="12" spans="1:14" s="29" customFormat="1" ht="21">
-      <c r="A12" s="52">
-        <v>45530</v>
-      </c>
-      <c r="B12" s="59"/>
-      <c r="C12" s="9">
-        <f>C3</f>
-        <v>2500</v>
-      </c>
-      <c r="D12" s="60">
-        <v>0.14330000000000001</v>
-      </c>
-      <c r="E12" s="56"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="56"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="57">
-        <f>C12*D12</f>
-        <v>358.25</v>
-      </c>
-      <c r="J12" s="57">
-        <f>I12*0.9</f>
-        <v>322.42500000000001</v>
-      </c>
-      <c r="K12" s="10"/>
-      <c r="L12" s="12"/>
-      <c r="M12" s="58"/>
-      <c r="N12" s="58"/>
-    </row>
-    <row r="13" spans="1:14" s="12" customFormat="1">
-      <c r="A13" s="63">
-        <v>45460</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="9">
-        <v>2500</v>
-      </c>
-      <c r="D13" s="94">
-        <v>10.5</v>
-      </c>
-      <c r="E13" s="19">
-        <f>C13*D13</f>
-        <v>26250</v>
-      </c>
-      <c r="F13" s="19">
-        <f>E13*0.002</f>
-        <v>52.5</v>
-      </c>
-      <c r="G13" s="19">
-        <f>E13*0.00006</f>
-        <v>1.575</v>
-      </c>
-      <c r="H13" s="19">
-        <f>E13*0.00001</f>
-        <v>0.26250000000000001</v>
-      </c>
-      <c r="I13" s="19">
-        <f>(F13+G13+H13)*0.07</f>
-        <v>3.8036250000000007</v>
-      </c>
-      <c r="J13" s="19">
-        <f>E13+F13+I13+G13+H13</f>
-        <v>26308.141125000002</v>
-      </c>
-      <c r="K13" s="30"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="11"/>
-    </row>
-    <row r="14" spans="1:14" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A14" s="52">
-        <v>45525</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="9">
-        <f>C13</f>
-        <v>2500</v>
-      </c>
-      <c r="D14" s="32">
-        <v>11.5</v>
-      </c>
-      <c r="E14" s="10">
-        <f>C14*D14</f>
-        <v>28750</v>
-      </c>
-      <c r="F14" s="33">
-        <f>E14*0.002</f>
-        <v>57.5</v>
-      </c>
-      <c r="G14" s="32">
-        <f>E14*0.000068</f>
-        <v>1.9550000000000001</v>
-      </c>
-      <c r="H14" s="32">
-        <f>E14*0.00001</f>
-        <v>0.28750000000000003</v>
-      </c>
-      <c r="I14" s="32">
-        <f>(F14+G14+H14)*0.07</f>
-        <v>4.1819750000000004</v>
-      </c>
-      <c r="J14" s="32">
-        <f>E14-F14-G14-H14-I14</f>
-        <v>28686.075525</v>
-      </c>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="52"/>
-      <c r="B15" s="11">
-        <f>(D14-D13)/D13</f>
-        <v>9.5238095238095233E-2</v>
-      </c>
-      <c r="C15" s="9"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="33"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="32"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="52" t="s">
-        <v>3</v>
-      </c>
-      <c r="B16" s="12"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="19">
-        <f>E14-E13</f>
-        <v>2500</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="19"/>
-      <c r="I16" s="19"/>
-      <c r="J16" s="19">
-        <f>J14-J13</f>
-        <v>2377.9343999999983</v>
-      </c>
-    </row>
-    <row r="17" spans="10:10">
-      <c r="J17" s="50">
-        <f>J12+J16</f>
-        <v>2700.3593999999985</v>
-      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="J12" s="50"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -28155,7 +27923,7 @@
       </c>
     </row>
     <row r="19" spans="1:10">
-      <c r="J19" s="99">
+      <c r="J19" s="98">
         <f>J15+J18</f>
         <v>472.95973000000231</v>
       </c>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1666" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C871719-7412-4024-B898-59048F494210}"/>
+  <xr:revisionPtr revIDLastSave="1691" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F276051-CB6D-4BE3-BEAC-7A952E77A7F8}"/>
   <bookViews>
-    <workbookView xWindow="48" yWindow="1356" windowWidth="10788" windowHeight="10812" tabRatio="461" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="408" yWindow="1476" windowWidth="14820" windowHeight="10764" tabRatio="461" firstSheet="19" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
@@ -32,17 +32,15 @@
     <sheet name="ORI" sheetId="184" r:id="rId17"/>
     <sheet name="PTG" sheetId="216" r:id="rId18"/>
     <sheet name="PTT" sheetId="224" r:id="rId19"/>
-    <sheet name="Sheet1" sheetId="225" r:id="rId20"/>
-    <sheet name="RCL" sheetId="161" r:id="rId21"/>
-    <sheet name="SCC" sheetId="152" r:id="rId22"/>
-    <sheet name="SENA" sheetId="183" r:id="rId23"/>
-    <sheet name="SINGER" sheetId="203" r:id="rId24"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId25"/>
-    <sheet name="TFFIF" sheetId="214" r:id="rId26"/>
-    <sheet name="TOA" sheetId="218" r:id="rId27"/>
-    <sheet name="TVO" sheetId="221" r:id="rId28"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId29"/>
-    <sheet name="WHART" sheetId="171" r:id="rId30"/>
+    <sheet name="RCL" sheetId="161" r:id="rId20"/>
+    <sheet name="SENA" sheetId="183" r:id="rId21"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
+    <sheet name="TFFIF" sheetId="214" r:id="rId24"/>
+    <sheet name="TOA" sheetId="218" r:id="rId25"/>
+    <sheet name="TVO" sheetId="221" r:id="rId26"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId27"/>
+    <sheet name="WHART" sheetId="171" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -65,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="41">
   <si>
     <t>BUY</t>
   </si>
@@ -146,9 +144,6 @@
   </si>
   <si>
     <t>RCL</t>
-  </si>
-  <si>
-    <t>SCC</t>
   </si>
   <si>
     <t>SENA</t>
@@ -12609,38 +12604,38 @@
         <v>5000</v>
       </c>
       <c r="D10" s="43">
-        <v>4.24</v>
+        <v>4.5599999999999996</v>
       </c>
       <c r="E10" s="19">
         <f>C10*D10</f>
-        <v>21200</v>
+        <v>22799.999999999996</v>
       </c>
       <c r="F10" s="19">
         <f>E10*0.002</f>
-        <v>42.4</v>
+        <v>45.599999999999994</v>
       </c>
       <c r="G10" s="19">
         <f>E10*0.00006</f>
-        <v>1.272</v>
+        <v>1.3679999999999999</v>
       </c>
       <c r="H10" s="19">
         <f>E10*0.00001</f>
-        <v>0.21200000000000002</v>
+        <v>0.22799999999999998</v>
       </c>
       <c r="I10" s="19">
         <f>(F10+G10+H10)*0.07</f>
-        <v>3.0718800000000002</v>
+        <v>3.3037200000000002</v>
       </c>
       <c r="J10" s="19">
         <f>E10+F10+I10+G10+H10</f>
-        <v>21246.955880000001</v>
+        <v>22850.499719999993</v>
       </c>
     </row>
     <row r="11" spans="1:13" s="1" customFormat="1">
       <c r="A11" s="52"/>
       <c r="B11" s="11">
         <f>(D10-D9)/D9</f>
-        <v>-0.43087248322147648</v>
+        <v>-0.3879194630872484</v>
       </c>
       <c r="C11" s="9">
         <f>SUM(C9:C10)</f>
@@ -12648,31 +12643,31 @@
       </c>
       <c r="D11" s="60">
         <f>E11/C11</f>
-        <v>6.9484374999999998</v>
+        <v>6.9984374999999996</v>
       </c>
       <c r="E11" s="9">
         <f t="shared" ref="E11:J11" si="3">SUM(E9:E10)</f>
-        <v>222350</v>
+        <v>223950</v>
       </c>
       <c r="F11" s="9">
         <f t="shared" si="3"/>
-        <v>444.7</v>
+        <v>447.9</v>
       </c>
       <c r="G11" s="9">
         <f t="shared" si="3"/>
-        <v>13.341000000000001</v>
+        <v>13.437000000000001</v>
       </c>
       <c r="H11" s="9">
         <f t="shared" si="3"/>
-        <v>2.2235000000000005</v>
+        <v>2.2395000000000005</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="3"/>
-        <v>32.218515000000011</v>
+        <v>32.450355000000009</v>
       </c>
       <c r="J11" s="9">
         <f t="shared" si="3"/>
-        <v>222842.48301499998</v>
+        <v>224446.02685499997</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -14120,7 +14115,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="35" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -14598,7 +14593,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -17154,15 +17149,6 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F4434CF-52C0-49FA-BAB4-58743FBD0F61}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:N51"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -19050,322 +19036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{650D376F-67DD-4980-BF1B-8A055D89D41A}">
-  <dimension ref="A1:M8"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="10.6640625" style="35" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="20" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="20" customWidth="1"/>
-    <col min="6" max="6" width="9" style="20"/>
-    <col min="7" max="7" width="6.6640625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="5.77734375" style="20" customWidth="1"/>
-    <col min="9" max="9" width="7.21875" style="20" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" style="20" customWidth="1"/>
-    <col min="11" max="11" width="18" style="20" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="20"/>
-    <col min="13" max="13" width="8.88671875" style="23"/>
-    <col min="14" max="16384" width="8.88671875" style="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="20" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="12" customFormat="1">
-      <c r="A2" s="36">
-        <v>44459</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>300</v>
-      </c>
-      <c r="D2" s="16">
-        <v>410</v>
-      </c>
-      <c r="E2" s="17">
-        <f>C2*D2</f>
-        <v>123000</v>
-      </c>
-      <c r="F2" s="17">
-        <f>E2*0.002</f>
-        <v>246</v>
-      </c>
-      <c r="G2" s="17">
-        <f>E2*0.00006</f>
-        <v>7.38</v>
-      </c>
-      <c r="H2" s="17">
-        <f>E2*0.00001</f>
-        <v>1.2300000000000002</v>
-      </c>
-      <c r="I2" s="17">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>17.822700000000001</v>
-      </c>
-      <c r="J2" s="17">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>123272.4327</v>
-      </c>
-      <c r="K2" s="27"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="28"/>
-    </row>
-    <row r="3" spans="1:13" s="12" customFormat="1">
-      <c r="A3" s="36">
-        <v>44469</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15">
-        <v>300</v>
-      </c>
-      <c r="D3" s="16">
-        <v>400</v>
-      </c>
-      <c r="E3" s="17">
-        <f>C3*D3</f>
-        <v>120000</v>
-      </c>
-      <c r="F3" s="17">
-        <f>E3*0.002</f>
-        <v>240</v>
-      </c>
-      <c r="G3" s="17">
-        <f>E3*0.00006</f>
-        <v>7.2</v>
-      </c>
-      <c r="H3" s="17">
-        <f>E3*0.00001</f>
-        <v>1.2000000000000002</v>
-      </c>
-      <c r="I3" s="17">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>17.388000000000002</v>
-      </c>
-      <c r="J3" s="17">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>120265.788</v>
-      </c>
-      <c r="K3" s="30"/>
-      <c r="L3" s="10"/>
-      <c r="M3" s="11"/>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="66"/>
-      <c r="B4" s="6">
-        <f>(D3-D2)/D2</f>
-        <v>-2.4390243902439025E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>600</v>
-      </c>
-      <c r="D4" s="67">
-        <f>E4/C4</f>
-        <v>405</v>
-      </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>243000</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>486</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>14.58</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.4300000000000006</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>35.210700000000003</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>243538.22070000001</v>
-      </c>
-      <c r="L4" s="23"/>
-      <c r="M4" s="20"/>
-    </row>
-    <row r="5" spans="1:13" s="12" customFormat="1">
-      <c r="A5" s="36">
-        <v>44579</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="15">
-        <v>300</v>
-      </c>
-      <c r="D5" s="16">
-        <v>384</v>
-      </c>
-      <c r="E5" s="17">
-        <f>C5*D5</f>
-        <v>115200</v>
-      </c>
-      <c r="F5" s="17">
-        <f>E5*0.002</f>
-        <v>230.4</v>
-      </c>
-      <c r="G5" s="17">
-        <f>E5*0.00006</f>
-        <v>6.9119999999999999</v>
-      </c>
-      <c r="H5" s="17">
-        <f>E5*0.00001</f>
-        <v>1.1520000000000001</v>
-      </c>
-      <c r="I5" s="17">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>16.69248</v>
-      </c>
-      <c r="J5" s="17">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>115455.15647999999</v>
-      </c>
-      <c r="K5" s="30"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="11"/>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="66"/>
-      <c r="B6" s="6">
-        <f>(D5-D4)/D4</f>
-        <v>-5.185185185185185E-2</v>
-      </c>
-      <c r="C6" s="5">
-        <f>SUM(C4:C5)</f>
-        <v>900</v>
-      </c>
-      <c r="D6" s="67">
-        <f>E6/C6</f>
-        <v>398</v>
-      </c>
-      <c r="E6" s="5">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>358200</v>
-      </c>
-      <c r="F6" s="5">
-        <f t="shared" si="1"/>
-        <v>716.4</v>
-      </c>
-      <c r="G6" s="5">
-        <f t="shared" si="1"/>
-        <v>21.492000000000001</v>
-      </c>
-      <c r="H6" s="5">
-        <f t="shared" si="1"/>
-        <v>3.5820000000000007</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="1"/>
-        <v>51.903180000000006</v>
-      </c>
-      <c r="J6" s="5">
-        <f t="shared" si="1"/>
-        <v>358993.37718000001</v>
-      </c>
-      <c r="L6" s="23"/>
-      <c r="M6" s="20"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="63">
-        <v>44579</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="9">
-        <v>300</v>
-      </c>
-      <c r="D7" s="10">
-        <v>207</v>
-      </c>
-      <c r="E7" s="19">
-        <f>C7*D7</f>
-        <v>62100</v>
-      </c>
-      <c r="F7" s="19">
-        <f>E7*0.002</f>
-        <v>124.2</v>
-      </c>
-      <c r="G7" s="19">
-        <f>E7*0.00006</f>
-        <v>3.726</v>
-      </c>
-      <c r="H7" s="19">
-        <f>E7*0.00001</f>
-        <v>0.621</v>
-      </c>
-      <c r="I7" s="19">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>8.9982900000000008</v>
-      </c>
-      <c r="J7" s="19">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>62237.545290000002</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="B8" s="23">
-        <f>(D7-D6)/D6</f>
-        <v>-0.47989949748743721</v>
-      </c>
-      <c r="C8" s="21">
-        <f>SUM(C6:C7)</f>
-        <v>1200</v>
-      </c>
-      <c r="D8" s="64">
-        <f>E8/C8</f>
-        <v>350.25</v>
-      </c>
-      <c r="E8" s="21">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>420300</v>
-      </c>
-      <c r="F8" s="21">
-        <f t="shared" si="2"/>
-        <v>840.6</v>
-      </c>
-      <c r="G8" s="21">
-        <f t="shared" si="2"/>
-        <v>25.218</v>
-      </c>
-      <c r="H8" s="21">
-        <f t="shared" si="2"/>
-        <v>4.2030000000000012</v>
-      </c>
-      <c r="I8" s="21">
-        <f t="shared" si="2"/>
-        <v>60.901470000000003</v>
-      </c>
-      <c r="J8" s="21">
-        <f t="shared" si="2"/>
-        <v>421230.92246999999</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -19387,7 +19058,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1">
@@ -19981,7 +19652,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -20004,7 +19675,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="12" customFormat="1">
@@ -20385,7 +20056,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -20408,7 +20079,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="20" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -21268,7 +20939,7 @@
     </row>
     <row r="24" spans="1:13">
       <c r="C24" s="96" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -21810,7 +21481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D30CFA7-C46B-4885-A4A3-CF2E8439A3D7}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -21830,7 +21501,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="47" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="18" customFormat="1" ht="15.6">
@@ -22428,7 +22099,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E0B64A-B432-4F71-9E82-2EF3D53BA2E8}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -22451,7 +22122,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="12" customFormat="1">
@@ -22764,7 +22435,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2313500C-829E-4589-85F6-0C28EBDE7508}">
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -23125,7 +22796,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -23148,7 +22819,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="18" customFormat="1" ht="15.6">
@@ -23764,6 +23435,661 @@
       <c r="J18" s="17">
         <f t="shared" si="6"/>
         <v>7773.2070799999929</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
+  <sheetPr>
+    <tabColor rgb="FFFF0000"/>
+  </sheetPr>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="7.44140625" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="20" customWidth="1"/>
+    <col min="6" max="6" width="8.5546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="6.77734375" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="20" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18" style="20" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="20"/>
+    <col min="13" max="13" width="8.88671875" style="23"/>
+    <col min="14" max="16384" width="8.88671875" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="B1" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="12" customFormat="1">
+      <c r="A2" s="36">
+        <v>44566</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15">
+        <v>10000</v>
+      </c>
+      <c r="D2" s="16">
+        <v>12.5</v>
+      </c>
+      <c r="E2" s="17">
+        <f>C2*D2</f>
+        <v>125000</v>
+      </c>
+      <c r="F2" s="17">
+        <f>E2*0.002</f>
+        <v>250</v>
+      </c>
+      <c r="G2" s="17">
+        <f>E2*0.00006</f>
+        <v>7.5</v>
+      </c>
+      <c r="H2" s="17">
+        <f>E2*0.00001</f>
+        <v>1.25</v>
+      </c>
+      <c r="I2" s="17">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>18.112500000000001</v>
+      </c>
+      <c r="J2" s="17">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>125276.8625</v>
+      </c>
+      <c r="K2" s="27"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="28"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="13">
+        <v>44627</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15">
+        <v>10000</v>
+      </c>
+      <c r="D3" s="38">
+        <v>12.1</v>
+      </c>
+      <c r="E3" s="17">
+        <f>C3*D3</f>
+        <v>121000</v>
+      </c>
+      <c r="F3" s="17">
+        <f>E3*0.002</f>
+        <v>242</v>
+      </c>
+      <c r="G3" s="17">
+        <f>E3*0.000068</f>
+        <v>8.2279999999999998</v>
+      </c>
+      <c r="H3" s="17">
+        <f>E3*0.00001</f>
+        <v>1.2100000000000002</v>
+      </c>
+      <c r="I3" s="17">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>17.600660000000001</v>
+      </c>
+      <c r="J3" s="17">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>121269.03866000001</v>
+      </c>
+      <c r="M3" s="20"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="39"/>
+      <c r="B4" s="70">
+        <f>(D3-D2)/D2</f>
+        <v>-3.2000000000000028E-2</v>
+      </c>
+      <c r="C4" s="5">
+        <f>SUM(C2:C3)</f>
+        <v>20000</v>
+      </c>
+      <c r="D4" s="34">
+        <f>E4/C4</f>
+        <v>12.3</v>
+      </c>
+      <c r="E4" s="45">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>246000</v>
+      </c>
+      <c r="F4" s="5">
+        <f t="shared" si="0"/>
+        <v>492</v>
+      </c>
+      <c r="G4" s="5">
+        <f t="shared" si="0"/>
+        <v>15.728</v>
+      </c>
+      <c r="H4" s="5">
+        <f t="shared" si="0"/>
+        <v>2.46</v>
+      </c>
+      <c r="I4" s="5">
+        <f t="shared" si="0"/>
+        <v>35.713160000000002</v>
+      </c>
+      <c r="J4" s="5">
+        <f t="shared" si="0"/>
+        <v>246545.90116000001</v>
+      </c>
+      <c r="K4" s="23"/>
+      <c r="M4" s="20"/>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="7">
+        <v>45846</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>5000</v>
+      </c>
+      <c r="D5" s="43">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="E5" s="19">
+        <f>C5*D5</f>
+        <v>49000</v>
+      </c>
+      <c r="F5" s="19">
+        <f>E5*0.002</f>
+        <v>98</v>
+      </c>
+      <c r="G5" s="19">
+        <f>E5*0.000068</f>
+        <v>3.3319999999999999</v>
+      </c>
+      <c r="H5" s="19">
+        <f>E5*0.00001</f>
+        <v>0.49000000000000005</v>
+      </c>
+      <c r="I5" s="19">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>7.1275399999999998</v>
+      </c>
+      <c r="J5" s="19">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>49108.949540000001</v>
+      </c>
+      <c r="M5" s="20"/>
+    </row>
+    <row r="6" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A6" s="41"/>
+      <c r="B6" s="70" t="e">
+        <f>(D5-#REF!)/#REF!</f>
+        <v>#REF!</v>
+      </c>
+      <c r="C6" s="21">
+        <f>SUM(C4:C5)</f>
+        <v>25000</v>
+      </c>
+      <c r="D6" s="31">
+        <f>E6/C6</f>
+        <v>11.8</v>
+      </c>
+      <c r="E6" s="21">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>295000</v>
+      </c>
+      <c r="F6" s="21">
+        <f t="shared" si="1"/>
+        <v>590</v>
+      </c>
+      <c r="G6" s="21">
+        <f t="shared" si="1"/>
+        <v>19.059999999999999</v>
+      </c>
+      <c r="H6" s="21">
+        <f t="shared" si="1"/>
+        <v>2.95</v>
+      </c>
+      <c r="I6" s="21">
+        <f t="shared" si="1"/>
+        <v>42.840699999999998</v>
+      </c>
+      <c r="J6" s="21">
+        <f t="shared" si="1"/>
+        <v>295654.85070000001</v>
+      </c>
+      <c r="K6" s="23"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="13"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="38"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="M7" s="20"/>
+    </row>
+    <row r="8" spans="1:14" s="87" customFormat="1" ht="20.399999999999999">
+      <c r="A8" s="46">
+        <v>45524</v>
+      </c>
+      <c r="B8" s="90"/>
+      <c r="C8" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D8" s="37">
+        <v>0.193</v>
+      </c>
+      <c r="E8" s="91"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="91"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="92">
+        <v>965</v>
+      </c>
+      <c r="J8" s="92">
+        <v>868.5</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+    </row>
+    <row r="9" spans="1:14" s="87" customFormat="1">
+      <c r="A9" s="46">
+        <v>44956</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D9" s="38">
+        <v>8.6</v>
+      </c>
+      <c r="E9" s="17">
+        <v>43000</v>
+      </c>
+      <c r="F9" s="17">
+        <v>86</v>
+      </c>
+      <c r="G9" s="17">
+        <v>2.58</v>
+      </c>
+      <c r="H9" s="17">
+        <v>0.43000000000000005</v>
+      </c>
+      <c r="I9" s="17">
+        <v>6.2307000000000006</v>
+      </c>
+      <c r="J9" s="17">
+        <v>43095.240700000002</v>
+      </c>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1">
+      <c r="A10" s="46">
+        <v>45525</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D10" s="24">
+        <v>10.1</v>
+      </c>
+      <c r="E10" s="16">
+        <v>50500</v>
+      </c>
+      <c r="F10" s="25">
+        <v>101</v>
+      </c>
+      <c r="G10" s="24">
+        <v>3.4340000000000002</v>
+      </c>
+      <c r="H10" s="24">
+        <v>0.505</v>
+      </c>
+      <c r="I10" s="24">
+        <v>7.3457300000000005</v>
+      </c>
+      <c r="J10" s="24">
+        <v>50387.715270000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1">
+      <c r="A11" s="46"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17">
+        <v>7500</v>
+      </c>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17">
+        <v>7292.4745699999985</v>
+      </c>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="51"/>
+      <c r="B13" s="87"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="87"/>
+      <c r="F13" s="87"/>
+      <c r="G13" s="87"/>
+      <c r="H13" s="87"/>
+      <c r="I13" s="87"/>
+      <c r="J13" s="93">
+        <v>8160.9745699999985</v>
+      </c>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+    </row>
+    <row r="14" spans="1:14" ht="20.399999999999999">
+      <c r="A14" s="46">
+        <v>45524</v>
+      </c>
+      <c r="B14" s="90"/>
+      <c r="C14" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="37">
+        <v>0.193</v>
+      </c>
+      <c r="E14" s="91"/>
+      <c r="F14" s="27"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="92">
+        <v>965</v>
+      </c>
+      <c r="J14" s="92">
+        <v>868.5</v>
+      </c>
+      <c r="K14" s="10"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="58"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="13">
+        <v>45436</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="89">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E15" s="17">
+        <v>44000</v>
+      </c>
+      <c r="F15" s="17">
+        <v>88</v>
+      </c>
+      <c r="G15" s="17">
+        <v>2.992</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0.44000000000000006</v>
+      </c>
+      <c r="I15" s="17">
+        <v>6.400240000000001</v>
+      </c>
+      <c r="J15" s="17">
+        <v>44097.832240000003</v>
+      </c>
+      <c r="M15" s="20"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="A16" s="46">
+        <v>45530</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D16" s="24">
+        <v>10.3</v>
+      </c>
+      <c r="E16" s="16">
+        <v>51500</v>
+      </c>
+      <c r="F16" s="25">
+        <v>103</v>
+      </c>
+      <c r="G16" s="24">
+        <v>3.5019999999999998</v>
+      </c>
+      <c r="H16" s="24">
+        <v>0.51500000000000001</v>
+      </c>
+      <c r="I16" s="24">
+        <v>7.4911900000000005</v>
+      </c>
+      <c r="J16" s="24">
+        <v>51385.49181</v>
+      </c>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="46"/>
+      <c r="B17" s="28">
+        <v>0.17045454545454544</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="24"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="46" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="14"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="17">
+        <v>7500</v>
+      </c>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
+      <c r="I18" s="17"/>
+      <c r="J18" s="17">
+        <v>7287.6595699999962</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="51"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="49"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="87"/>
+      <c r="G19" s="87"/>
+      <c r="H19" s="87"/>
+      <c r="I19" s="87"/>
+      <c r="J19" s="93">
+        <v>8156.1595699999962</v>
+      </c>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="13">
+        <v>45846</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D20" s="38">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E20" s="17">
+        <f>C20*D20</f>
+        <v>44000</v>
+      </c>
+      <c r="F20" s="17">
+        <f>E20*0.002</f>
+        <v>88</v>
+      </c>
+      <c r="G20" s="17">
+        <f>E20*0.000068</f>
+        <v>2.992</v>
+      </c>
+      <c r="H20" s="17">
+        <f>E20*0.00001</f>
+        <v>0.44000000000000006</v>
+      </c>
+      <c r="I20" s="17">
+        <f>(F20+G20+H20)*0.07</f>
+        <v>6.400240000000001</v>
+      </c>
+      <c r="J20" s="17">
+        <f>E20+F20+I20+G20+H20</f>
+        <v>44097.832240000003</v>
+      </c>
+      <c r="M20" s="20"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1">
+      <c r="A21" s="46">
+        <v>45915</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C21" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D21" s="24">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="E21" s="16">
+        <f>C21*D21</f>
+        <v>48500</v>
+      </c>
+      <c r="F21" s="25">
+        <f>E21*0.002</f>
+        <v>97</v>
+      </c>
+      <c r="G21" s="24">
+        <f>E21*0.000068</f>
+        <v>3.298</v>
+      </c>
+      <c r="H21" s="24">
+        <f>E21*0.00001</f>
+        <v>0.48500000000000004</v>
+      </c>
+      <c r="I21" s="24">
+        <f>(F21+G21+H21)*0.07</f>
+        <v>7.0548100000000007</v>
+      </c>
+      <c r="J21" s="24">
+        <f>E21-F21-G21-H21-I21</f>
+        <v>48392.162189999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="E22" s="17">
+        <f>E21-E20</f>
+        <v>4500</v>
+      </c>
+      <c r="F22" s="17">
+        <f t="shared" ref="F22:J22" si="2">F21-F20</f>
+        <v>9</v>
+      </c>
+      <c r="G22" s="17">
+        <f t="shared" si="2"/>
+        <v>0.30600000000000005</v>
+      </c>
+      <c r="H22" s="17">
+        <f t="shared" si="2"/>
+        <v>4.4999999999999984E-2</v>
+      </c>
+      <c r="I22" s="17">
+        <f t="shared" si="2"/>
+        <v>0.65456999999999965</v>
+      </c>
+      <c r="J22" s="17">
+        <f t="shared" si="2"/>
+        <v>4294.3299499999921</v>
       </c>
     </row>
   </sheetData>
@@ -23794,7 +24120,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="18" customFormat="1" ht="15.6">
@@ -24972,661 +25298,6 @@
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
-  <sheetPr>
-    <tabColor rgb="FFFF0000"/>
-  </sheetPr>
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="10.6640625" style="35" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" style="21" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="20" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="20" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.77734375" style="20" customWidth="1"/>
-    <col min="9" max="9" width="6.77734375" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="20" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18" style="20" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="20"/>
-    <col min="13" max="13" width="8.88671875" style="23"/>
-    <col min="14" max="16384" width="8.88671875" style="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="B1" s="20" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="12" customFormat="1">
-      <c r="A2" s="36">
-        <v>44566</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>10000</v>
-      </c>
-      <c r="D2" s="16">
-        <v>12.5</v>
-      </c>
-      <c r="E2" s="17">
-        <f>C2*D2</f>
-        <v>125000</v>
-      </c>
-      <c r="F2" s="17">
-        <f>E2*0.002</f>
-        <v>250</v>
-      </c>
-      <c r="G2" s="17">
-        <f>E2*0.00006</f>
-        <v>7.5</v>
-      </c>
-      <c r="H2" s="17">
-        <f>E2*0.00001</f>
-        <v>1.25</v>
-      </c>
-      <c r="I2" s="17">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>18.112500000000001</v>
-      </c>
-      <c r="J2" s="17">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>125276.8625</v>
-      </c>
-      <c r="K2" s="27"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="28"/>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="13">
-        <v>44627</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15">
-        <v>10000</v>
-      </c>
-      <c r="D3" s="38">
-        <v>12.1</v>
-      </c>
-      <c r="E3" s="17">
-        <f>C3*D3</f>
-        <v>121000</v>
-      </c>
-      <c r="F3" s="17">
-        <f>E3*0.002</f>
-        <v>242</v>
-      </c>
-      <c r="G3" s="17">
-        <f>E3*0.000068</f>
-        <v>8.2279999999999998</v>
-      </c>
-      <c r="H3" s="17">
-        <f>E3*0.00001</f>
-        <v>1.2100000000000002</v>
-      </c>
-      <c r="I3" s="17">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>17.600660000000001</v>
-      </c>
-      <c r="J3" s="17">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>121269.03866000001</v>
-      </c>
-      <c r="M3" s="20"/>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="39"/>
-      <c r="B4" s="70">
-        <f>(D3-D2)/D2</f>
-        <v>-3.2000000000000028E-2</v>
-      </c>
-      <c r="C4" s="5">
-        <f>SUM(C2:C3)</f>
-        <v>20000</v>
-      </c>
-      <c r="D4" s="34">
-        <f>E4/C4</f>
-        <v>12.3</v>
-      </c>
-      <c r="E4" s="45">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>246000</v>
-      </c>
-      <c r="F4" s="5">
-        <f t="shared" si="0"/>
-        <v>492</v>
-      </c>
-      <c r="G4" s="5">
-        <f t="shared" si="0"/>
-        <v>15.728</v>
-      </c>
-      <c r="H4" s="5">
-        <f t="shared" si="0"/>
-        <v>2.46</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>35.713160000000002</v>
-      </c>
-      <c r="J4" s="5">
-        <f t="shared" si="0"/>
-        <v>246545.90116000001</v>
-      </c>
-      <c r="K4" s="23"/>
-      <c r="M4" s="20"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="7">
-        <v>45846</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="9">
-        <v>5000</v>
-      </c>
-      <c r="D5" s="43">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="E5" s="19">
-        <f>C5*D5</f>
-        <v>49000</v>
-      </c>
-      <c r="F5" s="19">
-        <f>E5*0.002</f>
-        <v>98</v>
-      </c>
-      <c r="G5" s="19">
-        <f>E5*0.000068</f>
-        <v>3.3319999999999999</v>
-      </c>
-      <c r="H5" s="19">
-        <f>E5*0.00001</f>
-        <v>0.49000000000000005</v>
-      </c>
-      <c r="I5" s="19">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>7.1275399999999998</v>
-      </c>
-      <c r="J5" s="19">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>49108.949540000001</v>
-      </c>
-      <c r="M5" s="20"/>
-    </row>
-    <row r="6" spans="1:14" s="59" customFormat="1" ht="21">
-      <c r="A6" s="41"/>
-      <c r="B6" s="70" t="e">
-        <f>(D5-#REF!)/#REF!</f>
-        <v>#REF!</v>
-      </c>
-      <c r="C6" s="21">
-        <f>SUM(C4:C5)</f>
-        <v>25000</v>
-      </c>
-      <c r="D6" s="31">
-        <f>E6/C6</f>
-        <v>11.8</v>
-      </c>
-      <c r="E6" s="21">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>295000</v>
-      </c>
-      <c r="F6" s="21">
-        <f t="shared" si="1"/>
-        <v>590</v>
-      </c>
-      <c r="G6" s="21">
-        <f t="shared" si="1"/>
-        <v>19.059999999999999</v>
-      </c>
-      <c r="H6" s="21">
-        <f t="shared" si="1"/>
-        <v>2.95</v>
-      </c>
-      <c r="I6" s="21">
-        <f t="shared" si="1"/>
-        <v>42.840699999999998</v>
-      </c>
-      <c r="J6" s="21">
-        <f t="shared" si="1"/>
-        <v>295654.85070000001</v>
-      </c>
-      <c r="K6" s="23"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="13"/>
-      <c r="B7" s="14"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="M7" s="20"/>
-    </row>
-    <row r="8" spans="1:14" s="87" customFormat="1" ht="20.399999999999999">
-      <c r="A8" s="46">
-        <v>45524</v>
-      </c>
-      <c r="B8" s="90"/>
-      <c r="C8" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D8" s="37">
-        <v>0.193</v>
-      </c>
-      <c r="E8" s="91"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="91"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="92">
-        <v>965</v>
-      </c>
-      <c r="J8" s="92">
-        <v>868.5</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-    </row>
-    <row r="9" spans="1:14" s="87" customFormat="1">
-      <c r="A9" s="46">
-        <v>44956</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D9" s="38">
-        <v>8.6</v>
-      </c>
-      <c r="E9" s="17">
-        <v>43000</v>
-      </c>
-      <c r="F9" s="17">
-        <v>86</v>
-      </c>
-      <c r="G9" s="17">
-        <v>2.58</v>
-      </c>
-      <c r="H9" s="17">
-        <v>0.43000000000000005</v>
-      </c>
-      <c r="I9" s="17">
-        <v>6.2307000000000006</v>
-      </c>
-      <c r="J9" s="17">
-        <v>43095.240700000002</v>
-      </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1">
-      <c r="A10" s="46">
-        <v>45525</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D10" s="24">
-        <v>10.1</v>
-      </c>
-      <c r="E10" s="16">
-        <v>50500</v>
-      </c>
-      <c r="F10" s="25">
-        <v>101</v>
-      </c>
-      <c r="G10" s="24">
-        <v>3.4340000000000002</v>
-      </c>
-      <c r="H10" s="24">
-        <v>0.505</v>
-      </c>
-      <c r="I10" s="24">
-        <v>7.3457300000000005</v>
-      </c>
-      <c r="J10" s="24">
-        <v>50387.715270000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1">
-      <c r="A11" s="46"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17">
-        <v>7500</v>
-      </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17">
-        <v>7292.4745699999985</v>
-      </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="51"/>
-      <c r="B13" s="87"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="87"/>
-      <c r="F13" s="87"/>
-      <c r="G13" s="87"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="87"/>
-      <c r="J13" s="93">
-        <v>8160.9745699999985</v>
-      </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-    </row>
-    <row r="14" spans="1:14" ht="20.399999999999999">
-      <c r="A14" s="46">
-        <v>45524</v>
-      </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D14" s="37">
-        <v>0.193</v>
-      </c>
-      <c r="E14" s="91"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="92">
-        <v>965</v>
-      </c>
-      <c r="J14" s="92">
-        <v>868.5</v>
-      </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="12"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="13">
-        <v>45436</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="89">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E15" s="17">
-        <v>44000</v>
-      </c>
-      <c r="F15" s="17">
-        <v>88</v>
-      </c>
-      <c r="G15" s="17">
-        <v>2.992</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="I15" s="17">
-        <v>6.400240000000001</v>
-      </c>
-      <c r="J15" s="17">
-        <v>44097.832240000003</v>
-      </c>
-      <c r="M15" s="20"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="46">
-        <v>45530</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D16" s="24">
-        <v>10.3</v>
-      </c>
-      <c r="E16" s="16">
-        <v>51500</v>
-      </c>
-      <c r="F16" s="25">
-        <v>103</v>
-      </c>
-      <c r="G16" s="24">
-        <v>3.5019999999999998</v>
-      </c>
-      <c r="H16" s="24">
-        <v>0.51500000000000001</v>
-      </c>
-      <c r="I16" s="24">
-        <v>7.4911900000000005</v>
-      </c>
-      <c r="J16" s="24">
-        <v>51385.49181</v>
-      </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="46"/>
-      <c r="B17" s="28">
-        <v>0.17045454545454544</v>
-      </c>
-      <c r="C17" s="15"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="25"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-      <c r="I17" s="24"/>
-      <c r="J17" s="24"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="46" t="s">
-        <v>3</v>
-      </c>
-      <c r="B18" s="14"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="17">
-        <v>7500</v>
-      </c>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17">
-        <v>7287.6595699999962</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="51"/>
-      <c r="B19" s="87"/>
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="87"/>
-      <c r="G19" s="87"/>
-      <c r="H19" s="87"/>
-      <c r="I19" s="87"/>
-      <c r="J19" s="93">
-        <v>8156.1595699999962</v>
-      </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="13">
-        <v>45846</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D20" s="38">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E20" s="17">
-        <f>C20*D20</f>
-        <v>44000</v>
-      </c>
-      <c r="F20" s="17">
-        <f>E20*0.002</f>
-        <v>88</v>
-      </c>
-      <c r="G20" s="17">
-        <f>E20*0.000068</f>
-        <v>2.992</v>
-      </c>
-      <c r="H20" s="17">
-        <f>E20*0.00001</f>
-        <v>0.44000000000000006</v>
-      </c>
-      <c r="I20" s="17">
-        <f>(F20+G20+H20)*0.07</f>
-        <v>6.400240000000001</v>
-      </c>
-      <c r="J20" s="17">
-        <f>E20+F20+I20+G20+H20</f>
-        <v>44097.832240000003</v>
-      </c>
-      <c r="M20" s="20"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1">
-      <c r="A21" s="46">
-        <v>45915</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C21" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D21" s="24">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="E21" s="16">
-        <f>C21*D21</f>
-        <v>48500</v>
-      </c>
-      <c r="F21" s="25">
-        <f>E21*0.002</f>
-        <v>97</v>
-      </c>
-      <c r="G21" s="24">
-        <f>E21*0.000068</f>
-        <v>3.298</v>
-      </c>
-      <c r="H21" s="24">
-        <f>E21*0.00001</f>
-        <v>0.48500000000000004</v>
-      </c>
-      <c r="I21" s="24">
-        <f>(F21+G21+H21)*0.07</f>
-        <v>7.0548100000000007</v>
-      </c>
-      <c r="J21" s="24">
-        <f>E21-F21-G21-H21-I21</f>
-        <v>48392.162189999995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="E22" s="17">
-        <f>E21-E20</f>
-        <v>4500</v>
-      </c>
-      <c r="F22" s="17">
-        <f t="shared" ref="F22:J22" si="2">F21-F20</f>
-        <v>9</v>
-      </c>
-      <c r="G22" s="17">
-        <f t="shared" si="2"/>
-        <v>0.30600000000000005</v>
-      </c>
-      <c r="H22" s="17">
-        <f t="shared" si="2"/>
-        <v>4.4999999999999984E-2</v>
-      </c>
-      <c r="I22" s="17">
-        <f t="shared" si="2"/>
-        <v>0.65456999999999965</v>
-      </c>
-      <c r="J22" s="17">
-        <f t="shared" si="2"/>
-        <v>4294.3299499999921</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
@@ -27369,7 +27040,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -27807,7 +27478,7 @@
         <v>45871</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C15" s="2">
         <v>5000</v>
@@ -27930,7 +27601,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -28033,7 +27704,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="B24" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:10">

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1691" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5F276051-CB6D-4BE3-BEAC-7A952E77A7F8}"/>
+  <xr:revisionPtr revIDLastSave="1698" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A7CCE2F-D6BD-4EC0-8071-1ECFEC2127D8}"/>
   <bookViews>
-    <workbookView xWindow="408" yWindow="1476" windowWidth="14820" windowHeight="10764" tabRatio="461" firstSheet="19" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9060" yWindow="1308" windowWidth="10992" windowHeight="10764" tabRatio="461" firstSheet="23" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
@@ -21709,38 +21709,38 @@
         <v>5000</v>
       </c>
       <c r="D7" s="43">
-        <v>6.1</v>
+        <v>6.4</v>
       </c>
       <c r="E7" s="19">
         <f>C7*D7</f>
-        <v>30500</v>
+        <v>32000</v>
       </c>
       <c r="F7" s="19">
         <f>E7*0.002</f>
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G7" s="19">
         <f>E7*0.000068</f>
-        <v>2.0739999999999998</v>
+        <v>2.1760000000000002</v>
       </c>
       <c r="H7" s="19">
         <f>E7*0.00001</f>
-        <v>0.30500000000000005</v>
+        <v>0.32</v>
       </c>
       <c r="I7" s="19">
         <f>(F7+G7+H7)*0.07</f>
-        <v>4.4365300000000003</v>
+        <v>4.6547200000000002</v>
       </c>
       <c r="J7" s="19">
         <f>E7+F7+I7+G7+H7</f>
-        <v>30567.81553</v>
+        <v>32071.150719999998</v>
       </c>
     </row>
     <row r="8" spans="1:11" s="20" customFormat="1">
       <c r="A8" s="41"/>
       <c r="B8" s="23">
         <f>(D7-D6)/D6</f>
-        <v>-0.16438356164383564</v>
+        <v>-0.12328767123287664</v>
       </c>
       <c r="C8" s="21">
         <f>SUM(C6:C7)</f>
@@ -21748,31 +21748,31 @@
       </c>
       <c r="D8" s="31">
         <f>E8/C8</f>
-        <v>7.1</v>
+        <v>7.15</v>
       </c>
       <c r="E8" s="21">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>213000</v>
+        <v>214500</v>
       </c>
       <c r="F8" s="21">
         <f t="shared" si="2"/>
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="G8" s="21">
         <f t="shared" si="2"/>
-        <v>13.88</v>
+        <v>13.982000000000001</v>
       </c>
       <c r="H8" s="21">
         <f t="shared" si="2"/>
-        <v>2.1300000000000003</v>
+        <v>2.145</v>
       </c>
       <c r="I8" s="21">
         <f t="shared" si="2"/>
-        <v>30.940700000000007</v>
+        <v>31.158890000000007</v>
       </c>
       <c r="J8" s="21">
         <f t="shared" si="2"/>
-        <v>213472.95069999999</v>
+        <v>214976.28589</v>
       </c>
       <c r="K8" s="23"/>
     </row>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1698" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A7CCE2F-D6BD-4EC0-8071-1ECFEC2127D8}"/>
+  <xr:revisionPtr revIDLastSave="1704" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39367170-049F-4756-A63D-B45ABD1B2CE7}"/>
   <bookViews>
-    <workbookView xWindow="9060" yWindow="1308" windowWidth="10992" windowHeight="10764" tabRatio="461" firstSheet="23" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6300" yWindow="3396" windowWidth="16332" windowHeight="8268" tabRatio="461" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
@@ -193,15 +193,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="\฿#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="171" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="187" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="190" formatCode="\฿#,##0.000"/>
+    <numFmt numFmtId="191" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="192" formatCode="0.0000"/>
+    <numFmt numFmtId="193" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="194" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="195" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -360,64 +360,64 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -425,30 +425,30 @@
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -464,10 +464,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6901,8 +6897,8 @@
     <row r="8" spans="1:14" s="59" customFormat="1" ht="21">
       <c r="A8" s="52"/>
       <c r="B8" s="72">
-        <f>(D7-D15)/D15</f>
-        <v>-0.12663755458515277</v>
+        <f>(D7-D6)/D6</f>
+        <v>-0.5</v>
       </c>
       <c r="C8" s="9">
         <f>SUM(C6:C7)</f>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,39 +8,40 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1704" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39367170-049F-4756-A63D-B45ABD1B2CE7}"/>
+  <xr:revisionPtr revIDLastSave="1745" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FB50B5C-2277-4E6F-BB28-263CB052D67B}"/>
   <bookViews>
-    <workbookView xWindow="6300" yWindow="3396" windowWidth="16332" windowHeight="8268" tabRatio="461" firstSheet="11" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4164" yWindow="864" windowWidth="18420" windowHeight="11364" tabRatio="461" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
     <sheet name="STA" sheetId="197" r:id="rId2"/>
     <sheet name="3BBIF" sheetId="46" r:id="rId3"/>
-    <sheet name="AH" sheetId="217" r:id="rId4"/>
-    <sheet name="AIMIRT" sheetId="210" r:id="rId5"/>
-    <sheet name="AWC" sheetId="212" r:id="rId6"/>
-    <sheet name="BCH" sheetId="150" r:id="rId7"/>
-    <sheet name="CPF" sheetId="223" r:id="rId8"/>
-    <sheet name="CPNREIT" sheetId="194" r:id="rId9"/>
-    <sheet name="DIF" sheetId="57" r:id="rId10"/>
-    <sheet name="GVREIT" sheetId="195" r:id="rId11"/>
-    <sheet name="IVL" sheetId="196" r:id="rId12"/>
-    <sheet name="JMART" sheetId="204" r:id="rId13"/>
-    <sheet name="JMT" sheetId="205" r:id="rId14"/>
-    <sheet name="MCS" sheetId="20" r:id="rId15"/>
-    <sheet name="NER" sheetId="117" r:id="rId16"/>
-    <sheet name="ORI" sheetId="184" r:id="rId17"/>
-    <sheet name="PTG" sheetId="216" r:id="rId18"/>
-    <sheet name="PTT" sheetId="224" r:id="rId19"/>
-    <sheet name="RCL" sheetId="161" r:id="rId20"/>
-    <sheet name="SENA" sheetId="183" r:id="rId21"/>
-    <sheet name="SINGER" sheetId="203" r:id="rId22"/>
-    <sheet name="SYNEX" sheetId="199" r:id="rId23"/>
-    <sheet name="TFFIF" sheetId="214" r:id="rId24"/>
-    <sheet name="TOA" sheetId="218" r:id="rId25"/>
-    <sheet name="TVO" sheetId="221" r:id="rId26"/>
-    <sheet name="WHAIR" sheetId="157" r:id="rId27"/>
-    <sheet name="WHART" sheetId="171" r:id="rId28"/>
+    <sheet name="ADVANC" sheetId="225" r:id="rId4"/>
+    <sheet name="AH" sheetId="217" r:id="rId5"/>
+    <sheet name="AIMIRT" sheetId="210" r:id="rId6"/>
+    <sheet name="AWC" sheetId="212" r:id="rId7"/>
+    <sheet name="BCH" sheetId="150" r:id="rId8"/>
+    <sheet name="CPF" sheetId="223" r:id="rId9"/>
+    <sheet name="CPNREIT" sheetId="194" r:id="rId10"/>
+    <sheet name="DIF" sheetId="57" r:id="rId11"/>
+    <sheet name="GVREIT" sheetId="195" r:id="rId12"/>
+    <sheet name="IVL" sheetId="196" r:id="rId13"/>
+    <sheet name="JMART" sheetId="204" r:id="rId14"/>
+    <sheet name="JMT" sheetId="205" r:id="rId15"/>
+    <sheet name="MCS" sheetId="20" r:id="rId16"/>
+    <sheet name="NER" sheetId="117" r:id="rId17"/>
+    <sheet name="ORI" sheetId="184" r:id="rId18"/>
+    <sheet name="PTG" sheetId="216" r:id="rId19"/>
+    <sheet name="PTT" sheetId="224" r:id="rId20"/>
+    <sheet name="RCL" sheetId="161" r:id="rId21"/>
+    <sheet name="SENA" sheetId="183" r:id="rId22"/>
+    <sheet name="SINGER" sheetId="203" r:id="rId23"/>
+    <sheet name="SYNEX" sheetId="199" r:id="rId24"/>
+    <sheet name="TFFIF" sheetId="214" r:id="rId25"/>
+    <sheet name="TOA" sheetId="218" r:id="rId26"/>
+    <sheet name="TVO" sheetId="221" r:id="rId27"/>
+    <sheet name="WHAIR" sheetId="157" r:id="rId28"/>
+    <sheet name="WHART" sheetId="171" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="42">
   <si>
     <t>BUY</t>
   </si>
@@ -186,6 +187,9 @@
   </si>
   <si>
     <t>PTT</t>
+  </si>
+  <si>
+    <t>ADVANC</t>
   </si>
 </sst>
 </file>
@@ -2860,6 +2864,879 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB529E6-7221-4171-9EDF-80891E84F736}">
+  <dimension ref="A1:N26"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" style="47" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="44" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.6640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="B1" s="47" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="18" customFormat="1" ht="15.6">
+      <c r="A2" s="46">
+        <v>44789</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D2" s="38">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E2" s="17">
+        <f>C2*D2</f>
+        <v>97000</v>
+      </c>
+      <c r="F2" s="17">
+        <f>E2*0.002</f>
+        <v>194</v>
+      </c>
+      <c r="G2" s="17">
+        <f>E2*0.00006</f>
+        <v>5.82</v>
+      </c>
+      <c r="H2" s="17">
+        <f>E2*0.00001</f>
+        <v>0.97000000000000008</v>
+      </c>
+      <c r="I2" s="17">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>14.055300000000001</v>
+      </c>
+      <c r="J2" s="17">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>97214.845300000015</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="73" customFormat="1">
+      <c r="A3" s="77">
+        <v>44818</v>
+      </c>
+      <c r="B3" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="79">
+        <v>5000</v>
+      </c>
+      <c r="D3" s="80">
+        <v>19</v>
+      </c>
+      <c r="E3" s="81">
+        <f>C3*D3</f>
+        <v>95000</v>
+      </c>
+      <c r="F3" s="81">
+        <f>E3*0.002</f>
+        <v>190</v>
+      </c>
+      <c r="G3" s="81">
+        <f>E3*0.000068</f>
+        <v>6.46</v>
+      </c>
+      <c r="H3" s="81">
+        <f>E3*0.00001</f>
+        <v>0.95000000000000007</v>
+      </c>
+      <c r="I3" s="81">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>13.818700000000002</v>
+      </c>
+      <c r="J3" s="81">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>95211.228700000007</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="73" customFormat="1">
+      <c r="A4" s="77"/>
+      <c r="B4" s="82">
+        <f>(D3-D2)/D2</f>
+        <v>-2.0618556701030855E-2</v>
+      </c>
+      <c r="C4" s="79">
+        <f>SUM(C2:C3)</f>
+        <v>10000</v>
+      </c>
+      <c r="D4" s="80">
+        <f>E4/C4</f>
+        <v>19.2</v>
+      </c>
+      <c r="E4" s="79">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>192000</v>
+      </c>
+      <c r="F4" s="79">
+        <f t="shared" si="0"/>
+        <v>384</v>
+      </c>
+      <c r="G4" s="79">
+        <f t="shared" si="0"/>
+        <v>12.280000000000001</v>
+      </c>
+      <c r="H4" s="79">
+        <f t="shared" si="0"/>
+        <v>1.9200000000000002</v>
+      </c>
+      <c r="I4" s="79">
+        <f t="shared" si="0"/>
+        <v>27.874000000000002</v>
+      </c>
+      <c r="J4" s="79">
+        <f t="shared" si="0"/>
+        <v>192426.07400000002</v>
+      </c>
+      <c r="K4" s="76"/>
+    </row>
+    <row r="5" spans="1:14" s="73" customFormat="1">
+      <c r="A5" s="77">
+        <v>44880</v>
+      </c>
+      <c r="B5" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D5" s="80">
+        <v>18.600000000000001</v>
+      </c>
+      <c r="E5" s="81">
+        <f>C5*D5</f>
+        <v>186000</v>
+      </c>
+      <c r="F5" s="81">
+        <f>E5*0.002</f>
+        <v>372</v>
+      </c>
+      <c r="G5" s="81">
+        <f>E5*0.000068</f>
+        <v>12.648</v>
+      </c>
+      <c r="H5" s="81">
+        <f>E5*0.00001</f>
+        <v>1.86</v>
+      </c>
+      <c r="I5" s="81">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>27.055560000000007</v>
+      </c>
+      <c r="J5" s="81">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>186413.56355999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="73" customFormat="1">
+      <c r="A6" s="77"/>
+      <c r="B6" s="82">
+        <f>(D5-D4)/D4</f>
+        <v>-3.1249999999999889E-2</v>
+      </c>
+      <c r="C6" s="79">
+        <f>SUM(C4:C5)</f>
+        <v>20000</v>
+      </c>
+      <c r="D6" s="80">
+        <f>E6/C6</f>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="E6" s="79">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>378000</v>
+      </c>
+      <c r="F6" s="79">
+        <f t="shared" si="1"/>
+        <v>756</v>
+      </c>
+      <c r="G6" s="79">
+        <f t="shared" si="1"/>
+        <v>24.928000000000001</v>
+      </c>
+      <c r="H6" s="79">
+        <f t="shared" si="1"/>
+        <v>3.7800000000000002</v>
+      </c>
+      <c r="I6" s="79">
+        <f t="shared" si="1"/>
+        <v>54.929560000000009</v>
+      </c>
+      <c r="J6" s="79">
+        <f t="shared" si="1"/>
+        <v>378839.63756</v>
+      </c>
+      <c r="K6" s="76"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="77">
+        <v>44950</v>
+      </c>
+      <c r="B7" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D7" s="80">
+        <v>19.5</v>
+      </c>
+      <c r="E7" s="81">
+        <f>C7*D7</f>
+        <v>195000</v>
+      </c>
+      <c r="F7" s="81">
+        <f>E7*0.002</f>
+        <v>390</v>
+      </c>
+      <c r="G7" s="81">
+        <f>E7*0.000068</f>
+        <v>13.26</v>
+      </c>
+      <c r="H7" s="81">
+        <f>E7*0.00001</f>
+        <v>1.9500000000000002</v>
+      </c>
+      <c r="I7" s="81">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>28.364700000000003</v>
+      </c>
+      <c r="J7" s="81">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>195433.57470000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A8" s="77"/>
+      <c r="B8" s="82">
+        <f>(D7-D6)/D6</f>
+        <v>3.1746031746031821E-2</v>
+      </c>
+      <c r="C8" s="79">
+        <f>SUM(C6:C7)</f>
+        <v>30000</v>
+      </c>
+      <c r="D8" s="80">
+        <f>E8/C8</f>
+        <v>19.100000000000001</v>
+      </c>
+      <c r="E8" s="79">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>573000</v>
+      </c>
+      <c r="F8" s="79">
+        <f t="shared" si="2"/>
+        <v>1146</v>
+      </c>
+      <c r="G8" s="79">
+        <f t="shared" si="2"/>
+        <v>38.188000000000002</v>
+      </c>
+      <c r="H8" s="79">
+        <f t="shared" si="2"/>
+        <v>5.73</v>
+      </c>
+      <c r="I8" s="79">
+        <f t="shared" si="2"/>
+        <v>83.294260000000008</v>
+      </c>
+      <c r="J8" s="79">
+        <f t="shared" si="2"/>
+        <v>574273.21226000006</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="77">
+        <v>44964</v>
+      </c>
+      <c r="B9" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D9" s="80">
+        <v>18.3</v>
+      </c>
+      <c r="E9" s="81">
+        <f>C9*D9</f>
+        <v>183000</v>
+      </c>
+      <c r="F9" s="81">
+        <f>E9*0.002</f>
+        <v>366</v>
+      </c>
+      <c r="G9" s="81">
+        <f>E9*0.000068</f>
+        <v>12.443999999999999</v>
+      </c>
+      <c r="H9" s="81">
+        <f>E9*0.00001</f>
+        <v>1.83</v>
+      </c>
+      <c r="I9" s="81">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>26.619180000000004</v>
+      </c>
+      <c r="J9" s="81">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>183406.89317999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="77"/>
+      <c r="B10" s="82">
+        <f>(D9-D8)/D8</f>
+        <v>-4.1884816753926739E-2</v>
+      </c>
+      <c r="C10" s="79">
+        <f>SUM(C8:C9)</f>
+        <v>40000</v>
+      </c>
+      <c r="D10" s="80">
+        <f>E10/C10</f>
+        <v>18.899999999999999</v>
+      </c>
+      <c r="E10" s="79">
+        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
+        <v>756000</v>
+      </c>
+      <c r="F10" s="79">
+        <f t="shared" si="3"/>
+        <v>1512</v>
+      </c>
+      <c r="G10" s="79">
+        <f t="shared" si="3"/>
+        <v>50.632000000000005</v>
+      </c>
+      <c r="H10" s="79">
+        <f t="shared" si="3"/>
+        <v>7.5600000000000005</v>
+      </c>
+      <c r="I10" s="79">
+        <f t="shared" si="3"/>
+        <v>109.91344000000001</v>
+      </c>
+      <c r="J10" s="79">
+        <f t="shared" si="3"/>
+        <v>757680.10544000007</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="77">
+        <v>44986</v>
+      </c>
+      <c r="B11" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="79">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="80">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="E11" s="81">
+        <f>C11*D11</f>
+        <v>164000</v>
+      </c>
+      <c r="F11" s="81">
+        <f>E11*0.002</f>
+        <v>328</v>
+      </c>
+      <c r="G11" s="81">
+        <f>E11*0.000068</f>
+        <v>11.151999999999999</v>
+      </c>
+      <c r="H11" s="81">
+        <f>E11*0.00001</f>
+        <v>1.6400000000000001</v>
+      </c>
+      <c r="I11" s="81">
+        <f>(F11+G11+H11)*0.07</f>
+        <v>23.855440000000002</v>
+      </c>
+      <c r="J11" s="81">
+        <f>E11+F11+I11+G11+H11</f>
+        <v>164364.64744000003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="A12" s="77"/>
+      <c r="B12" s="82">
+        <f>(D11-D10)/D10</f>
+        <v>-0.1322751322751323</v>
+      </c>
+      <c r="C12" s="79">
+        <f>SUM(C10:C11)</f>
+        <v>50000</v>
+      </c>
+      <c r="D12" s="80">
+        <f>E12/C12</f>
+        <v>18.399999999999999</v>
+      </c>
+      <c r="E12" s="79">
+        <f t="shared" ref="E12:J12" si="4">SUM(E10:E11)</f>
+        <v>920000</v>
+      </c>
+      <c r="F12" s="79">
+        <f t="shared" si="4"/>
+        <v>1840</v>
+      </c>
+      <c r="G12" s="79">
+        <f t="shared" si="4"/>
+        <v>61.784000000000006</v>
+      </c>
+      <c r="H12" s="79">
+        <f t="shared" si="4"/>
+        <v>9.2000000000000011</v>
+      </c>
+      <c r="I12" s="79">
+        <f t="shared" si="4"/>
+        <v>133.76888000000002</v>
+      </c>
+      <c r="J12" s="79">
+        <f t="shared" si="4"/>
+        <v>922044.75288000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="A13" s="77">
+        <v>44994</v>
+      </c>
+      <c r="B13" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" s="79">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="80">
+        <v>14</v>
+      </c>
+      <c r="E13" s="81">
+        <f>C13*D13</f>
+        <v>70000</v>
+      </c>
+      <c r="F13" s="81">
+        <f>E13*0.002</f>
+        <v>140</v>
+      </c>
+      <c r="G13" s="81">
+        <f>E13*0.000068</f>
+        <v>4.76</v>
+      </c>
+      <c r="H13" s="81">
+        <f>E13*0.00001</f>
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="I13" s="81">
+        <f>(F13+G13+H13)*0.07</f>
+        <v>10.1822</v>
+      </c>
+      <c r="J13" s="81">
+        <f>E13+F13+I13+G13+H13</f>
+        <v>70155.642199999987</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="77"/>
+      <c r="B14" s="82">
+        <f>(D13-D12)/D12</f>
+        <v>-0.23913043478260865</v>
+      </c>
+      <c r="C14" s="79">
+        <f>SUM(C12:C13)</f>
+        <v>55000</v>
+      </c>
+      <c r="D14" s="80">
+        <f>E14/C14</f>
+        <v>18</v>
+      </c>
+      <c r="E14" s="79">
+        <f t="shared" ref="E14:J14" si="5">SUM(E12:E13)</f>
+        <v>990000</v>
+      </c>
+      <c r="F14" s="79">
+        <f t="shared" si="5"/>
+        <v>1980</v>
+      </c>
+      <c r="G14" s="79">
+        <f t="shared" si="5"/>
+        <v>66.544000000000011</v>
+      </c>
+      <c r="H14" s="79">
+        <f t="shared" si="5"/>
+        <v>9.9</v>
+      </c>
+      <c r="I14" s="79">
+        <f t="shared" si="5"/>
+        <v>143.95108000000002</v>
+      </c>
+      <c r="J14" s="79">
+        <f t="shared" si="5"/>
+        <v>992200.39508000005</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" s="20" customFormat="1">
+      <c r="A15" s="7">
+        <v>44260</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="75">
+        <v>10.8</v>
+      </c>
+      <c r="E15" s="86">
+        <f>C15*D15</f>
+        <v>54000</v>
+      </c>
+      <c r="F15" s="86">
+        <f>E15*0.002</f>
+        <v>108</v>
+      </c>
+      <c r="G15" s="86">
+        <f>E15*0.000068</f>
+        <v>3.6720000000000002</v>
+      </c>
+      <c r="H15" s="86">
+        <f>E15*0.00001</f>
+        <v>0.54</v>
+      </c>
+      <c r="I15" s="86">
+        <f>(F15+G15+H15)*0.07</f>
+        <v>7.8548400000000012</v>
+      </c>
+      <c r="J15" s="86">
+        <f>E15+F15+I15+G15+H15</f>
+        <v>54120.06684</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="20" customFormat="1">
+      <c r="A16" s="41"/>
+      <c r="B16" s="76">
+        <f>(D15-D14)/D14</f>
+        <v>-0.39999999999999997</v>
+      </c>
+      <c r="C16" s="21">
+        <f>SUM(C14:C15)</f>
+        <v>60000</v>
+      </c>
+      <c r="D16" s="31">
+        <f>E16/C16</f>
+        <v>17.399999999999999</v>
+      </c>
+      <c r="E16" s="21">
+        <f t="shared" ref="E16:J16" si="6">SUM(E14:E15)</f>
+        <v>1044000</v>
+      </c>
+      <c r="F16" s="21">
+        <f t="shared" si="6"/>
+        <v>2088</v>
+      </c>
+      <c r="G16" s="21">
+        <f t="shared" si="6"/>
+        <v>70.216000000000008</v>
+      </c>
+      <c r="H16" s="21">
+        <f t="shared" si="6"/>
+        <v>10.440000000000001</v>
+      </c>
+      <c r="I16" s="21">
+        <f t="shared" si="6"/>
+        <v>151.80592000000001</v>
+      </c>
+      <c r="J16" s="21">
+        <f t="shared" si="6"/>
+        <v>1046320.46192</v>
+      </c>
+      <c r="K16" s="23"/>
+    </row>
+    <row r="17" spans="1:14" s="20" customFormat="1">
+      <c r="A17" s="41"/>
+      <c r="B17" s="76"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="23"/>
+    </row>
+    <row r="18" spans="1:14" s="20" customFormat="1">
+      <c r="A18" s="77">
+        <v>45097</v>
+      </c>
+      <c r="B18" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" s="79">
+        <v>3000</v>
+      </c>
+      <c r="D18" s="80">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="E18" s="81">
+        <f>C18*D18</f>
+        <v>30599.999999999996</v>
+      </c>
+      <c r="F18" s="81">
+        <f>E18*0.002</f>
+        <v>61.199999999999996</v>
+      </c>
+      <c r="G18" s="81">
+        <f>E18*0.000068</f>
+        <v>2.0807999999999995</v>
+      </c>
+      <c r="H18" s="81">
+        <f>E18*0.00001</f>
+        <v>0.30599999999999999</v>
+      </c>
+      <c r="I18" s="81">
+        <f>(F18+G18+H18)*0.07</f>
+        <v>4.4510759999999996</v>
+      </c>
+      <c r="J18" s="81">
+        <f>E18+F18+I18+G18+H18</f>
+        <v>30668.037875999999</v>
+      </c>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+    </row>
+    <row r="19" spans="1:14" s="20" customFormat="1">
+      <c r="A19" s="13">
+        <v>45100</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="15">
+        <f>C18</f>
+        <v>3000</v>
+      </c>
+      <c r="D19" s="24">
+        <v>10.7</v>
+      </c>
+      <c r="E19" s="16">
+        <f>C19*D19</f>
+        <v>32099.999999999996</v>
+      </c>
+      <c r="F19" s="25">
+        <f>E19*0.002</f>
+        <v>64.199999999999989</v>
+      </c>
+      <c r="G19" s="24">
+        <f>E19*0.000068</f>
+        <v>2.1827999999999999</v>
+      </c>
+      <c r="H19" s="24">
+        <f>E19*0.00001</f>
+        <v>0.32100000000000001</v>
+      </c>
+      <c r="I19" s="24">
+        <f>(F19+G19+H19)*0.07</f>
+        <v>4.6692659999999995</v>
+      </c>
+      <c r="J19" s="24">
+        <f>E19-F19-G19-H19-I19</f>
+        <v>32028.626933999996</v>
+      </c>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+    </row>
+    <row r="20" spans="1:14" s="20" customFormat="1" ht="18.600000000000001">
+      <c r="A20" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B20" s="14"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="17">
+        <f>E19-E18</f>
+        <v>1500</v>
+      </c>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
+      <c r="I20" s="17"/>
+      <c r="J20" s="17">
+        <f>J19-J18</f>
+        <v>1360.5890579999977</v>
+      </c>
+      <c r="K20" s="11"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="77">
+        <v>44998</v>
+      </c>
+      <c r="B21" s="78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="79">
+        <v>5000</v>
+      </c>
+      <c r="D21" s="80">
+        <v>12.6</v>
+      </c>
+      <c r="E21" s="81">
+        <f>C21*D21</f>
+        <v>63000</v>
+      </c>
+      <c r="F21" s="81">
+        <f>E21*0.002</f>
+        <v>126</v>
+      </c>
+      <c r="G21" s="81">
+        <f>E21*0.000068</f>
+        <v>4.2839999999999998</v>
+      </c>
+      <c r="H21" s="81">
+        <f>E21*0.00001</f>
+        <v>0.63</v>
+      </c>
+      <c r="I21" s="81">
+        <f>(F21+G21+H21)*0.07</f>
+        <v>9.1639800000000005</v>
+      </c>
+      <c r="J21" s="81">
+        <f>E21+F21+I21+G21+H21</f>
+        <v>63140.077979999995</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" s="12" customFormat="1">
+      <c r="A22" s="13">
+        <v>45545</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="15">
+        <f>C21</f>
+        <v>5000</v>
+      </c>
+      <c r="D22" s="24">
+        <v>12.7</v>
+      </c>
+      <c r="E22" s="16">
+        <f>C22*D22</f>
+        <v>63500</v>
+      </c>
+      <c r="F22" s="25">
+        <f>E22*0.002</f>
+        <v>127</v>
+      </c>
+      <c r="G22" s="24">
+        <f>E22*0.000068</f>
+        <v>4.3179999999999996</v>
+      </c>
+      <c r="H22" s="24">
+        <f>E22*0.00001</f>
+        <v>0.63500000000000001</v>
+      </c>
+      <c r="I22" s="24">
+        <f>(F22+G22+H22)*0.07</f>
+        <v>9.2367100000000004</v>
+      </c>
+      <c r="J22" s="24">
+        <f>E22-F22-G22-H22-I22</f>
+        <v>63358.810290000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A23" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="14"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="17">
+        <f>E22-E21</f>
+        <v>500</v>
+      </c>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17">
+        <f>J22-J21</f>
+        <v>218.73231000000669</v>
+      </c>
+      <c r="K23" s="11"/>
+    </row>
+    <row r="26" spans="1:14">
+      <c r="A26" s="77">
+        <v>45021</v>
+      </c>
+      <c r="B26" s="78" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26" s="79">
+        <v>24000</v>
+      </c>
+      <c r="D26" s="80">
+        <v>12.95</v>
+      </c>
+      <c r="E26" s="81">
+        <f>C26*D26</f>
+        <v>310800</v>
+      </c>
+      <c r="F26" s="81">
+        <f>E26*0.002</f>
+        <v>621.6</v>
+      </c>
+      <c r="G26" s="81">
+        <f>E26*0.000068</f>
+        <v>21.134399999999999</v>
+      </c>
+      <c r="H26" s="81">
+        <f>E26*0.00001</f>
+        <v>3.1080000000000001</v>
+      </c>
+      <c r="I26" s="81">
+        <f>(F26+G26+H26)*0.07</f>
+        <v>45.208968000000006</v>
+      </c>
+      <c r="J26" s="81">
+        <f>E26+F26+I26+G26+H26</f>
+        <v>311491.05136799999</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:K65"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -5193,7 +6070,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4115D497-67E5-4755-A37C-D801F1CE1CC8}">
   <dimension ref="A1:N39"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -6627,7 +7504,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BECE484-9DAC-4EE9-A8FE-27A01698073E}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -7291,7 +8168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61165D-6E4D-45AE-A027-1F0635508A9D}">
   <dimension ref="A1:M36"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -8258,7 +9135,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAF9A6BF-841A-4E49-8659-89A8DE11562A}">
   <dimension ref="A1:O44"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -9744,7 +10621,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:M76"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -12262,7 +13139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9C5701E-1EA3-43D6-ACCE-96288D740D8D}">
   <dimension ref="A1:M24"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -13031,7 +13908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EB85145-85AB-4FD8-916A-3D8FBC3904D4}">
   <dimension ref="A1:O35"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -14280,7 +15157,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65E8F5AF-E88A-4677-AEAF-7B4DD5AE4F27}">
   <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -14562,498 +15439,6 @@
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF44050E-F770-4816-B0BF-6EDA56061E31}">
-  <dimension ref="A1:M14"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="10.109375" style="35" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="20" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" style="20" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="20" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="20" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="20"/>
-    <col min="7" max="7" width="6.6640625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="5.77734375" style="20" customWidth="1"/>
-    <col min="9" max="9" width="7.21875" style="20" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" style="20" customWidth="1"/>
-    <col min="11" max="11" width="5.6640625" style="20" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" style="20"/>
-    <col min="13" max="13" width="8.88671875" style="23"/>
-    <col min="14" max="16384" width="8.88671875" style="20"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:13">
-      <c r="B1" s="20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" s="1" customFormat="1">
-      <c r="A2" s="46">
-        <v>45877</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>2500</v>
-      </c>
-      <c r="D2" s="38">
-        <v>32</v>
-      </c>
-      <c r="E2" s="17">
-        <f>C2*D2</f>
-        <v>80000</v>
-      </c>
-      <c r="F2" s="17">
-        <f>E2*0.002</f>
-        <v>160</v>
-      </c>
-      <c r="G2" s="17">
-        <f>E2*0.00006</f>
-        <v>4.8</v>
-      </c>
-      <c r="H2" s="17">
-        <f>E2*0.00001</f>
-        <v>0.8</v>
-      </c>
-      <c r="I2" s="17">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>11.592000000000002</v>
-      </c>
-      <c r="J2" s="17">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>80177.19200000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" s="1" customFormat="1">
-      <c r="A3" s="46">
-        <v>45901</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15">
-        <v>2500</v>
-      </c>
-      <c r="D3" s="38">
-        <v>31</v>
-      </c>
-      <c r="E3" s="17">
-        <f>C3*D3</f>
-        <v>77500</v>
-      </c>
-      <c r="F3" s="17">
-        <f>E3*0.002</f>
-        <v>155</v>
-      </c>
-      <c r="G3" s="17">
-        <f>E3*0.00006</f>
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="H3" s="17">
-        <f>E3*0.00001</f>
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="I3" s="17">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>11.229750000000001</v>
-      </c>
-      <c r="J3" s="17">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>77671.654749999987</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" s="1" customFormat="1">
-      <c r="A4" s="46"/>
-      <c r="B4" s="28">
-        <f>(D3-D2)/D2</f>
-        <v>-3.125E-2</v>
-      </c>
-      <c r="C4" s="15">
-        <f>SUM(C2:C3)</f>
-        <v>5000</v>
-      </c>
-      <c r="D4" s="37">
-        <f>E4/C4</f>
-        <v>31.5</v>
-      </c>
-      <c r="E4" s="15">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>157500</v>
-      </c>
-      <c r="F4" s="15">
-        <f t="shared" si="0"/>
-        <v>315</v>
-      </c>
-      <c r="G4" s="15">
-        <f t="shared" si="0"/>
-        <v>9.4499999999999993</v>
-      </c>
-      <c r="H4" s="15">
-        <f t="shared" si="0"/>
-        <v>1.5750000000000002</v>
-      </c>
-      <c r="I4" s="15">
-        <f t="shared" si="0"/>
-        <v>22.821750000000002</v>
-      </c>
-      <c r="J4" s="15">
-        <f t="shared" si="0"/>
-        <v>157848.84675</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" s="1" customFormat="1">
-      <c r="A5" s="46">
-        <v>45919</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="15">
-        <v>2500</v>
-      </c>
-      <c r="D5" s="38">
-        <v>33</v>
-      </c>
-      <c r="E5" s="17">
-        <f>C5*D5</f>
-        <v>82500</v>
-      </c>
-      <c r="F5" s="17">
-        <f>E5*0.002</f>
-        <v>165</v>
-      </c>
-      <c r="G5" s="17">
-        <f>E5*0.00006</f>
-        <v>4.95</v>
-      </c>
-      <c r="H5" s="17">
-        <f>E5*0.00001</f>
-        <v>0.82500000000000007</v>
-      </c>
-      <c r="I5" s="17">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>11.95425</v>
-      </c>
-      <c r="J5" s="17">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>82682.729249999989</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" s="1" customFormat="1">
-      <c r="A6" s="46"/>
-      <c r="B6" s="28">
-        <f>(D5-D4)/D4</f>
-        <v>4.7619047619047616E-2</v>
-      </c>
-      <c r="C6" s="15">
-        <f>SUM(C4:C5)</f>
-        <v>7500</v>
-      </c>
-      <c r="D6" s="37">
-        <f>E6/C6</f>
-        <v>32</v>
-      </c>
-      <c r="E6" s="15">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>240000</v>
-      </c>
-      <c r="F6" s="15">
-        <f t="shared" si="1"/>
-        <v>480</v>
-      </c>
-      <c r="G6" s="15">
-        <f t="shared" si="1"/>
-        <v>14.399999999999999</v>
-      </c>
-      <c r="H6" s="15">
-        <f t="shared" si="1"/>
-        <v>2.4000000000000004</v>
-      </c>
-      <c r="I6" s="15">
-        <f t="shared" si="1"/>
-        <v>34.776000000000003</v>
-      </c>
-      <c r="J6" s="15">
-        <f t="shared" si="1"/>
-        <v>240531.576</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" s="1" customFormat="1">
-      <c r="A7" s="46">
-        <v>45946</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="15">
-        <v>2500</v>
-      </c>
-      <c r="D7" s="38">
-        <v>31</v>
-      </c>
-      <c r="E7" s="17">
-        <f>C7*D7</f>
-        <v>77500</v>
-      </c>
-      <c r="F7" s="17">
-        <f>E7*0.002</f>
-        <v>155</v>
-      </c>
-      <c r="G7" s="17">
-        <f>E7*0.00006</f>
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="H7" s="17">
-        <f>E7*0.00001</f>
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="I7" s="17">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>11.229750000000001</v>
-      </c>
-      <c r="J7" s="17">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>77671.654749999987</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" s="1" customFormat="1">
-      <c r="A8" s="46"/>
-      <c r="B8" s="28">
-        <f>(D7-D6)/D6</f>
-        <v>-3.125E-2</v>
-      </c>
-      <c r="C8" s="15">
-        <f>SUM(C6:C7)</f>
-        <v>10000</v>
-      </c>
-      <c r="D8" s="37">
-        <f>E8/C8</f>
-        <v>31.75</v>
-      </c>
-      <c r="E8" s="15">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>317500</v>
-      </c>
-      <c r="F8" s="15">
-        <f t="shared" si="2"/>
-        <v>635</v>
-      </c>
-      <c r="G8" s="15">
-        <f t="shared" si="2"/>
-        <v>19.049999999999997</v>
-      </c>
-      <c r="H8" s="15">
-        <f t="shared" si="2"/>
-        <v>3.1750000000000003</v>
-      </c>
-      <c r="I8" s="15">
-        <f t="shared" si="2"/>
-        <v>46.005750000000006</v>
-      </c>
-      <c r="J8" s="15">
-        <f t="shared" si="2"/>
-        <v>318203.23074999999</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="52">
-        <v>45946</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="9">
-        <v>2500</v>
-      </c>
-      <c r="D9" s="43">
-        <v>30.5</v>
-      </c>
-      <c r="E9" s="19">
-        <f>C9*D9</f>
-        <v>76250</v>
-      </c>
-      <c r="F9" s="19">
-        <f>E9*0.002</f>
-        <v>152.5</v>
-      </c>
-      <c r="G9" s="19">
-        <f>E9*0.00006</f>
-        <v>4.5750000000000002</v>
-      </c>
-      <c r="H9" s="19">
-        <f>E9*0.00001</f>
-        <v>0.76250000000000007</v>
-      </c>
-      <c r="I9" s="19">
-        <f>(F9+G9+H9)*0.07</f>
-        <v>11.048624999999999</v>
-      </c>
-      <c r="J9" s="19">
-        <f>E9+F9+I9+G9+H9</f>
-        <v>76418.88612499999</v>
-      </c>
-      <c r="M9" s="20"/>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="52"/>
-      <c r="B10" s="11">
-        <f>(D9-D8)/D8</f>
-        <v>-3.937007874015748E-2</v>
-      </c>
-      <c r="C10" s="9">
-        <f>SUM(C8:C9)</f>
-        <v>12500</v>
-      </c>
-      <c r="D10" s="60">
-        <f>E10/C10</f>
-        <v>31.5</v>
-      </c>
-      <c r="E10" s="9">
-        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
-        <v>393750</v>
-      </c>
-      <c r="F10" s="9">
-        <f t="shared" si="3"/>
-        <v>787.5</v>
-      </c>
-      <c r="G10" s="9">
-        <f t="shared" si="3"/>
-        <v>23.624999999999996</v>
-      </c>
-      <c r="H10" s="9">
-        <f t="shared" si="3"/>
-        <v>3.9375000000000004</v>
-      </c>
-      <c r="I10" s="9">
-        <f t="shared" si="3"/>
-        <v>57.054375000000007</v>
-      </c>
-      <c r="J10" s="9">
-        <f t="shared" si="3"/>
-        <v>394622.11687499995</v>
-      </c>
-      <c r="M10" s="20"/>
-    </row>
-    <row r="11" spans="1:13" s="12" customFormat="1">
-      <c r="A11" s="52"/>
-      <c r="B11" s="14"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
-      <c r="J11" s="32"/>
-    </row>
-    <row r="12" spans="1:13" s="1" customFormat="1">
-      <c r="A12" s="46">
-        <v>45946</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C12" s="15">
-        <v>2500</v>
-      </c>
-      <c r="D12" s="38">
-        <v>31</v>
-      </c>
-      <c r="E12" s="17">
-        <f>C12*D12</f>
-        <v>77500</v>
-      </c>
-      <c r="F12" s="17">
-        <f>E12*0.002</f>
-        <v>155</v>
-      </c>
-      <c r="G12" s="17">
-        <f>E12*0.00006</f>
-        <v>4.6500000000000004</v>
-      </c>
-      <c r="H12" s="17">
-        <f>E12*0.00001</f>
-        <v>0.77500000000000002</v>
-      </c>
-      <c r="I12" s="17">
-        <f>(F12+G12+H12)*0.07</f>
-        <v>11.229750000000001</v>
-      </c>
-      <c r="J12" s="17">
-        <f>E12+F12+I12+G12+H12</f>
-        <v>77671.654749999987</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" s="52">
-        <v>44853</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C13" s="9">
-        <f>C12</f>
-        <v>2500</v>
-      </c>
-      <c r="D13" s="32">
-        <v>31.25</v>
-      </c>
-      <c r="E13" s="10">
-        <f>C13*D13</f>
-        <v>78125</v>
-      </c>
-      <c r="F13" s="33">
-        <f>E13*0.002</f>
-        <v>156.25</v>
-      </c>
-      <c r="G13" s="32">
-        <f>E13*0.000068</f>
-        <v>5.3125</v>
-      </c>
-      <c r="H13" s="32">
-        <f>E13*0.00001</f>
-        <v>0.78125000000000011</v>
-      </c>
-      <c r="I13" s="32">
-        <f>(F13+G13+H13)*0.07</f>
-        <v>11.364062500000001</v>
-      </c>
-      <c r="J13" s="32">
-        <f>E13-F13-G13-H13-I13</f>
-        <v>77951.292187500003</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="52"/>
-      <c r="B14" s="11">
-        <f>(D13-D12)/D12</f>
-        <v>8.0645161290322578E-3</v>
-      </c>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="19">
-        <f>E13-E12</f>
-        <v>625</v>
-      </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19"/>
-      <c r="J14" s="19">
-        <f>J13-J12</f>
-        <v>279.63743750001595</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
@@ -17145,6 +17530,498 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF44050E-F770-4816-B0BF-6EDA56061E31}">
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="10.109375" style="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="7.6640625" style="20" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="20" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="20"/>
+    <col min="7" max="7" width="6.6640625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="7.21875" style="20" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" style="20" customWidth="1"/>
+    <col min="11" max="11" width="5.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="20"/>
+    <col min="13" max="13" width="8.88671875" style="23"/>
+    <col min="14" max="16384" width="8.88671875" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="B1" s="20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" s="1" customFormat="1">
+      <c r="A2" s="46">
+        <v>45877</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15">
+        <v>2500</v>
+      </c>
+      <c r="D2" s="38">
+        <v>32</v>
+      </c>
+      <c r="E2" s="17">
+        <f>C2*D2</f>
+        <v>80000</v>
+      </c>
+      <c r="F2" s="17">
+        <f>E2*0.002</f>
+        <v>160</v>
+      </c>
+      <c r="G2" s="17">
+        <f>E2*0.00006</f>
+        <v>4.8</v>
+      </c>
+      <c r="H2" s="17">
+        <f>E2*0.00001</f>
+        <v>0.8</v>
+      </c>
+      <c r="I2" s="17">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>11.592000000000002</v>
+      </c>
+      <c r="J2" s="17">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>80177.19200000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" s="1" customFormat="1">
+      <c r="A3" s="46">
+        <v>45901</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15">
+        <v>2500</v>
+      </c>
+      <c r="D3" s="38">
+        <v>31</v>
+      </c>
+      <c r="E3" s="17">
+        <f>C3*D3</f>
+        <v>77500</v>
+      </c>
+      <c r="F3" s="17">
+        <f>E3*0.002</f>
+        <v>155</v>
+      </c>
+      <c r="G3" s="17">
+        <f>E3*0.00006</f>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H3" s="17">
+        <f>E3*0.00001</f>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="I3" s="17">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>11.229750000000001</v>
+      </c>
+      <c r="J3" s="17">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>77671.654749999987</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" s="1" customFormat="1">
+      <c r="A4" s="46"/>
+      <c r="B4" s="28">
+        <f>(D3-D2)/D2</f>
+        <v>-3.125E-2</v>
+      </c>
+      <c r="C4" s="15">
+        <f>SUM(C2:C3)</f>
+        <v>5000</v>
+      </c>
+      <c r="D4" s="37">
+        <f>E4/C4</f>
+        <v>31.5</v>
+      </c>
+      <c r="E4" s="15">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>157500</v>
+      </c>
+      <c r="F4" s="15">
+        <f t="shared" si="0"/>
+        <v>315</v>
+      </c>
+      <c r="G4" s="15">
+        <f t="shared" si="0"/>
+        <v>9.4499999999999993</v>
+      </c>
+      <c r="H4" s="15">
+        <f t="shared" si="0"/>
+        <v>1.5750000000000002</v>
+      </c>
+      <c r="I4" s="15">
+        <f t="shared" si="0"/>
+        <v>22.821750000000002</v>
+      </c>
+      <c r="J4" s="15">
+        <f t="shared" si="0"/>
+        <v>157848.84675</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" s="1" customFormat="1">
+      <c r="A5" s="46">
+        <v>45919</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="15">
+        <v>2500</v>
+      </c>
+      <c r="D5" s="38">
+        <v>33</v>
+      </c>
+      <c r="E5" s="17">
+        <f>C5*D5</f>
+        <v>82500</v>
+      </c>
+      <c r="F5" s="17">
+        <f>E5*0.002</f>
+        <v>165</v>
+      </c>
+      <c r="G5" s="17">
+        <f>E5*0.00006</f>
+        <v>4.95</v>
+      </c>
+      <c r="H5" s="17">
+        <f>E5*0.00001</f>
+        <v>0.82500000000000007</v>
+      </c>
+      <c r="I5" s="17">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>11.95425</v>
+      </c>
+      <c r="J5" s="17">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>82682.729249999989</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" s="1" customFormat="1">
+      <c r="A6" s="46"/>
+      <c r="B6" s="28">
+        <f>(D5-D4)/D4</f>
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="C6" s="15">
+        <f>SUM(C4:C5)</f>
+        <v>7500</v>
+      </c>
+      <c r="D6" s="37">
+        <f>E6/C6</f>
+        <v>32</v>
+      </c>
+      <c r="E6" s="15">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>240000</v>
+      </c>
+      <c r="F6" s="15">
+        <f t="shared" si="1"/>
+        <v>480</v>
+      </c>
+      <c r="G6" s="15">
+        <f t="shared" si="1"/>
+        <v>14.399999999999999</v>
+      </c>
+      <c r="H6" s="15">
+        <f t="shared" si="1"/>
+        <v>2.4000000000000004</v>
+      </c>
+      <c r="I6" s="15">
+        <f t="shared" si="1"/>
+        <v>34.776000000000003</v>
+      </c>
+      <c r="J6" s="15">
+        <f t="shared" si="1"/>
+        <v>240531.576</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" s="1" customFormat="1">
+      <c r="A7" s="46">
+        <v>45946</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="15">
+        <v>2500</v>
+      </c>
+      <c r="D7" s="38">
+        <v>31</v>
+      </c>
+      <c r="E7" s="17">
+        <f>C7*D7</f>
+        <v>77500</v>
+      </c>
+      <c r="F7" s="17">
+        <f>E7*0.002</f>
+        <v>155</v>
+      </c>
+      <c r="G7" s="17">
+        <f>E7*0.00006</f>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H7" s="17">
+        <f>E7*0.00001</f>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="I7" s="17">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>11.229750000000001</v>
+      </c>
+      <c r="J7" s="17">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>77671.654749999987</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" s="1" customFormat="1">
+      <c r="A8" s="46"/>
+      <c r="B8" s="28">
+        <f>(D7-D6)/D6</f>
+        <v>-3.125E-2</v>
+      </c>
+      <c r="C8" s="15">
+        <f>SUM(C6:C7)</f>
+        <v>10000</v>
+      </c>
+      <c r="D8" s="37">
+        <f>E8/C8</f>
+        <v>31.75</v>
+      </c>
+      <c r="E8" s="15">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>317500</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="2"/>
+        <v>635</v>
+      </c>
+      <c r="G8" s="15">
+        <f t="shared" si="2"/>
+        <v>19.049999999999997</v>
+      </c>
+      <c r="H8" s="15">
+        <f t="shared" si="2"/>
+        <v>3.1750000000000003</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="2"/>
+        <v>46.005750000000006</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="2"/>
+        <v>318203.23074999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="52">
+        <v>45946</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>2500</v>
+      </c>
+      <c r="D9" s="43">
+        <v>30.5</v>
+      </c>
+      <c r="E9" s="19">
+        <f>C9*D9</f>
+        <v>76250</v>
+      </c>
+      <c r="F9" s="19">
+        <f>E9*0.002</f>
+        <v>152.5</v>
+      </c>
+      <c r="G9" s="19">
+        <f>E9*0.00006</f>
+        <v>4.5750000000000002</v>
+      </c>
+      <c r="H9" s="19">
+        <f>E9*0.00001</f>
+        <v>0.76250000000000007</v>
+      </c>
+      <c r="I9" s="19">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>11.048624999999999</v>
+      </c>
+      <c r="J9" s="19">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>76418.88612499999</v>
+      </c>
+      <c r="M9" s="20"/>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="52"/>
+      <c r="B10" s="11">
+        <f>(D9-D8)/D8</f>
+        <v>-3.937007874015748E-2</v>
+      </c>
+      <c r="C10" s="9">
+        <f>SUM(C8:C9)</f>
+        <v>12500</v>
+      </c>
+      <c r="D10" s="60">
+        <f>E10/C10</f>
+        <v>31.5</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
+        <v>393750</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" si="3"/>
+        <v>787.5</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" si="3"/>
+        <v>23.624999999999996</v>
+      </c>
+      <c r="H10" s="9">
+        <f t="shared" si="3"/>
+        <v>3.9375000000000004</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="3"/>
+        <v>57.054375000000007</v>
+      </c>
+      <c r="J10" s="9">
+        <f t="shared" si="3"/>
+        <v>394622.11687499995</v>
+      </c>
+      <c r="M10" s="20"/>
+    </row>
+    <row r="11" spans="1:13" s="12" customFormat="1">
+      <c r="A11" s="52"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+    </row>
+    <row r="12" spans="1:13" s="1" customFormat="1">
+      <c r="A12" s="46">
+        <v>45946</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="15">
+        <v>2500</v>
+      </c>
+      <c r="D12" s="38">
+        <v>31</v>
+      </c>
+      <c r="E12" s="17">
+        <f>C12*D12</f>
+        <v>77500</v>
+      </c>
+      <c r="F12" s="17">
+        <f>E12*0.002</f>
+        <v>155</v>
+      </c>
+      <c r="G12" s="17">
+        <f>E12*0.00006</f>
+        <v>4.6500000000000004</v>
+      </c>
+      <c r="H12" s="17">
+        <f>E12*0.00001</f>
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="I12" s="17">
+        <f>(F12+G12+H12)*0.07</f>
+        <v>11.229750000000001</v>
+      </c>
+      <c r="J12" s="17">
+        <f>E12+F12+I12+G12+H12</f>
+        <v>77671.654749999987</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="52">
+        <v>44853</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" s="9">
+        <f>C12</f>
+        <v>2500</v>
+      </c>
+      <c r="D13" s="32">
+        <v>31.25</v>
+      </c>
+      <c r="E13" s="10">
+        <f>C13*D13</f>
+        <v>78125</v>
+      </c>
+      <c r="F13" s="33">
+        <f>E13*0.002</f>
+        <v>156.25</v>
+      </c>
+      <c r="G13" s="32">
+        <f>E13*0.000068</f>
+        <v>5.3125</v>
+      </c>
+      <c r="H13" s="32">
+        <f>E13*0.00001</f>
+        <v>0.78125000000000011</v>
+      </c>
+      <c r="I13" s="32">
+        <f>(F13+G13+H13)*0.07</f>
+        <v>11.364062500000001</v>
+      </c>
+      <c r="J13" s="32">
+        <f>E13-F13-G13-H13-I13</f>
+        <v>77951.292187500003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="52"/>
+      <c r="B14" s="11">
+        <f>(D13-D12)/D12</f>
+        <v>8.0645161290322578E-3</v>
+      </c>
+      <c r="C14" s="9"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="19">
+        <f>E13-E12</f>
+        <v>625</v>
+      </c>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19">
+        <f>J13-J12</f>
+        <v>279.63743750001595</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CA21CC0-18F7-46BF-9D73-A50571C8D635}">
   <dimension ref="A1:N51"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -19032,7 +19909,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5868373-E563-434B-9630-0799FB268869}">
   <dimension ref="A1:M16"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -19648,7 +20525,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0248C1A-0BE1-4664-895A-D29EA068DDA6}">
   <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -20052,7 +20929,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
   <dimension ref="A1:M40"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -21477,7 +22354,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D30CFA7-C46B-4885-A4A3-CF2E8439A3D7}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -22095,7 +22972,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6E0B64A-B432-4F71-9E82-2EF3D53BA2E8}">
   <dimension ref="A1:N13"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -22431,7 +23308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2313500C-829E-4589-85F6-0C28EBDE7508}">
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -22792,7 +23669,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8D35EBD-FACE-4A0A-BE47-8E8EEE95DB23}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -23441,7 +24318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E38AEBDA-97A4-44E7-92FF-AB904E0EA610}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
@@ -25299,6 +26176,511 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A1E39D-E0DC-4E64-B1B9-8FC123E1523A}">
+  <dimension ref="A1:N13"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
+  <cols>
+    <col min="1" max="1" width="10.6640625" style="35" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="20" customWidth="1"/>
+    <col min="3" max="3" width="6.6640625" style="20" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" style="88" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="20" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" style="20"/>
+    <col min="7" max="7" width="6.6640625" style="20" customWidth="1"/>
+    <col min="8" max="8" width="5.77734375" style="20" customWidth="1"/>
+    <col min="9" max="9" width="7.21875" style="20" customWidth="1"/>
+    <col min="10" max="10" width="11.109375" style="20" customWidth="1"/>
+    <col min="11" max="11" width="5.6640625" style="20" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.88671875" style="20"/>
+    <col min="13" max="13" width="8.88671875" style="23"/>
+    <col min="14" max="16384" width="8.88671875" style="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="B1" s="20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1">
+      <c r="A2" s="46">
+        <v>46080</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="15">
+        <v>100</v>
+      </c>
+      <c r="D2" s="27">
+        <v>380</v>
+      </c>
+      <c r="E2" s="17">
+        <f>C2*D2</f>
+        <v>38000</v>
+      </c>
+      <c r="F2" s="17">
+        <f>E2*0.002</f>
+        <v>76</v>
+      </c>
+      <c r="G2" s="17">
+        <f>E2*0.00006</f>
+        <v>2.2800000000000002</v>
+      </c>
+      <c r="H2" s="17">
+        <f>E2*0.00001</f>
+        <v>0.38</v>
+      </c>
+      <c r="I2" s="17">
+        <f>(F2+G2+H2)*0.07</f>
+        <v>5.5062000000000006</v>
+      </c>
+      <c r="J2" s="17">
+        <f>E2+F2+I2+G2+H2</f>
+        <v>38084.1662</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="12" customFormat="1">
+      <c r="A3" s="63">
+        <v>44473</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="9">
+        <v>100</v>
+      </c>
+      <c r="D3" s="30">
+        <v>360</v>
+      </c>
+      <c r="E3" s="19">
+        <f>C3*D3</f>
+        <v>36000</v>
+      </c>
+      <c r="F3" s="19">
+        <f>E3*0.002</f>
+        <v>72</v>
+      </c>
+      <c r="G3" s="19">
+        <f>E3*0.00006</f>
+        <v>2.16</v>
+      </c>
+      <c r="H3" s="19">
+        <f>E3*0.00001</f>
+        <v>0.36000000000000004</v>
+      </c>
+      <c r="I3" s="19">
+        <f>(F3+G3+H3)*0.07</f>
+        <v>5.2164000000000001</v>
+      </c>
+      <c r="J3" s="19">
+        <f>E3+F3+I3+G3+H3</f>
+        <v>36079.736400000002</v>
+      </c>
+      <c r="K3" s="30"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="11"/>
+    </row>
+    <row r="4" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A4" s="52"/>
+      <c r="B4" s="72">
+        <f>(D3-D2)/D2</f>
+        <v>-5.2631578947368418E-2</v>
+      </c>
+      <c r="C4" s="9">
+        <f>SUM(C2:C3)</f>
+        <v>200</v>
+      </c>
+      <c r="D4" s="30">
+        <f>E4/C4</f>
+        <v>370</v>
+      </c>
+      <c r="E4" s="9">
+        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
+        <v>74000</v>
+      </c>
+      <c r="F4" s="9">
+        <f t="shared" si="0"/>
+        <v>148</v>
+      </c>
+      <c r="G4" s="9">
+        <f t="shared" si="0"/>
+        <v>4.4400000000000004</v>
+      </c>
+      <c r="H4" s="9">
+        <f t="shared" si="0"/>
+        <v>0.74</v>
+      </c>
+      <c r="I4" s="9">
+        <f t="shared" si="0"/>
+        <v>10.7226</v>
+      </c>
+      <c r="J4" s="9">
+        <f t="shared" si="0"/>
+        <v>74163.902600000001</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="L4" s="12"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+    </row>
+    <row r="5" spans="1:14" s="12" customFormat="1">
+      <c r="A5" s="63">
+        <v>44473</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="9">
+        <v>100</v>
+      </c>
+      <c r="D5" s="30">
+        <v>358</v>
+      </c>
+      <c r="E5" s="19">
+        <f>C5*D5</f>
+        <v>35800</v>
+      </c>
+      <c r="F5" s="19">
+        <f>E5*0.002</f>
+        <v>71.600000000000009</v>
+      </c>
+      <c r="G5" s="19">
+        <f>E5*0.00006</f>
+        <v>2.1480000000000001</v>
+      </c>
+      <c r="H5" s="19">
+        <f>E5*0.00001</f>
+        <v>0.35800000000000004</v>
+      </c>
+      <c r="I5" s="19">
+        <f>(F5+G5+H5)*0.07</f>
+        <v>5.1874200000000013</v>
+      </c>
+      <c r="J5" s="19">
+        <f>E5+F5+I5+G5+H5</f>
+        <v>35879.293420000002</v>
+      </c>
+      <c r="K5" s="30"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A6" s="52"/>
+      <c r="B6" s="72">
+        <f>(D5-D4)/D4</f>
+        <v>-3.2432432432432434E-2</v>
+      </c>
+      <c r="C6" s="9">
+        <f>SUM(C4:C5)</f>
+        <v>300</v>
+      </c>
+      <c r="D6" s="30">
+        <f>E6/C6</f>
+        <v>366</v>
+      </c>
+      <c r="E6" s="9">
+        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
+        <v>109800</v>
+      </c>
+      <c r="F6" s="9">
+        <f t="shared" si="1"/>
+        <v>219.60000000000002</v>
+      </c>
+      <c r="G6" s="9">
+        <f t="shared" si="1"/>
+        <v>6.588000000000001</v>
+      </c>
+      <c r="H6" s="9">
+        <f t="shared" si="1"/>
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="I6" s="9">
+        <f t="shared" si="1"/>
+        <v>15.910020000000001</v>
+      </c>
+      <c r="J6" s="9">
+        <f t="shared" si="1"/>
+        <v>110043.19602</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="12"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+    </row>
+    <row r="7" spans="1:14" s="12" customFormat="1">
+      <c r="A7" s="63">
+        <v>44473</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="9">
+        <v>100</v>
+      </c>
+      <c r="D7" s="30">
+        <v>362</v>
+      </c>
+      <c r="E7" s="19">
+        <f>C7*D7</f>
+        <v>36200</v>
+      </c>
+      <c r="F7" s="19">
+        <f>E7*0.002</f>
+        <v>72.400000000000006</v>
+      </c>
+      <c r="G7" s="19">
+        <f>E7*0.00006</f>
+        <v>2.1720000000000002</v>
+      </c>
+      <c r="H7" s="19">
+        <f>E7*0.00001</f>
+        <v>0.36200000000000004</v>
+      </c>
+      <c r="I7" s="19">
+        <f>(F7+G7+H7)*0.07</f>
+        <v>5.2453799999999999</v>
+      </c>
+      <c r="J7" s="19">
+        <f>E7+F7+I7+G7+H7</f>
+        <v>36280.179380000001</v>
+      </c>
+      <c r="K7" s="30"/>
+      <c r="L7" s="10"/>
+      <c r="M7" s="11"/>
+    </row>
+    <row r="8" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A8" s="52"/>
+      <c r="B8" s="72">
+        <f>(D7-D6)/D6</f>
+        <v>-1.092896174863388E-2</v>
+      </c>
+      <c r="C8" s="9">
+        <f>SUM(C6:C7)</f>
+        <v>400</v>
+      </c>
+      <c r="D8" s="30">
+        <f>E8/C8</f>
+        <v>365</v>
+      </c>
+      <c r="E8" s="9">
+        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
+        <v>146000</v>
+      </c>
+      <c r="F8" s="9">
+        <f t="shared" si="2"/>
+        <v>292</v>
+      </c>
+      <c r="G8" s="9">
+        <f t="shared" si="2"/>
+        <v>8.7600000000000016</v>
+      </c>
+      <c r="H8" s="9">
+        <f t="shared" si="2"/>
+        <v>1.4600000000000002</v>
+      </c>
+      <c r="I8" s="9">
+        <f t="shared" si="2"/>
+        <v>21.1554</v>
+      </c>
+      <c r="J8" s="9">
+        <f t="shared" si="2"/>
+        <v>146323.37540000002</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+    </row>
+    <row r="9" spans="1:14" s="12" customFormat="1">
+      <c r="A9" s="63">
+        <v>44473</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="9">
+        <v>100</v>
+      </c>
+      <c r="D9" s="30">
+        <v>355</v>
+      </c>
+      <c r="E9" s="19">
+        <f>C9*D9</f>
+        <v>35500</v>
+      </c>
+      <c r="F9" s="19">
+        <f>E9*0.002</f>
+        <v>71</v>
+      </c>
+      <c r="G9" s="19">
+        <f>E9*0.00006</f>
+        <v>2.13</v>
+      </c>
+      <c r="H9" s="19">
+        <f>E9*0.00001</f>
+        <v>0.35500000000000004</v>
+      </c>
+      <c r="I9" s="19">
+        <f>(F9+G9+H9)*0.07</f>
+        <v>5.1439500000000002</v>
+      </c>
+      <c r="J9" s="19">
+        <f>E9+F9+I9+G9+H9</f>
+        <v>35578.628949999998</v>
+      </c>
+      <c r="K9" s="30"/>
+      <c r="L9" s="10"/>
+      <c r="M9" s="11"/>
+    </row>
+    <row r="10" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A10" s="52"/>
+      <c r="B10" s="72">
+        <f>(D9-D8)/D8</f>
+        <v>-2.7397260273972601E-2</v>
+      </c>
+      <c r="C10" s="9">
+        <f>SUM(C8:C9)</f>
+        <v>500</v>
+      </c>
+      <c r="D10" s="30">
+        <f>E10/C10</f>
+        <v>363</v>
+      </c>
+      <c r="E10" s="9">
+        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
+        <v>181500</v>
+      </c>
+      <c r="F10" s="9">
+        <f t="shared" si="3"/>
+        <v>363</v>
+      </c>
+      <c r="G10" s="9">
+        <f t="shared" si="3"/>
+        <v>10.89</v>
+      </c>
+      <c r="H10" s="9">
+        <f t="shared" si="3"/>
+        <v>1.8150000000000002</v>
+      </c>
+      <c r="I10" s="9">
+        <f t="shared" si="3"/>
+        <v>26.29935</v>
+      </c>
+      <c r="J10" s="9">
+        <f t="shared" si="3"/>
+        <v>181902.00435</v>
+      </c>
+      <c r="K10" s="10"/>
+      <c r="L10" s="12"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="58"/>
+    </row>
+    <row r="11" spans="1:14" s="12" customFormat="1">
+      <c r="A11" s="63">
+        <v>44473</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="9">
+        <v>100</v>
+      </c>
+      <c r="D11" s="30">
+        <v>345</v>
+      </c>
+      <c r="E11" s="19">
+        <f>C11*D11</f>
+        <v>34500</v>
+      </c>
+      <c r="F11" s="19">
+        <f>E11*0.002</f>
+        <v>69</v>
+      </c>
+      <c r="G11" s="19">
+        <f>E11*0.00006</f>
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="H11" s="19">
+        <f>E11*0.00001</f>
+        <v>0.34500000000000003</v>
+      </c>
+      <c r="I11" s="19">
+        <f>(F11+G11+H11)*0.07</f>
+        <v>4.9990499999999995</v>
+      </c>
+      <c r="J11" s="19">
+        <f>E11+F11+I11+G11+H11</f>
+        <v>34576.414049999999</v>
+      </c>
+      <c r="K11" s="30"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="11"/>
+    </row>
+    <row r="12" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A12" s="52"/>
+      <c r="B12" s="72">
+        <f>(D11-D10)/D10</f>
+        <v>-4.9586776859504134E-2</v>
+      </c>
+      <c r="C12" s="9">
+        <f>SUM(C10:C11)</f>
+        <v>600</v>
+      </c>
+      <c r="D12" s="30">
+        <f>E12/C12</f>
+        <v>360</v>
+      </c>
+      <c r="E12" s="9">
+        <f t="shared" ref="E12:J12" si="4">SUM(E10:E11)</f>
+        <v>216000</v>
+      </c>
+      <c r="F12" s="9">
+        <f t="shared" si="4"/>
+        <v>432</v>
+      </c>
+      <c r="G12" s="9">
+        <f t="shared" si="4"/>
+        <v>12.96</v>
+      </c>
+      <c r="H12" s="9">
+        <f t="shared" si="4"/>
+        <v>2.16</v>
+      </c>
+      <c r="I12" s="9">
+        <f t="shared" si="4"/>
+        <v>31.298400000000001</v>
+      </c>
+      <c r="J12" s="9">
+        <f t="shared" si="4"/>
+        <v>216478.4184</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="C13" s="20">
+        <v>400</v>
+      </c>
+      <c r="D13" s="88">
+        <f>E13/C13</f>
+        <v>355</v>
+      </c>
+      <c r="E13" s="22">
+        <f>E5+E7+E9+E11</f>
+        <v>142000</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4839E04C-5799-4EDF-A8E5-4A6D5C617CB4}">
   <dimension ref="A1:N8"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -25555,7 +26937,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05574364-77F0-49AB-A1F4-209718CEC5C7}">
   <dimension ref="A1:N12"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -25955,7 +27337,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BC0A6D1-469B-4A9E-8AB4-B1F9082325E0}">
   <dimension ref="A1:O9"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -26231,7 +27613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9557670-D125-4921-A689-63714DB07995}">
   <dimension ref="A1:M23"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -27016,7 +28398,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E3593A5-F4A3-43B6-A6B6-3CA4F1D0F412}">
   <dimension ref="A1:N30"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
@@ -27899,877 +29281,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFB529E6-7221-4171-9EDF-80891E84F736}">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
-  <cols>
-    <col min="1" max="1" width="10.109375" style="47" customWidth="1"/>
-    <col min="2" max="2" width="7.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="6.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.109375" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14">
-      <c r="B1" s="47" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" s="18" customFormat="1" ht="15.6">
-      <c r="A2" s="46">
-        <v>44789</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="15">
-        <v>5000</v>
-      </c>
-      <c r="D2" s="38">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="E2" s="17">
-        <f>C2*D2</f>
-        <v>97000</v>
-      </c>
-      <c r="F2" s="17">
-        <f>E2*0.002</f>
-        <v>194</v>
-      </c>
-      <c r="G2" s="17">
-        <f>E2*0.00006</f>
-        <v>5.82</v>
-      </c>
-      <c r="H2" s="17">
-        <f>E2*0.00001</f>
-        <v>0.97000000000000008</v>
-      </c>
-      <c r="I2" s="17">
-        <f>(F2+G2+H2)*0.07</f>
-        <v>14.055300000000001</v>
-      </c>
-      <c r="J2" s="17">
-        <f>E2+F2+I2+G2+H2</f>
-        <v>97214.845300000015</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" s="73" customFormat="1">
-      <c r="A3" s="77">
-        <v>44818</v>
-      </c>
-      <c r="B3" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="79">
-        <v>5000</v>
-      </c>
-      <c r="D3" s="80">
-        <v>19</v>
-      </c>
-      <c r="E3" s="81">
-        <f>C3*D3</f>
-        <v>95000</v>
-      </c>
-      <c r="F3" s="81">
-        <f>E3*0.002</f>
-        <v>190</v>
-      </c>
-      <c r="G3" s="81">
-        <f>E3*0.000068</f>
-        <v>6.46</v>
-      </c>
-      <c r="H3" s="81">
-        <f>E3*0.00001</f>
-        <v>0.95000000000000007</v>
-      </c>
-      <c r="I3" s="81">
-        <f>(F3+G3+H3)*0.07</f>
-        <v>13.818700000000002</v>
-      </c>
-      <c r="J3" s="81">
-        <f>E3+F3+I3+G3+H3</f>
-        <v>95211.228700000007</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" s="73" customFormat="1">
-      <c r="A4" s="77"/>
-      <c r="B4" s="82">
-        <f>(D3-D2)/D2</f>
-        <v>-2.0618556701030855E-2</v>
-      </c>
-      <c r="C4" s="79">
-        <f>SUM(C2:C3)</f>
-        <v>10000</v>
-      </c>
-      <c r="D4" s="80">
-        <f>E4/C4</f>
-        <v>19.2</v>
-      </c>
-      <c r="E4" s="79">
-        <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>192000</v>
-      </c>
-      <c r="F4" s="79">
-        <f t="shared" si="0"/>
-        <v>384</v>
-      </c>
-      <c r="G4" s="79">
-        <f t="shared" si="0"/>
-        <v>12.280000000000001</v>
-      </c>
-      <c r="H4" s="79">
-        <f t="shared" si="0"/>
-        <v>1.9200000000000002</v>
-      </c>
-      <c r="I4" s="79">
-        <f t="shared" si="0"/>
-        <v>27.874000000000002</v>
-      </c>
-      <c r="J4" s="79">
-        <f t="shared" si="0"/>
-        <v>192426.07400000002</v>
-      </c>
-      <c r="K4" s="76"/>
-    </row>
-    <row r="5" spans="1:14" s="73" customFormat="1">
-      <c r="A5" s="77">
-        <v>44880</v>
-      </c>
-      <c r="B5" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="79">
-        <v>10000</v>
-      </c>
-      <c r="D5" s="80">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="E5" s="81">
-        <f>C5*D5</f>
-        <v>186000</v>
-      </c>
-      <c r="F5" s="81">
-        <f>E5*0.002</f>
-        <v>372</v>
-      </c>
-      <c r="G5" s="81">
-        <f>E5*0.000068</f>
-        <v>12.648</v>
-      </c>
-      <c r="H5" s="81">
-        <f>E5*0.00001</f>
-        <v>1.86</v>
-      </c>
-      <c r="I5" s="81">
-        <f>(F5+G5+H5)*0.07</f>
-        <v>27.055560000000007</v>
-      </c>
-      <c r="J5" s="81">
-        <f>E5+F5+I5+G5+H5</f>
-        <v>186413.56355999998</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="73" customFormat="1">
-      <c r="A6" s="77"/>
-      <c r="B6" s="82">
-        <f>(D5-D4)/D4</f>
-        <v>-3.1249999999999889E-2</v>
-      </c>
-      <c r="C6" s="79">
-        <f>SUM(C4:C5)</f>
-        <v>20000</v>
-      </c>
-      <c r="D6" s="80">
-        <f>E6/C6</f>
-        <v>18.899999999999999</v>
-      </c>
-      <c r="E6" s="79">
-        <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>378000</v>
-      </c>
-      <c r="F6" s="79">
-        <f t="shared" si="1"/>
-        <v>756</v>
-      </c>
-      <c r="G6" s="79">
-        <f t="shared" si="1"/>
-        <v>24.928000000000001</v>
-      </c>
-      <c r="H6" s="79">
-        <f t="shared" si="1"/>
-        <v>3.7800000000000002</v>
-      </c>
-      <c r="I6" s="79">
-        <f t="shared" si="1"/>
-        <v>54.929560000000009</v>
-      </c>
-      <c r="J6" s="79">
-        <f t="shared" si="1"/>
-        <v>378839.63756</v>
-      </c>
-      <c r="K6" s="76"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="77">
-        <v>44950</v>
-      </c>
-      <c r="B7" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="79">
-        <v>10000</v>
-      </c>
-      <c r="D7" s="80">
-        <v>19.5</v>
-      </c>
-      <c r="E7" s="81">
-        <f>C7*D7</f>
-        <v>195000</v>
-      </c>
-      <c r="F7" s="81">
-        <f>E7*0.002</f>
-        <v>390</v>
-      </c>
-      <c r="G7" s="81">
-        <f>E7*0.000068</f>
-        <v>13.26</v>
-      </c>
-      <c r="H7" s="81">
-        <f>E7*0.00001</f>
-        <v>1.9500000000000002</v>
-      </c>
-      <c r="I7" s="81">
-        <f>(F7+G7+H7)*0.07</f>
-        <v>28.364700000000003</v>
-      </c>
-      <c r="J7" s="81">
-        <f>E7+F7+I7+G7+H7</f>
-        <v>195433.57470000003</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="59" customFormat="1" ht="21">
-      <c r="A8" s="77"/>
-      <c r="B8" s="82">
-        <f>(D7-D6)/D6</f>
-        <v>3.1746031746031821E-2</v>
-      </c>
-      <c r="C8" s="79">
-        <f>SUM(C6:C7)</f>
-        <v>30000</v>
-      </c>
-      <c r="D8" s="80">
-        <f>E8/C8</f>
-        <v>19.100000000000001</v>
-      </c>
-      <c r="E8" s="79">
-        <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>573000</v>
-      </c>
-      <c r="F8" s="79">
-        <f t="shared" si="2"/>
-        <v>1146</v>
-      </c>
-      <c r="G8" s="79">
-        <f t="shared" si="2"/>
-        <v>38.188000000000002</v>
-      </c>
-      <c r="H8" s="79">
-        <f t="shared" si="2"/>
-        <v>5.73</v>
-      </c>
-      <c r="I8" s="79">
-        <f t="shared" si="2"/>
-        <v>83.294260000000008</v>
-      </c>
-      <c r="J8" s="79">
-        <f t="shared" si="2"/>
-        <v>574273.21226000006</v>
-      </c>
-      <c r="K8" s="10"/>
-      <c r="L8" s="12"/>
-      <c r="M8" s="58"/>
-      <c r="N8" s="58"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="77">
-        <v>44964</v>
-      </c>
-      <c r="B9" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C9" s="79">
-        <v>10000</v>
-      </c>
-      <c r="D9" s="80">
-        <v>18.3</v>
-      </c>
-      <c r="E9" s="81">
-        <f>C9*D9</f>
-        <v>183000</v>
-      </c>
-      <c r="F9" s="81">
-        <f>E9*0.002</f>
-        <v>366</v>
-      </c>
-      <c r="G9" s="81">
-        <f>E9*0.000068</f>
-        <v>12.443999999999999</v>
-      </c>
-      <c r="H9" s="81">
-        <f>E9*0.00001</f>
-        <v>1.83</v>
-      </c>
-      <c r="I9" s="81">
-        <f>(F9+G9+H9)*0.07</f>
-        <v>26.619180000000004</v>
-      </c>
-      <c r="J9" s="81">
-        <f>E9+F9+I9+G9+H9</f>
-        <v>183406.89317999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="77"/>
-      <c r="B10" s="82">
-        <f>(D9-D8)/D8</f>
-        <v>-4.1884816753926739E-2</v>
-      </c>
-      <c r="C10" s="79">
-        <f>SUM(C8:C9)</f>
-        <v>40000</v>
-      </c>
-      <c r="D10" s="80">
-        <f>E10/C10</f>
-        <v>18.899999999999999</v>
-      </c>
-      <c r="E10" s="79">
-        <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
-        <v>756000</v>
-      </c>
-      <c r="F10" s="79">
-        <f t="shared" si="3"/>
-        <v>1512</v>
-      </c>
-      <c r="G10" s="79">
-        <f t="shared" si="3"/>
-        <v>50.632000000000005</v>
-      </c>
-      <c r="H10" s="79">
-        <f t="shared" si="3"/>
-        <v>7.5600000000000005</v>
-      </c>
-      <c r="I10" s="79">
-        <f t="shared" si="3"/>
-        <v>109.91344000000001</v>
-      </c>
-      <c r="J10" s="79">
-        <f t="shared" si="3"/>
-        <v>757680.10544000007</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="77">
-        <v>44986</v>
-      </c>
-      <c r="B11" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="79">
-        <v>10000</v>
-      </c>
-      <c r="D11" s="80">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="E11" s="81">
-        <f>C11*D11</f>
-        <v>164000</v>
-      </c>
-      <c r="F11" s="81">
-        <f>E11*0.002</f>
-        <v>328</v>
-      </c>
-      <c r="G11" s="81">
-        <f>E11*0.000068</f>
-        <v>11.151999999999999</v>
-      </c>
-      <c r="H11" s="81">
-        <f>E11*0.00001</f>
-        <v>1.6400000000000001</v>
-      </c>
-      <c r="I11" s="81">
-        <f>(F11+G11+H11)*0.07</f>
-        <v>23.855440000000002</v>
-      </c>
-      <c r="J11" s="81">
-        <f>E11+F11+I11+G11+H11</f>
-        <v>164364.64744000003</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="77"/>
-      <c r="B12" s="82">
-        <f>(D11-D10)/D10</f>
-        <v>-0.1322751322751323</v>
-      </c>
-      <c r="C12" s="79">
-        <f>SUM(C10:C11)</f>
-        <v>50000</v>
-      </c>
-      <c r="D12" s="80">
-        <f>E12/C12</f>
-        <v>18.399999999999999</v>
-      </c>
-      <c r="E12" s="79">
-        <f t="shared" ref="E12:J12" si="4">SUM(E10:E11)</f>
-        <v>920000</v>
-      </c>
-      <c r="F12" s="79">
-        <f t="shared" si="4"/>
-        <v>1840</v>
-      </c>
-      <c r="G12" s="79">
-        <f t="shared" si="4"/>
-        <v>61.784000000000006</v>
-      </c>
-      <c r="H12" s="79">
-        <f t="shared" si="4"/>
-        <v>9.2000000000000011</v>
-      </c>
-      <c r="I12" s="79">
-        <f t="shared" si="4"/>
-        <v>133.76888000000002</v>
-      </c>
-      <c r="J12" s="79">
-        <f t="shared" si="4"/>
-        <v>922044.75288000004</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="77">
-        <v>44994</v>
-      </c>
-      <c r="B13" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C13" s="79">
-        <v>5000</v>
-      </c>
-      <c r="D13" s="80">
-        <v>14</v>
-      </c>
-      <c r="E13" s="81">
-        <f>C13*D13</f>
-        <v>70000</v>
-      </c>
-      <c r="F13" s="81">
-        <f>E13*0.002</f>
-        <v>140</v>
-      </c>
-      <c r="G13" s="81">
-        <f>E13*0.000068</f>
-        <v>4.76</v>
-      </c>
-      <c r="H13" s="81">
-        <f>E13*0.00001</f>
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="I13" s="81">
-        <f>(F13+G13+H13)*0.07</f>
-        <v>10.1822</v>
-      </c>
-      <c r="J13" s="81">
-        <f>E13+F13+I13+G13+H13</f>
-        <v>70155.642199999987</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="77"/>
-      <c r="B14" s="82">
-        <f>(D13-D12)/D12</f>
-        <v>-0.23913043478260865</v>
-      </c>
-      <c r="C14" s="79">
-        <f>SUM(C12:C13)</f>
-        <v>55000</v>
-      </c>
-      <c r="D14" s="80">
-        <f>E14/C14</f>
-        <v>18</v>
-      </c>
-      <c r="E14" s="79">
-        <f t="shared" ref="E14:J14" si="5">SUM(E12:E13)</f>
-        <v>990000</v>
-      </c>
-      <c r="F14" s="79">
-        <f t="shared" si="5"/>
-        <v>1980</v>
-      </c>
-      <c r="G14" s="79">
-        <f t="shared" si="5"/>
-        <v>66.544000000000011</v>
-      </c>
-      <c r="H14" s="79">
-        <f t="shared" si="5"/>
-        <v>9.9</v>
-      </c>
-      <c r="I14" s="79">
-        <f t="shared" si="5"/>
-        <v>143.95108000000002</v>
-      </c>
-      <c r="J14" s="79">
-        <f t="shared" si="5"/>
-        <v>992200.39508000005</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" s="20" customFormat="1">
-      <c r="A15" s="7">
-        <v>44260</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C15" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="75">
-        <v>10.8</v>
-      </c>
-      <c r="E15" s="86">
-        <f>C15*D15</f>
-        <v>54000</v>
-      </c>
-      <c r="F15" s="86">
-        <f>E15*0.002</f>
-        <v>108</v>
-      </c>
-      <c r="G15" s="86">
-        <f>E15*0.000068</f>
-        <v>3.6720000000000002</v>
-      </c>
-      <c r="H15" s="86">
-        <f>E15*0.00001</f>
-        <v>0.54</v>
-      </c>
-      <c r="I15" s="86">
-        <f>(F15+G15+H15)*0.07</f>
-        <v>7.8548400000000012</v>
-      </c>
-      <c r="J15" s="86">
-        <f>E15+F15+I15+G15+H15</f>
-        <v>54120.06684</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" s="20" customFormat="1">
-      <c r="A16" s="41"/>
-      <c r="B16" s="76">
-        <f>(D15-D14)/D14</f>
-        <v>-0.39999999999999997</v>
-      </c>
-      <c r="C16" s="21">
-        <f>SUM(C14:C15)</f>
-        <v>60000</v>
-      </c>
-      <c r="D16" s="31">
-        <f>E16/C16</f>
-        <v>17.399999999999999</v>
-      </c>
-      <c r="E16" s="21">
-        <f t="shared" ref="E16:J16" si="6">SUM(E14:E15)</f>
-        <v>1044000</v>
-      </c>
-      <c r="F16" s="21">
-        <f t="shared" si="6"/>
-        <v>2088</v>
-      </c>
-      <c r="G16" s="21">
-        <f t="shared" si="6"/>
-        <v>70.216000000000008</v>
-      </c>
-      <c r="H16" s="21">
-        <f t="shared" si="6"/>
-        <v>10.440000000000001</v>
-      </c>
-      <c r="I16" s="21">
-        <f t="shared" si="6"/>
-        <v>151.80592000000001</v>
-      </c>
-      <c r="J16" s="21">
-        <f t="shared" si="6"/>
-        <v>1046320.46192</v>
-      </c>
-      <c r="K16" s="23"/>
-    </row>
-    <row r="17" spans="1:14" s="20" customFormat="1">
-      <c r="A17" s="41"/>
-      <c r="B17" s="76"/>
-      <c r="C17" s="21"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-      <c r="K17" s="23"/>
-    </row>
-    <row r="18" spans="1:14" s="20" customFormat="1">
-      <c r="A18" s="77">
-        <v>45097</v>
-      </c>
-      <c r="B18" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="79">
-        <v>3000</v>
-      </c>
-      <c r="D18" s="80">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="E18" s="81">
-        <f>C18*D18</f>
-        <v>30599.999999999996</v>
-      </c>
-      <c r="F18" s="81">
-        <f>E18*0.002</f>
-        <v>61.199999999999996</v>
-      </c>
-      <c r="G18" s="81">
-        <f>E18*0.000068</f>
-        <v>2.0807999999999995</v>
-      </c>
-      <c r="H18" s="81">
-        <f>E18*0.00001</f>
-        <v>0.30599999999999999</v>
-      </c>
-      <c r="I18" s="81">
-        <f>(F18+G18+H18)*0.07</f>
-        <v>4.4510759999999996</v>
-      </c>
-      <c r="J18" s="81">
-        <f>E18+F18+I18+G18+H18</f>
-        <v>30668.037875999999</v>
-      </c>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-    </row>
-    <row r="19" spans="1:14" s="20" customFormat="1">
-      <c r="A19" s="13">
-        <v>45100</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C19" s="15">
-        <f>C18</f>
-        <v>3000</v>
-      </c>
-      <c r="D19" s="24">
-        <v>10.7</v>
-      </c>
-      <c r="E19" s="16">
-        <f>C19*D19</f>
-        <v>32099.999999999996</v>
-      </c>
-      <c r="F19" s="25">
-        <f>E19*0.002</f>
-        <v>64.199999999999989</v>
-      </c>
-      <c r="G19" s="24">
-        <f>E19*0.000068</f>
-        <v>2.1827999999999999</v>
-      </c>
-      <c r="H19" s="24">
-        <f>E19*0.00001</f>
-        <v>0.32100000000000001</v>
-      </c>
-      <c r="I19" s="24">
-        <f>(F19+G19+H19)*0.07</f>
-        <v>4.6692659999999995</v>
-      </c>
-      <c r="J19" s="24">
-        <f>E19-F19-G19-H19-I19</f>
-        <v>32028.626933999996</v>
-      </c>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-    </row>
-    <row r="20" spans="1:14" s="20" customFormat="1" ht="18.600000000000001">
-      <c r="A20" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B20" s="14"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="17">
-        <f>E19-E18</f>
-        <v>1500</v>
-      </c>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17">
-        <f>J19-J18</f>
-        <v>1360.5890579999977</v>
-      </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="77">
-        <v>44998</v>
-      </c>
-      <c r="B21" s="78" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="79">
-        <v>5000</v>
-      </c>
-      <c r="D21" s="80">
-        <v>12.6</v>
-      </c>
-      <c r="E21" s="81">
-        <f>C21*D21</f>
-        <v>63000</v>
-      </c>
-      <c r="F21" s="81">
-        <f>E21*0.002</f>
-        <v>126</v>
-      </c>
-      <c r="G21" s="81">
-        <f>E21*0.000068</f>
-        <v>4.2839999999999998</v>
-      </c>
-      <c r="H21" s="81">
-        <f>E21*0.00001</f>
-        <v>0.63</v>
-      </c>
-      <c r="I21" s="81">
-        <f>(F21+G21+H21)*0.07</f>
-        <v>9.1639800000000005</v>
-      </c>
-      <c r="J21" s="81">
-        <f>E21+F21+I21+G21+H21</f>
-        <v>63140.077979999995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" s="12" customFormat="1">
-      <c r="A22" s="13">
-        <v>45545</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C22" s="15">
-        <f>C21</f>
-        <v>5000</v>
-      </c>
-      <c r="D22" s="24">
-        <v>12.7</v>
-      </c>
-      <c r="E22" s="16">
-        <f>C22*D22</f>
-        <v>63500</v>
-      </c>
-      <c r="F22" s="25">
-        <f>E22*0.002</f>
-        <v>127</v>
-      </c>
-      <c r="G22" s="24">
-        <f>E22*0.000068</f>
-        <v>4.3179999999999996</v>
-      </c>
-      <c r="H22" s="24">
-        <f>E22*0.00001</f>
-        <v>0.63500000000000001</v>
-      </c>
-      <c r="I22" s="24">
-        <f>(F22+G22+H22)*0.07</f>
-        <v>9.2367100000000004</v>
-      </c>
-      <c r="J22" s="24">
-        <f>E22-F22-G22-H22-I22</f>
-        <v>63358.810290000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A23" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="14"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17">
-        <f>E22-E21</f>
-        <v>500</v>
-      </c>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17">
-        <f>J22-J21</f>
-        <v>218.73231000000669</v>
-      </c>
-      <c r="K23" s="11"/>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="77">
-        <v>45021</v>
-      </c>
-      <c r="B26" s="78" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="79">
-        <v>24000</v>
-      </c>
-      <c r="D26" s="80">
-        <v>12.95</v>
-      </c>
-      <c r="E26" s="81">
-        <f>C26*D26</f>
-        <v>310800</v>
-      </c>
-      <c r="F26" s="81">
-        <f>E26*0.002</f>
-        <v>621.6</v>
-      </c>
-      <c r="G26" s="81">
-        <f>E26*0.000068</f>
-        <v>21.134399999999999</v>
-      </c>
-      <c r="H26" s="81">
-        <f>E26*0.00001</f>
-        <v>3.1080000000000001</v>
-      </c>
-      <c r="I26" s="81">
-        <f>(F26+G26+H26)*0.07</f>
-        <v>45.208968000000006</v>
-      </c>
-      <c r="J26" s="81">
-        <f>E26+F26+I26+G26+H26</f>
-        <v>311491.05136799999</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1745" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FB50B5C-2277-4E6F-BB28-263CB052D67B}"/>
+  <xr:revisionPtr revIDLastSave="1841" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25641D0C-D666-4834-B152-240364F62029}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4164" yWindow="864" windowWidth="18420" windowHeight="11364" tabRatio="461" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12120" yWindow="1608" windowWidth="10068" windowHeight="10764" tabRatio="461" firstSheet="27" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="44">
   <si>
     <t>BUY</t>
   </si>
@@ -168,9 +168,6 @@
     <t>WHAIR</t>
   </si>
   <si>
-    <t>-----------</t>
-  </si>
-  <si>
     <t>CPF</t>
   </si>
   <si>
@@ -191,21 +188,30 @@
   <si>
     <t>ADVANC</t>
   </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>HD</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="187" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="189" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="190" formatCode="\฿#,##0.000"/>
-    <numFmt numFmtId="191" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="192" formatCode="0.0000"/>
-    <numFmt numFmtId="193" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="194" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="195" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="\฿#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="171" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -333,12 +339,24 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -353,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="106">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -364,64 +382,64 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -429,30 +447,45 @@
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -468,6 +501,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10623,18 +10660,19 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
-  <dimension ref="A1:M76"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.109375" style="41" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.44140625" style="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5546875" style="97" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" style="97" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8" style="97" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="5.5546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.5546875" style="20" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" style="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" style="97" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="97" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.109375" style="97" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.44140625" style="97" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.6640625" style="97" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.5546875" style="97" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12" style="97" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.109375" style="97" bestFit="1" customWidth="1"/>
     <col min="11" max="16384" width="8.88671875" style="20"/>
   </cols>
   <sheetData>
@@ -10683,13 +10721,13 @@
       <c r="K2" s="16"/>
     </row>
     <row r="3" spans="1:13" s="12" customFormat="1">
-      <c r="A3" s="13">
+      <c r="A3" s="99">
         <v>42633</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="15">
+      <c r="B3" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="101">
         <v>10000</v>
       </c>
       <c r="D3" s="24">
@@ -10755,13 +10793,13 @@
       </c>
     </row>
     <row r="5" spans="1:13" s="12" customFormat="1">
-      <c r="A5" s="13">
+      <c r="A5" s="99">
         <v>42656</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="15">
+      <c r="B5" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="101">
         <v>10000</v>
       </c>
       <c r="D5" s="24">
@@ -11277,13 +11315,13 @@
       </c>
     </row>
     <row r="21" spans="1:13" s="12" customFormat="1">
-      <c r="A21" s="13">
+      <c r="A21" s="99">
         <v>42674</v>
       </c>
-      <c r="B21" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="15">
+      <c r="B21" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" s="101">
         <v>10000</v>
       </c>
       <c r="D21" s="24">
@@ -11416,13 +11454,13 @@
       <c r="K24" s="16"/>
     </row>
     <row r="25" spans="1:13" s="12" customFormat="1">
-      <c r="A25" s="13">
+      <c r="A25" s="99">
         <v>42688</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="15">
+      <c r="B25" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="101">
         <v>10000</v>
       </c>
       <c r="D25" s="24">
@@ -11712,13 +11750,13 @@
       </c>
     </row>
     <row r="33" spans="1:11" s="12" customFormat="1">
-      <c r="A33" s="13">
+      <c r="A33" s="99">
         <v>42691</v>
       </c>
-      <c r="B33" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C33" s="15">
+      <c r="B33" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" s="101">
         <v>10000</v>
       </c>
       <c r="D33" s="24">
@@ -12425,13 +12463,13 @@
       </c>
     </row>
     <row r="54" spans="1:10" s="12" customFormat="1">
-      <c r="A54" s="13">
+      <c r="A54" s="99">
         <v>44669</v>
       </c>
-      <c r="B54" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C54" s="15">
+      <c r="B54" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="C54" s="101">
         <v>25000</v>
       </c>
       <c r="D54" s="24">
@@ -12641,278 +12679,204 @@
       <c r="H59" s="24"/>
       <c r="I59" s="24"/>
       <c r="J59" s="24">
-        <f>J58-J57</f>
-        <v>-1151177.546232</v>
+        <f>J57-J58</f>
+        <v>1151177.546232</v>
       </c>
     </row>
     <row r="60" spans="1:10" s="12" customFormat="1">
-      <c r="A60" s="7">
-        <v>45709</v>
-      </c>
-      <c r="B60" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C60" s="9">
+      <c r="A60" s="13">
+        <v>46139</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C60" s="15">
         <v>5000</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="24">
         <v>8</v>
       </c>
-      <c r="E60" s="32">
+      <c r="E60" s="24">
         <f>C60*D60</f>
         <v>40000</v>
       </c>
-      <c r="F60" s="32">
+      <c r="F60" s="24">
         <f>E60*0.002</f>
         <v>80</v>
       </c>
-      <c r="G60" s="32">
+      <c r="G60" s="24">
         <f>E60*0.000068</f>
         <v>2.72</v>
       </c>
-      <c r="H60" s="32">
+      <c r="H60" s="24">
         <f>E60*0.00001</f>
         <v>0.4</v>
       </c>
-      <c r="I60" s="32">
+      <c r="I60" s="24">
         <f>(F60+G60+H60)*0.07</f>
         <v>5.8184000000000005</v>
       </c>
-      <c r="J60" s="32">
+      <c r="J60" s="24">
         <f>E60+F60+I60+G60+H60</f>
         <v>40088.938399999999</v>
       </c>
     </row>
     <row r="61" spans="1:10">
-      <c r="B61" s="11">
-        <f>(D60-D59)/D59</f>
-        <v>-0.47753396029258094</v>
-      </c>
-      <c r="C61" s="21">
-        <f>SUM(C59:C60)</f>
-        <v>80000</v>
-      </c>
-      <c r="D61" s="97">
-        <f>E61/C61</f>
-        <v>14.855</v>
-      </c>
-      <c r="E61" s="97">
-        <f t="shared" ref="E61:J61" si="18">SUM(E59:E60)</f>
-        <v>1188400</v>
-      </c>
-      <c r="F61" s="97">
-        <f t="shared" si="18"/>
-        <v>80</v>
-      </c>
-      <c r="G61" s="97">
-        <f t="shared" si="18"/>
-        <v>2.72</v>
-      </c>
-      <c r="H61" s="97">
-        <f t="shared" si="18"/>
-        <v>0.4</v>
-      </c>
-      <c r="I61" s="97">
-        <f t="shared" si="18"/>
-        <v>5.8184000000000005</v>
-      </c>
-      <c r="J61" s="97">
-        <f t="shared" si="18"/>
-        <v>-1111088.6078319999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:10" s="12" customFormat="1">
-      <c r="A63" s="13">
-        <v>44672</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C63" s="15">
-        <v>15000</v>
-      </c>
-      <c r="D63" s="24">
-        <v>12.1</v>
-      </c>
-      <c r="E63" s="24">
-        <f>C63*D63</f>
-        <v>181500</v>
-      </c>
-      <c r="F63" s="24">
-        <f>E63*0.002</f>
-        <v>363</v>
-      </c>
-      <c r="G63" s="24">
-        <f>E63*0.000068</f>
-        <v>12.342000000000001</v>
-      </c>
-      <c r="H63" s="24">
-        <f>E63*0.00001</f>
-        <v>1.8150000000000002</v>
-      </c>
-      <c r="I63" s="24">
-        <f>(F63+G63+H63)*0.07</f>
-        <v>26.40099</v>
-      </c>
-      <c r="J63" s="24">
-        <f>E63+F63+I63+G63+H63</f>
-        <v>181903.55799</v>
-      </c>
+      <c r="A61" s="46">
+        <v>46153</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C61" s="15">
+        <v>5000</v>
+      </c>
+      <c r="D61" s="24">
+        <v>7.8</v>
+      </c>
+      <c r="E61" s="24">
+        <f>C61*D61</f>
+        <v>39000</v>
+      </c>
+      <c r="F61" s="24">
+        <f>E61*0.002</f>
+        <v>78</v>
+      </c>
+      <c r="G61" s="24">
+        <f>E61*0.000068</f>
+        <v>2.6520000000000001</v>
+      </c>
+      <c r="H61" s="24">
+        <f>E61*0.00001</f>
+        <v>0.39</v>
+      </c>
+      <c r="I61" s="24">
+        <f>(F61+G61+H61)*0.07</f>
+        <v>5.6729400000000005</v>
+      </c>
+      <c r="J61" s="24">
+        <f>E61-F61-G61-H61-I61</f>
+        <v>38913.285060000002</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="41">
+        <v>46153</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C62" s="21">
+        <v>75000</v>
+      </c>
+      <c r="D62" s="31">
+        <f>E62/C62</f>
+        <v>15.311999999999999</v>
+      </c>
+      <c r="E62" s="45">
+        <v>1148400</v>
+      </c>
+      <c r="J62" s="97">
+        <v>1151177.546232</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="E63" s="45"/>
     </row>
     <row r="64" spans="1:10">
-      <c r="A64" s="46">
-        <v>44679</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>2</v>
-      </c>
-      <c r="C64" s="15">
-        <f>C63</f>
-        <v>15000</v>
-      </c>
-      <c r="D64" s="24">
-        <v>12.5</v>
-      </c>
-      <c r="E64" s="24">
-        <f>C64*D64</f>
-        <v>187500</v>
-      </c>
-      <c r="F64" s="24">
-        <f>E64*0.002</f>
-        <v>375</v>
-      </c>
-      <c r="G64" s="24">
-        <f>E64*0.000068</f>
-        <v>12.75</v>
-      </c>
-      <c r="H64" s="24">
-        <f>E64*0.00001</f>
-        <v>1.8750000000000002</v>
-      </c>
-      <c r="I64" s="24">
-        <f>(F64+G64+H64)*0.07</f>
-        <v>27.273750000000003</v>
-      </c>
-      <c r="J64" s="24">
-        <f>E64-F64-G64-H64-I64</f>
-        <v>187083.10125000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:10">
-      <c r="A65" s="26">
-        <f>DAYS360(A63,A64)</f>
-        <v>7</v>
-      </c>
-      <c r="B65" s="28">
-        <f>(D64-D63)/D63</f>
-        <v>3.305785123966945E-2</v>
-      </c>
-      <c r="C65" s="15"/>
-      <c r="D65" s="24"/>
-      <c r="E65" s="24">
-        <f>E64-E63</f>
-        <v>6000</v>
-      </c>
-      <c r="F65" s="24"/>
-      <c r="G65" s="24"/>
-      <c r="H65" s="24"/>
-      <c r="I65" s="24"/>
-      <c r="J65" s="24">
-        <f>J64-J63</f>
-        <v>5179.5432600000058</v>
-      </c>
+      <c r="E64" s="45"/>
     </row>
     <row r="66" spans="1:10" s="12" customFormat="1">
       <c r="A66" s="13">
-        <v>44740</v>
+        <v>44672</v>
       </c>
       <c r="B66" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C66" s="15">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="D66" s="24">
-        <v>7.6</v>
+        <v>12.1</v>
       </c>
       <c r="E66" s="24">
         <f>C66*D66</f>
-        <v>22800</v>
+        <v>181500</v>
       </c>
       <c r="F66" s="24">
         <f>E66*0.002</f>
-        <v>45.6</v>
+        <v>363</v>
       </c>
       <c r="G66" s="24">
         <f>E66*0.000068</f>
-        <v>1.5504</v>
+        <v>12.342000000000001</v>
       </c>
       <c r="H66" s="24">
         <f>E66*0.00001</f>
-        <v>0.22800000000000001</v>
+        <v>1.8150000000000002</v>
       </c>
       <c r="I66" s="24">
         <f>(F66+G66+H66)*0.07</f>
-        <v>3.3164880000000005</v>
+        <v>26.40099</v>
       </c>
       <c r="J66" s="24">
         <f>E66+F66+I66+G66+H66</f>
-        <v>22850.694887999998</v>
+        <v>181903.55799</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="46">
-        <v>44741</v>
+        <v>44679</v>
       </c>
       <c r="B67" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C67" s="15">
         <f>C66</f>
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="D67" s="24">
-        <v>11.7</v>
+        <v>12.5</v>
       </c>
       <c r="E67" s="24">
         <f>C67*D67</f>
-        <v>35100</v>
+        <v>187500</v>
       </c>
       <c r="F67" s="24">
         <f>E67*0.002</f>
-        <v>70.2</v>
+        <v>375</v>
       </c>
       <c r="G67" s="24">
         <f>E67*0.000068</f>
-        <v>2.3868</v>
+        <v>12.75</v>
       </c>
       <c r="H67" s="24">
         <f>E67*0.00001</f>
-        <v>0.35100000000000003</v>
+        <v>1.8750000000000002</v>
       </c>
       <c r="I67" s="24">
         <f>(F67+G67+H67)*0.07</f>
-        <v>5.1056460000000001</v>
+        <v>27.273750000000003</v>
       </c>
       <c r="J67" s="24">
         <f>E67-F67-G67-H67-I67</f>
-        <v>35021.956553999997</v>
+        <v>187083.10125000001</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="26">
         <f>DAYS360(A66,A67)</f>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B68" s="28">
         <f>(D67-D66)/D66</f>
-        <v>0.53947368421052633</v>
+        <v>3.305785123966945E-2</v>
       </c>
       <c r="C68" s="15"/>
       <c r="D68" s="24"/>
       <c r="E68" s="24">
         <f>E67-E66</f>
-        <v>12300</v>
+        <v>6000</v>
       </c>
       <c r="F68" s="24"/>
       <c r="G68" s="24"/>
@@ -12920,12 +12884,12 @@
       <c r="I68" s="24"/>
       <c r="J68" s="24">
         <f>J67-J66</f>
-        <v>12171.261665999999</v>
-      </c>
-    </row>
-    <row r="69" spans="1:10" s="14" customFormat="1">
+        <v>5179.5432600000058</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" s="12" customFormat="1">
       <c r="A69" s="13">
-        <v>45063</v>
+        <v>44740</v>
       </c>
       <c r="B69" s="14" t="s">
         <v>0</v>
@@ -12963,7 +12927,7 @@
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="46">
-        <v>45560</v>
+        <v>44741</v>
       </c>
       <c r="B70" s="14" t="s">
         <v>2</v>
@@ -12973,47 +12937,47 @@
         <v>3000</v>
       </c>
       <c r="D70" s="24">
-        <v>8.0500000000000007</v>
+        <v>11.7</v>
       </c>
       <c r="E70" s="24">
         <f>C70*D70</f>
-        <v>24150.000000000004</v>
+        <v>35100</v>
       </c>
       <c r="F70" s="24">
         <f>E70*0.002</f>
-        <v>48.300000000000011</v>
+        <v>70.2</v>
       </c>
       <c r="G70" s="24">
         <f>E70*0.000068</f>
-        <v>1.6422000000000003</v>
+        <v>2.3868</v>
       </c>
       <c r="H70" s="24">
         <f>E70*0.00001</f>
-        <v>0.24150000000000005</v>
+        <v>0.35100000000000003</v>
       </c>
       <c r="I70" s="24">
         <f>(F70+G70+H70)*0.07</f>
-        <v>3.5128590000000015</v>
+        <v>5.1056460000000001</v>
       </c>
       <c r="J70" s="24">
         <f>E70-F70-G70-H70-I70</f>
-        <v>24096.303441000007</v>
+        <v>35021.956553999997</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="26">
         <f>DAYS360(A69,A70)</f>
-        <v>488</v>
+        <v>1</v>
       </c>
       <c r="B71" s="28">
         <f>(D70-D69)/D69</f>
-        <v>5.9210526315789616E-2</v>
+        <v>0.53947368421052633</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="24"/>
       <c r="E71" s="24">
         <f>E70-E69</f>
-        <v>1350.0000000000036</v>
+        <v>12300</v>
       </c>
       <c r="F71" s="24"/>
       <c r="G71" s="24"/>
@@ -13021,100 +12985,100 @@
       <c r="I71" s="24"/>
       <c r="J71" s="24">
         <f>J70-J69</f>
-        <v>1245.6085530000091</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" s="12" customFormat="1">
+        <v>12171.261665999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" s="14" customFormat="1">
       <c r="A72" s="13">
-        <v>45709</v>
+        <v>45063</v>
       </c>
       <c r="B72" s="14" t="s">
         <v>0</v>
       </c>
       <c r="C72" s="15">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="D72" s="24">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="E72" s="24">
         <f>C72*D72</f>
-        <v>43800</v>
+        <v>22800</v>
       </c>
       <c r="F72" s="24">
         <f>E72*0.002</f>
-        <v>87.600000000000009</v>
+        <v>45.6</v>
       </c>
       <c r="G72" s="24">
         <f>E72*0.000068</f>
-        <v>2.9784000000000002</v>
+        <v>1.5504</v>
       </c>
       <c r="H72" s="24">
         <f>E72*0.00001</f>
-        <v>0.43800000000000006</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="I72" s="24">
         <f>(F72+G72+H72)*0.07</f>
-        <v>6.3711480000000007</v>
+        <v>3.3164880000000005</v>
       </c>
       <c r="J72" s="24">
         <f>E72+F72+I72+G72+H72</f>
-        <v>43897.387547999999</v>
+        <v>22850.694887999998</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="46">
-        <v>45896</v>
+        <v>45560</v>
       </c>
       <c r="B73" s="14" t="s">
         <v>2</v>
       </c>
       <c r="C73" s="15">
         <f>C72</f>
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="D73" s="24">
-        <v>8.4</v>
+        <v>8.0500000000000007</v>
       </c>
       <c r="E73" s="24">
         <f>C73*D73</f>
-        <v>50400</v>
+        <v>24150.000000000004</v>
       </c>
       <c r="F73" s="24">
         <f>E73*0.002</f>
-        <v>100.8</v>
+        <v>48.300000000000011</v>
       </c>
       <c r="G73" s="24">
         <f>E73*0.000068</f>
-        <v>3.4272</v>
+        <v>1.6422000000000003</v>
       </c>
       <c r="H73" s="24">
         <f>E73*0.00001</f>
-        <v>0.504</v>
+        <v>0.24150000000000005</v>
       </c>
       <c r="I73" s="24">
         <f>(F73+G73+H73)*0.07</f>
-        <v>7.3311840000000004</v>
+        <v>3.5128590000000015</v>
       </c>
       <c r="J73" s="24">
         <f>E73-F73-G73-H73-I73</f>
-        <v>50287.937615999996</v>
+        <v>24096.303441000007</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="26">
         <f>DAYS360(A72,A73)</f>
-        <v>186</v>
+        <v>488</v>
       </c>
       <c r="B74" s="28">
         <f>(D73-D72)/D72</f>
-        <v>0.15068493150684939</v>
+        <v>5.9210526315789616E-2</v>
       </c>
       <c r="C74" s="15"/>
       <c r="D74" s="24"/>
       <c r="E74" s="24">
         <f>E73-E72</f>
-        <v>6600</v>
+        <v>1350.0000000000036</v>
       </c>
       <c r="F74" s="24"/>
       <c r="G74" s="24"/>
@@ -13122,13 +13086,152 @@
       <c r="I74" s="24"/>
       <c r="J74" s="24">
         <f>J73-J72</f>
+        <v>1245.6085530000091</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" s="12" customFormat="1">
+      <c r="A75" s="13">
+        <v>45709</v>
+      </c>
+      <c r="B75" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="15">
+        <v>6000</v>
+      </c>
+      <c r="D75" s="24">
+        <v>7.3</v>
+      </c>
+      <c r="E75" s="24">
+        <f>C75*D75</f>
+        <v>43800</v>
+      </c>
+      <c r="F75" s="24">
+        <f>E75*0.002</f>
+        <v>87.600000000000009</v>
+      </c>
+      <c r="G75" s="24">
+        <f>E75*0.000068</f>
+        <v>2.9784000000000002</v>
+      </c>
+      <c r="H75" s="24">
+        <f>E75*0.00001</f>
+        <v>0.43800000000000006</v>
+      </c>
+      <c r="I75" s="24">
+        <f>(F75+G75+H75)*0.07</f>
+        <v>6.3711480000000007</v>
+      </c>
+      <c r="J75" s="24">
+        <f>E75+F75+I75+G75+H75</f>
+        <v>43897.387547999999</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10">
+      <c r="A76" s="46">
+        <v>45896</v>
+      </c>
+      <c r="B76" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="C76" s="15">
+        <f>C75</f>
+        <v>6000</v>
+      </c>
+      <c r="D76" s="24">
+        <v>8.4</v>
+      </c>
+      <c r="E76" s="24">
+        <f>C76*D76</f>
+        <v>50400</v>
+      </c>
+      <c r="F76" s="24">
+        <f>E76*0.002</f>
+        <v>100.8</v>
+      </c>
+      <c r="G76" s="24">
+        <f>E76*0.000068</f>
+        <v>3.4272</v>
+      </c>
+      <c r="H76" s="24">
+        <f>E76*0.00001</f>
+        <v>0.504</v>
+      </c>
+      <c r="I76" s="24">
+        <f>(F76+G76+H76)*0.07</f>
+        <v>7.3311840000000004</v>
+      </c>
+      <c r="J76" s="24">
+        <f>E76-F76-G76-H76-I76</f>
+        <v>50287.937615999996</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10">
+      <c r="A77" s="26">
+        <f>DAYS360(A75,A76)</f>
+        <v>186</v>
+      </c>
+      <c r="B77" s="28">
+        <f>(D76-D75)/D75</f>
+        <v>0.15068493150684939</v>
+      </c>
+      <c r="C77" s="15"/>
+      <c r="D77" s="24"/>
+      <c r="E77" s="24">
+        <f>E76-E75</f>
+        <v>6600</v>
+      </c>
+      <c r="F77" s="24"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24"/>
+      <c r="J77" s="24">
+        <f>J76-J75</f>
         <v>6390.5500679999968</v>
       </c>
     </row>
-    <row r="76" spans="1:10">
-      <c r="E76" s="97">
-        <f>E55+E72</f>
+    <row r="79" spans="1:10">
+      <c r="E79" s="97">
+        <f>E55+E75</f>
         <v>1198800</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12">
+      <c r="A81" s="102" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81" s="102">
+        <v>901</v>
+      </c>
+      <c r="C81" s="104">
+        <v>43</v>
+      </c>
+      <c r="D81" s="103">
+        <v>42826</v>
+      </c>
+      <c r="E81" s="104">
+        <v>10000</v>
+      </c>
+      <c r="F81" s="102">
+        <v>16.7</v>
+      </c>
+      <c r="G81" s="102">
+        <v>345.69</v>
+      </c>
+      <c r="H81" s="102">
+        <v>24.2</v>
+      </c>
+      <c r="I81" s="102" t="s">
+        <v>41</v>
+      </c>
+      <c r="J81" s="105">
+        <v>167369.89000000001</v>
+      </c>
+      <c r="K81" s="102" t="s">
+        <v>42</v>
+      </c>
+      <c r="L81" s="102" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -14988,7 +15091,7 @@
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:15">
@@ -17552,7 +17655,7 @@
   <sheetData>
     <row r="1" spans="1:13">
       <c r="B1" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:13" s="1" customFormat="1">
@@ -20931,7 +21034,7 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D015-9A6D-40DB-A099-73BBAC254E19}">
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M42"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="35" customWidth="1"/>
@@ -21740,31 +21843,31 @@
         <v>2500</v>
       </c>
       <c r="D22" s="10">
-        <v>9.6</v>
+        <v>9.1999999999999993</v>
       </c>
       <c r="E22" s="19">
         <f>C22*D22</f>
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="F22" s="19">
         <f>E22*0.002</f>
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G22" s="19">
         <f>E22*0.000068</f>
-        <v>1.6319999999999999</v>
+        <v>1.5640000000000001</v>
       </c>
       <c r="H22" s="19">
         <f>E22*0.00001</f>
-        <v>0.24000000000000002</v>
+        <v>0.23</v>
       </c>
       <c r="I22" s="19">
         <f>(F22+G22+H22)*0.07</f>
-        <v>3.4910400000000004</v>
+        <v>3.34558</v>
       </c>
       <c r="J22" s="19">
         <f>E22+F22+I22+G22+H22</f>
-        <v>24053.363040000004</v>
+        <v>23051.139579999999</v>
       </c>
       <c r="M22" s="20"/>
     </row>
@@ -21772,7 +21875,7 @@
       <c r="A23" s="41"/>
       <c r="B23" s="23">
         <f>(D22-D21)/D21</f>
-        <v>-0.63636363636363624</v>
+        <v>-0.65151515151515149</v>
       </c>
       <c r="C23" s="21">
         <f>SUM(C21:C22)</f>
@@ -21780,571 +21883,650 @@
       </c>
       <c r="D23" s="61">
         <f>E23/C23</f>
-        <v>24.3</v>
+        <v>24.25</v>
       </c>
       <c r="E23" s="21">
         <f t="shared" ref="E23:J23" si="11">SUM(E21:E22)</f>
-        <v>486000</v>
+        <v>485000</v>
       </c>
       <c r="F23" s="21">
         <f t="shared" si="11"/>
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="G23" s="21">
         <f t="shared" si="11"/>
-        <v>33.047999999999995</v>
+        <v>32.97999999999999</v>
       </c>
       <c r="H23" s="21">
         <f t="shared" si="11"/>
-        <v>4.8600000000000003</v>
+        <v>4.8500000000000005</v>
       </c>
       <c r="I23" s="21">
         <f t="shared" si="11"/>
-        <v>70.693560000000005</v>
+        <v>70.548100000000005</v>
       </c>
       <c r="J23" s="21">
         <f t="shared" si="11"/>
-        <v>487080.60156000004</v>
+        <v>486078.37810000003</v>
       </c>
       <c r="K23" s="22"/>
       <c r="L23" s="23"/>
       <c r="M23" s="20"/>
     </row>
     <row r="24" spans="1:13">
-      <c r="C24" s="96" t="s">
-        <v>34</v>
-      </c>
+      <c r="A24" s="7">
+        <v>45875</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" s="9">
+        <v>4400</v>
+      </c>
+      <c r="D24" s="10">
+        <v>9</v>
+      </c>
+      <c r="E24" s="19">
+        <f>C24*D24</f>
+        <v>39600</v>
+      </c>
+      <c r="F24" s="19">
+        <f>E24*0.002</f>
+        <v>79.2</v>
+      </c>
+      <c r="G24" s="19">
+        <f>E24*0.000068</f>
+        <v>2.6928000000000001</v>
+      </c>
+      <c r="H24" s="19">
+        <f>E24*0.00001</f>
+        <v>0.39600000000000002</v>
+      </c>
+      <c r="I24" s="19">
+        <f>(F24+G24+H24)*0.07</f>
+        <v>5.7602160000000016</v>
+      </c>
+      <c r="J24" s="19">
+        <f>E24+F24+I24+G24+H24</f>
+        <v>39688.049015999997</v>
+      </c>
+      <c r="M24" s="20"/>
     </row>
     <row r="25" spans="1:13">
-      <c r="A25" s="13">
+      <c r="A25" s="41"/>
+      <c r="B25" s="23">
+        <f>(D24-D23)/D23</f>
+        <v>-0.62886597938144329</v>
+      </c>
+      <c r="C25" s="21">
+        <f>SUM(C23:C24)</f>
+        <v>24400</v>
+      </c>
+      <c r="D25" s="61">
+        <f>E25/C25</f>
+        <v>21.5</v>
+      </c>
+      <c r="E25" s="21">
+        <f t="shared" ref="E25:J25" si="12">SUM(E23:E24)</f>
+        <v>524600</v>
+      </c>
+      <c r="F25" s="21">
+        <f t="shared" si="12"/>
+        <v>1049.2</v>
+      </c>
+      <c r="G25" s="21">
+        <f t="shared" si="12"/>
+        <v>35.672799999999988</v>
+      </c>
+      <c r="H25" s="21">
+        <f t="shared" si="12"/>
+        <v>5.2460000000000004</v>
+      </c>
+      <c r="I25" s="21">
+        <f t="shared" si="12"/>
+        <v>76.308316000000005</v>
+      </c>
+      <c r="J25" s="21">
+        <f t="shared" si="12"/>
+        <v>525766.42711599998</v>
+      </c>
+      <c r="K25" s="22"/>
+      <c r="L25" s="23"/>
+      <c r="M25" s="20"/>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="C26" s="96"/>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="13">
         <v>44641</v>
       </c>
-      <c r="B25" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="15">
+      <c r="B27" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="15">
         <v>3000</v>
       </c>
-      <c r="D25" s="16">
+      <c r="D27" s="16">
         <v>24.5</v>
       </c>
-      <c r="E25" s="17">
-        <f>C25*D25</f>
+      <c r="E27" s="17">
+        <f>C27*D27</f>
         <v>73500</v>
       </c>
-      <c r="F25" s="17">
-        <f>E25*0.002</f>
+      <c r="F27" s="17">
+        <f>E27*0.002</f>
         <v>147</v>
       </c>
-      <c r="G25" s="17">
-        <f>E25*0.000068</f>
+      <c r="G27" s="17">
+        <f>E27*0.000068</f>
         <v>4.9980000000000002</v>
       </c>
-      <c r="H25" s="17">
-        <f>E25*0.00001</f>
+      <c r="H27" s="17">
+        <f>E27*0.00001</f>
         <v>0.7350000000000001</v>
       </c>
-      <c r="I25" s="17">
-        <f>(F25+G25+H25)*0.07</f>
+      <c r="I27" s="17">
+        <f>(F27+G27+H27)*0.07</f>
         <v>10.691310000000001</v>
       </c>
-      <c r="J25" s="17">
-        <f>E25+F25+I25+G25+H25</f>
+      <c r="J27" s="17">
+        <f>E27+F27+I27+G27+H27</f>
         <v>73663.424310000002</v>
       </c>
-      <c r="M25" s="20"/>
-    </row>
-    <row r="26" spans="1:13" s="12" customFormat="1">
-      <c r="A26" s="13">
+      <c r="M27" s="20"/>
+    </row>
+    <row r="28" spans="1:13" s="12" customFormat="1">
+      <c r="A28" s="13">
         <v>44867</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B28" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C26" s="15">
-        <f>C25</f>
+      <c r="C28" s="15">
+        <f>C27</f>
         <v>3000</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D28" s="24">
         <v>16.100000000000001</v>
       </c>
-      <c r="E26" s="16">
-        <f>C26*D26</f>
+      <c r="E28" s="16">
+        <f>C28*D28</f>
         <v>48300.000000000007</v>
       </c>
-      <c r="F26" s="25">
-        <f>E26*0.002</f>
+      <c r="F28" s="25">
+        <f>E28*0.002</f>
         <v>96.600000000000023</v>
       </c>
-      <c r="G26" s="24">
-        <f>E26*0.000068</f>
+      <c r="G28" s="24">
+        <f>E28*0.000068</f>
         <v>3.2844000000000007</v>
       </c>
-      <c r="H26" s="24">
-        <f>E26*0.00001</f>
+      <c r="H28" s="24">
+        <f>E28*0.00001</f>
         <v>0.4830000000000001</v>
       </c>
-      <c r="I26" s="24">
-        <f>(F26+G26+H26)*0.07</f>
+      <c r="I28" s="24">
+        <f>(F28+G28+H28)*0.07</f>
         <v>7.025718000000003</v>
       </c>
-      <c r="J26" s="24">
-        <f>E26-F26-G26-H26-I26</f>
+      <c r="J28" s="24">
+        <f>E28-F28-G28-H28-I28</f>
         <v>48192.606882000015</v>
       </c>
     </row>
-    <row r="27" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A27" s="13" t="s">
+    <row r="29" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A29" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B27" s="6">
-        <f>(D26-D25)/D25</f>
+      <c r="B29" s="6">
+        <f>(D28-D27)/D27</f>
         <v>-0.3428571428571428</v>
       </c>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="17">
-        <f>E26-E25</f>
+      <c r="C29" s="15"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="17">
+        <f>E28-E27</f>
         <v>-25199.999999999993</v>
       </c>
-      <c r="F27" s="17"/>
-      <c r="G27" s="17"/>
-      <c r="H27" s="17"/>
-      <c r="I27" s="17"/>
-      <c r="J27" s="17">
-        <f>J26-J25</f>
+      <c r="F29" s="17"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="17"/>
+      <c r="I29" s="17"/>
+      <c r="J29" s="17">
+        <f>J28-J27</f>
         <v>-25470.817427999988</v>
       </c>
-      <c r="K27" s="11"/>
-    </row>
-    <row r="28" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A28" s="7"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="19"/>
-      <c r="H28" s="19"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="19"/>
-      <c r="K28" s="11"/>
-    </row>
-    <row r="29" spans="1:13" s="12" customFormat="1">
-      <c r="A29" s="36">
+      <c r="K29" s="11"/>
+    </row>
+    <row r="30" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A30" s="7"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="19"/>
+      <c r="G30" s="19"/>
+      <c r="H30" s="19"/>
+      <c r="I30" s="19"/>
+      <c r="J30" s="19"/>
+      <c r="K30" s="11"/>
+    </row>
+    <row r="31" spans="1:13" s="12" customFormat="1">
+      <c r="A31" s="36">
         <v>44372</v>
       </c>
-      <c r="B29" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="15">
+      <c r="B31" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="15">
         <v>1500</v>
       </c>
-      <c r="D29" s="16">
+      <c r="D31" s="16">
         <v>24.5</v>
       </c>
-      <c r="E29" s="17">
-        <f>C29*D29</f>
+      <c r="E31" s="17">
+        <f>C31*D31</f>
         <v>36750</v>
       </c>
-      <c r="F29" s="17">
-        <f>E29*0.002</f>
+      <c r="F31" s="17">
+        <f>E31*0.002</f>
         <v>73.5</v>
       </c>
-      <c r="G29" s="17">
-        <f>E29*0.00006</f>
+      <c r="G31" s="17">
+        <f>E31*0.00006</f>
         <v>2.2050000000000001</v>
       </c>
-      <c r="H29" s="17">
-        <f>E29*0.00001</f>
+      <c r="H31" s="17">
+        <f>E31*0.00001</f>
         <v>0.36750000000000005</v>
       </c>
-      <c r="I29" s="17">
-        <f>(F29+G29+H29)*0.07</f>
+      <c r="I31" s="17">
+        <f>(F31+G31+H31)*0.07</f>
         <v>5.3250750000000009</v>
       </c>
-      <c r="J29" s="17">
-        <f>E29+F29+I29+G29+H29</f>
+      <c r="J31" s="17">
+        <f>E31+F31+I31+G31+H31</f>
         <v>36831.397575000003</v>
       </c>
-      <c r="K29" s="30"/>
-      <c r="L29" s="10"/>
-      <c r="M29" s="11"/>
-    </row>
-    <row r="30" spans="1:13" s="12" customFormat="1">
-      <c r="A30" s="13">
+      <c r="K31" s="30"/>
+      <c r="L31" s="10"/>
+      <c r="M31" s="11"/>
+    </row>
+    <row r="32" spans="1:13" s="12" customFormat="1">
+      <c r="A32" s="13">
         <v>44533</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B32" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="15">
-        <f>C29</f>
+      <c r="C32" s="15">
+        <f>C31</f>
         <v>1500</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D32" s="24">
         <v>32</v>
       </c>
-      <c r="E30" s="16">
-        <f>C30*D30</f>
+      <c r="E32" s="16">
+        <f>C32*D32</f>
         <v>48000</v>
       </c>
-      <c r="F30" s="25">
-        <f>E30*0.002</f>
+      <c r="F32" s="25">
+        <f>E32*0.002</f>
         <v>96</v>
       </c>
-      <c r="G30" s="24">
-        <f>E30*0.000068</f>
+      <c r="G32" s="24">
+        <f>E32*0.000068</f>
         <v>3.2639999999999998</v>
       </c>
-      <c r="H30" s="24">
-        <f>E30*0.00001</f>
+      <c r="H32" s="24">
+        <f>E32*0.00001</f>
         <v>0.48000000000000004</v>
       </c>
-      <c r="I30" s="24">
-        <f>(F30+G30+H30)*0.07</f>
+      <c r="I32" s="24">
+        <f>(F32+G32+H32)*0.07</f>
         <v>6.9820800000000007</v>
       </c>
-      <c r="J30" s="24">
-        <f>E30-F30-G30-H30-I30</f>
+      <c r="J32" s="24">
+        <f>E32-F32-G32-H32-I32</f>
         <v>47893.273919999992</v>
       </c>
     </row>
-    <row r="31" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A31" s="13" t="s">
+    <row r="33" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A33" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B31" s="6">
-        <f>(D30-D29)/D29</f>
+      <c r="B33" s="6">
+        <f>(D32-D31)/D31</f>
         <v>0.30612244897959184</v>
       </c>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="17">
-        <f>E30-E29</f>
+      <c r="C33" s="15"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="17">
+        <f>E32-E31</f>
         <v>11250</v>
       </c>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17">
-        <f>J30-J29</f>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17">
+        <f>J32-J31</f>
         <v>11061.87634499999</v>
       </c>
-      <c r="K31" s="11"/>
-    </row>
-    <row r="32" spans="1:13" s="12" customFormat="1">
-      <c r="A32" s="36">
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" spans="1:13" s="12" customFormat="1">
+      <c r="A34" s="36">
         <v>44372</v>
       </c>
-      <c r="B32" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C32" s="15">
+      <c r="B34" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" s="15">
         <v>1500</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D34" s="16">
         <v>24.5</v>
       </c>
-      <c r="E32" s="17">
-        <f>C32*D32</f>
+      <c r="E34" s="17">
+        <f>C34*D34</f>
         <v>36750</v>
       </c>
-      <c r="F32" s="17">
-        <f>E32*0.002</f>
+      <c r="F34" s="17">
+        <f>E34*0.002</f>
         <v>73.5</v>
       </c>
-      <c r="G32" s="17">
-        <f>E32*0.00006</f>
+      <c r="G34" s="17">
+        <f>E34*0.00006</f>
         <v>2.2050000000000001</v>
       </c>
-      <c r="H32" s="17">
-        <f>E32*0.00001</f>
+      <c r="H34" s="17">
+        <f>E34*0.00001</f>
         <v>0.36750000000000005</v>
       </c>
-      <c r="I32" s="17">
-        <f>(F32+G32+H32)*0.07</f>
+      <c r="I34" s="17">
+        <f>(F34+G34+H34)*0.07</f>
         <v>5.3250750000000009</v>
       </c>
-      <c r="J32" s="17">
-        <f>E32+F32+I32+G32+H32</f>
+      <c r="J34" s="17">
+        <f>E34+F34+I34+G34+H34</f>
         <v>36831.397575000003</v>
       </c>
-      <c r="K32" s="30"/>
-      <c r="L32" s="10"/>
-      <c r="M32" s="11"/>
-    </row>
-    <row r="33" spans="1:13" s="12" customFormat="1">
-      <c r="A33" s="13">
+      <c r="K34" s="30"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="11"/>
+    </row>
+    <row r="35" spans="1:13" s="12" customFormat="1">
+      <c r="A35" s="13">
         <v>44537</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B35" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="15">
-        <f>C32</f>
+      <c r="C35" s="15">
+        <f>C34</f>
         <v>1500</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D35" s="24">
         <v>33</v>
       </c>
-      <c r="E33" s="16">
-        <f>C33*D33</f>
+      <c r="E35" s="16">
+        <f>C35*D35</f>
         <v>49500</v>
       </c>
-      <c r="F33" s="25">
-        <f>E33*0.002</f>
+      <c r="F35" s="25">
+        <f>E35*0.002</f>
         <v>99</v>
       </c>
-      <c r="G33" s="24">
-        <f>E33*0.000068</f>
+      <c r="G35" s="24">
+        <f>E35*0.000068</f>
         <v>3.3660000000000001</v>
       </c>
-      <c r="H33" s="24">
-        <f>E33*0.00001</f>
+      <c r="H35" s="24">
+        <f>E35*0.00001</f>
         <v>0.49500000000000005</v>
       </c>
-      <c r="I33" s="24">
-        <f>(F33+G33+H33)*0.07</f>
+      <c r="I35" s="24">
+        <f>(F35+G35+H35)*0.07</f>
         <v>7.2002700000000006</v>
       </c>
-      <c r="J33" s="24">
-        <f>E33-F33-G33-H33-I33</f>
+      <c r="J35" s="24">
+        <f>E35-F35-G35-H35-I35</f>
         <v>49389.938729999994</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A34" s="13" t="s">
+    <row r="36" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A36" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="6">
-        <f>(D33-D32)/D32</f>
+      <c r="B36" s="6">
+        <f>(D35-D34)/D34</f>
         <v>0.34693877551020408</v>
       </c>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="17">
-        <f>E33-E32</f>
+      <c r="C36" s="15"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="17">
+        <f>E35-E34</f>
         <v>12750</v>
       </c>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17">
-        <f>J33-J32</f>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17">
+        <f>J35-J34</f>
         <v>12558.541154999992</v>
       </c>
-      <c r="K34" s="11"/>
-    </row>
-    <row r="35" spans="1:13" s="12" customFormat="1">
-      <c r="A35" s="36">
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" spans="1:13" s="12" customFormat="1">
+      <c r="A37" s="36">
         <v>44372</v>
       </c>
-      <c r="B35" s="14" t="s">
-        <v>0</v>
-      </c>
-      <c r="C35" s="15">
+      <c r="B37" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C37" s="15">
         <v>1500</v>
       </c>
-      <c r="D35" s="16">
+      <c r="D37" s="16">
         <v>31.5</v>
       </c>
-      <c r="E35" s="17">
-        <f>C35*D35</f>
+      <c r="E37" s="17">
+        <f>C37*D37</f>
         <v>47250</v>
       </c>
-      <c r="F35" s="17">
-        <f>E35*0.002</f>
+      <c r="F37" s="17">
+        <f>E37*0.002</f>
         <v>94.5</v>
       </c>
-      <c r="G35" s="17">
-        <f>E35*0.00006</f>
+      <c r="G37" s="17">
+        <f>E37*0.00006</f>
         <v>2.835</v>
       </c>
-      <c r="H35" s="17">
-        <f>E35*0.00001</f>
+      <c r="H37" s="17">
+        <f>E37*0.00001</f>
         <v>0.47250000000000003</v>
       </c>
-      <c r="I35" s="17">
-        <f>(F35+G35+H35)*0.07</f>
+      <c r="I37" s="17">
+        <f>(F37+G37+H37)*0.07</f>
         <v>6.8465249999999997</v>
       </c>
-      <c r="J35" s="17">
-        <f>E35+F35+I35+G35+H35</f>
+      <c r="J37" s="17">
+        <f>E37+F37+I37+G37+H37</f>
         <v>47354.654025000003</v>
       </c>
-      <c r="K35" s="30"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="11"/>
-    </row>
-    <row r="36" spans="1:13" s="12" customFormat="1">
-      <c r="A36" s="13">
+      <c r="K37" s="30"/>
+      <c r="L37" s="10"/>
+      <c r="M37" s="11"/>
+    </row>
+    <row r="38" spans="1:13" s="12" customFormat="1">
+      <c r="A38" s="13">
         <v>44574</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B38" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="15">
-        <f>C35</f>
+      <c r="C38" s="15">
+        <f>C37</f>
         <v>1500</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D38" s="24">
         <v>33</v>
       </c>
-      <c r="E36" s="16">
-        <f>C36*D36</f>
+      <c r="E38" s="16">
+        <f>C38*D38</f>
         <v>49500</v>
       </c>
-      <c r="F36" s="25">
-        <f>E36*0.002</f>
+      <c r="F38" s="25">
+        <f>E38*0.002</f>
         <v>99</v>
       </c>
-      <c r="G36" s="24">
-        <f>E36*0.000068</f>
+      <c r="G38" s="24">
+        <f>E38*0.000068</f>
         <v>3.3660000000000001</v>
       </c>
-      <c r="H36" s="24">
-        <f>E36*0.00001</f>
+      <c r="H38" s="24">
+        <f>E38*0.00001</f>
         <v>0.49500000000000005</v>
       </c>
-      <c r="I36" s="24">
-        <f>(F36+G36+H36)*0.07</f>
+      <c r="I38" s="24">
+        <f>(F38+G38+H38)*0.07</f>
         <v>7.2002700000000006</v>
       </c>
-      <c r="J36" s="24">
-        <f>E36-F36-G36-H36-I36</f>
+      <c r="J38" s="24">
+        <f>E38-F38-G38-H38-I38</f>
         <v>49389.938729999994</v>
       </c>
     </row>
-    <row r="37" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A37" s="13" t="s">
+    <row r="39" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A39" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="6">
-        <f>(D36-D35)/D35</f>
+      <c r="B39" s="6">
+        <f>(D38-D37)/D37</f>
         <v>4.7619047619047616E-2</v>
       </c>
-      <c r="C37" s="15"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="17">
-        <f>E36-E35</f>
+      <c r="C39" s="15"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="17">
+        <f>E38-E37</f>
         <v>2250</v>
       </c>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17">
-        <f>J36-J35</f>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17">
+        <f>J38-J37</f>
         <v>2035.2847049999909</v>
       </c>
-      <c r="K37" s="11"/>
-    </row>
-    <row r="38" spans="1:13" s="12" customFormat="1">
-      <c r="A38" s="63">
+      <c r="K39" s="11"/>
+    </row>
+    <row r="40" spans="1:13" s="12" customFormat="1">
+      <c r="A40" s="63">
         <v>44372</v>
       </c>
-      <c r="B38" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C38" s="9">
+      <c r="B40" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C40" s="9">
         <v>2500</v>
       </c>
-      <c r="D38" s="10">
+      <c r="D40" s="10">
         <v>12.6</v>
       </c>
-      <c r="E38" s="19">
-        <f>C38*D38</f>
+      <c r="E40" s="19">
+        <f>C40*D40</f>
         <v>31500</v>
       </c>
-      <c r="F38" s="19">
-        <f>E38*0.002</f>
+      <c r="F40" s="19">
+        <f>E40*0.002</f>
         <v>63</v>
       </c>
-      <c r="G38" s="19">
-        <f>E38*0.00006</f>
+      <c r="G40" s="19">
+        <f>E40*0.00006</f>
         <v>1.8900000000000001</v>
       </c>
-      <c r="H38" s="19">
-        <f>E38*0.00001</f>
+      <c r="H40" s="19">
+        <f>E40*0.00001</f>
         <v>0.315</v>
       </c>
-      <c r="I38" s="19">
-        <f>(F38+G38+H38)*0.07</f>
+      <c r="I40" s="19">
+        <f>(F40+G40+H40)*0.07</f>
         <v>4.5643500000000001</v>
       </c>
-      <c r="J38" s="19">
-        <f>E38+F38+I38+G38+H38</f>
+      <c r="J40" s="19">
+        <f>E40+F40+I40+G40+H40</f>
         <v>31569.769349999999</v>
       </c>
-      <c r="K38" s="30"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="11"/>
-    </row>
-    <row r="39" spans="1:13" s="12" customFormat="1">
-      <c r="A39" s="7">
+      <c r="K40" s="30"/>
+      <c r="L40" s="10"/>
+      <c r="M40" s="11"/>
+    </row>
+    <row r="41" spans="1:13" s="12" customFormat="1">
+      <c r="A41" s="7">
         <v>44574</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B41" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="9">
-        <f>C38</f>
+      <c r="C41" s="9">
+        <f>C40</f>
         <v>2500</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D41" s="32">
         <v>12.8</v>
       </c>
-      <c r="E39" s="10">
-        <f>C39*D39</f>
+      <c r="E41" s="10">
+        <f>C41*D41</f>
         <v>32000</v>
       </c>
-      <c r="F39" s="33">
-        <f>E39*0.002</f>
+      <c r="F41" s="33">
+        <f>E41*0.002</f>
         <v>64</v>
       </c>
-      <c r="G39" s="32">
-        <f>E39*0.000068</f>
+      <c r="G41" s="32">
+        <f>E41*0.000068</f>
         <v>2.1760000000000002</v>
       </c>
-      <c r="H39" s="32">
-        <f>E39*0.00001</f>
+      <c r="H41" s="32">
+        <f>E41*0.00001</f>
         <v>0.32</v>
       </c>
-      <c r="I39" s="32">
-        <f>(F39+G39+H39)*0.07</f>
+      <c r="I41" s="32">
+        <f>(F41+G41+H41)*0.07</f>
         <v>4.6547200000000002</v>
       </c>
-      <c r="J39" s="32">
-        <f>E39-F39-G39-H39-I39</f>
+      <c r="J41" s="32">
+        <f>E41-F41-G41-H41-I41</f>
         <v>31928.849280000002</v>
       </c>
     </row>
-    <row r="40" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A40" s="7" t="s">
+    <row r="42" spans="1:13" s="29" customFormat="1" ht="18.600000000000001">
+      <c r="A42" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="23">
-        <f>(D39-D38)/D38</f>
+      <c r="B42" s="23">
+        <f>(D41-D40)/D40</f>
         <v>1.5873015873015959E-2</v>
       </c>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="19">
-        <f>E39-E38</f>
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="19">
+        <f>E41-E40</f>
         <v>500</v>
       </c>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19">
-        <f>J39-J38</f>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19">
+        <f>J41-J40</f>
         <v>359.07993000000351</v>
       </c>
-      <c r="K40" s="11"/>
+      <c r="K42" s="11"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -24131,73 +24313,73 @@
         <v>0</v>
       </c>
       <c r="C13" s="9">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="D13" s="43">
-        <v>4.5</v>
+        <v>7.05</v>
       </c>
       <c r="E13" s="19">
         <f>C13*D13</f>
-        <v>45000</v>
+        <v>35250</v>
       </c>
       <c r="F13" s="19">
         <f>E13*0.002</f>
-        <v>90</v>
+        <v>70.5</v>
       </c>
       <c r="G13" s="19">
         <f>E13*0.000068</f>
-        <v>3.06</v>
+        <v>2.3969999999999998</v>
       </c>
       <c r="H13" s="19">
         <f>E13*0.00001</f>
-        <v>0.45</v>
+        <v>0.35250000000000004</v>
       </c>
       <c r="I13" s="19">
         <f>(F13+G13+H13)*0.07</f>
-        <v>6.545700000000001</v>
+        <v>5.1274650000000017</v>
       </c>
       <c r="J13" s="19">
         <f>E13+F13+I13+G13+H13</f>
-        <v>45100.055699999997</v>
+        <v>35328.376964999996</v>
       </c>
     </row>
     <row r="14" spans="1:11" s="20" customFormat="1">
       <c r="A14" s="41"/>
       <c r="B14" s="70">
         <f>(D13-D12)/D12</f>
-        <v>-0.48275862068965514</v>
-      </c>
-      <c r="C14" s="21">
+        <v>-0.18965517241379307</v>
+      </c>
+      <c r="C14" s="5">
         <f>C12+C13</f>
-        <v>60000</v>
+        <v>55000</v>
       </c>
       <c r="D14" s="31">
         <f>E14/C14</f>
-        <v>8</v>
+        <v>8.5500000000000007</v>
       </c>
       <c r="E14" s="21">
         <f t="shared" ref="E14:J14" si="5">E12+E13</f>
-        <v>480000</v>
+        <v>470250</v>
       </c>
       <c r="F14" s="21">
         <f t="shared" si="5"/>
-        <v>960</v>
+        <v>940.5</v>
       </c>
       <c r="G14" s="21">
         <f t="shared" si="5"/>
-        <v>31.911999999999999</v>
+        <v>31.248999999999999</v>
       </c>
       <c r="H14" s="21">
         <f t="shared" si="5"/>
-        <v>4.8000000000000007</v>
+        <v>4.7025000000000006</v>
       </c>
       <c r="I14" s="21">
         <f t="shared" si="5"/>
-        <v>69.769840000000002</v>
+        <v>68.351605000000006</v>
       </c>
       <c r="J14" s="21">
         <f t="shared" si="5"/>
-        <v>481066.48184000002</v>
+        <v>471294.803105</v>
       </c>
       <c r="K14" s="23"/>
     </row>
@@ -24993,7 +25175,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:11" s="18" customFormat="1" ht="15.6">
@@ -26198,7 +26380,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1">
@@ -26240,83 +26422,83 @@
       </c>
     </row>
     <row r="3" spans="1:14" s="12" customFormat="1">
-      <c r="A3" s="63">
-        <v>44473</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="9">
-        <v>100</v>
-      </c>
-      <c r="D3" s="30">
-        <v>360</v>
-      </c>
-      <c r="E3" s="19">
+      <c r="A3" s="36">
+        <v>46134</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="15">
+        <v>200</v>
+      </c>
+      <c r="D3" s="27">
+        <v>350</v>
+      </c>
+      <c r="E3" s="17">
         <f>C3*D3</f>
-        <v>36000</v>
-      </c>
-      <c r="F3" s="19">
+        <v>70000</v>
+      </c>
+      <c r="F3" s="17">
         <f>E3*0.002</f>
-        <v>72</v>
-      </c>
-      <c r="G3" s="19">
+        <v>140</v>
+      </c>
+      <c r="G3" s="17">
         <f>E3*0.00006</f>
-        <v>2.16</v>
-      </c>
-      <c r="H3" s="19">
+        <v>4.2</v>
+      </c>
+      <c r="H3" s="17">
         <f>E3*0.00001</f>
-        <v>0.36000000000000004</v>
-      </c>
-      <c r="I3" s="19">
+        <v>0.70000000000000007</v>
+      </c>
+      <c r="I3" s="17">
         <f>(F3+G3+H3)*0.07</f>
-        <v>5.2164000000000001</v>
-      </c>
-      <c r="J3" s="19">
+        <v>10.142999999999999</v>
+      </c>
+      <c r="J3" s="17">
         <f>E3+F3+I3+G3+H3</f>
-        <v>36079.736400000002</v>
+        <v>70155.042999999991</v>
       </c>
       <c r="K3" s="30"/>
       <c r="L3" s="10"/>
       <c r="M3" s="11"/>
     </row>
     <row r="4" spans="1:14" s="59" customFormat="1" ht="21">
-      <c r="A4" s="52"/>
-      <c r="B4" s="72">
+      <c r="A4" s="46"/>
+      <c r="B4" s="71">
         <f>(D3-D2)/D2</f>
-        <v>-5.2631578947368418E-2</v>
-      </c>
-      <c r="C4" s="9">
+        <v>-7.8947368421052627E-2</v>
+      </c>
+      <c r="C4" s="15">
         <f>SUM(C2:C3)</f>
-        <v>200</v>
-      </c>
-      <c r="D4" s="30">
+        <v>300</v>
+      </c>
+      <c r="D4" s="27">
         <f>E4/C4</f>
-        <v>370</v>
-      </c>
-      <c r="E4" s="9">
+        <v>360</v>
+      </c>
+      <c r="E4" s="15">
         <f t="shared" ref="E4:J4" si="0">SUM(E2:E3)</f>
-        <v>74000</v>
-      </c>
-      <c r="F4" s="9">
+        <v>108000</v>
+      </c>
+      <c r="F4" s="15">
         <f t="shared" si="0"/>
-        <v>148</v>
-      </c>
-      <c r="G4" s="9">
+        <v>216</v>
+      </c>
+      <c r="G4" s="15">
         <f t="shared" si="0"/>
-        <v>4.4400000000000004</v>
-      </c>
-      <c r="H4" s="9">
+        <v>6.48</v>
+      </c>
+      <c r="H4" s="15">
         <f t="shared" si="0"/>
-        <v>0.74</v>
-      </c>
-      <c r="I4" s="9">
+        <v>1.08</v>
+      </c>
+      <c r="I4" s="15">
         <f t="shared" si="0"/>
-        <v>10.7226</v>
-      </c>
-      <c r="J4" s="9">
+        <v>15.6492</v>
+      </c>
+      <c r="J4" s="15">
         <f t="shared" si="0"/>
-        <v>74163.902600000001</v>
+        <v>108239.20919999998</v>
       </c>
       <c r="K4" s="10"/>
       <c r="L4" s="12"/>
@@ -26324,83 +26506,83 @@
       <c r="N4" s="58"/>
     </row>
     <row r="5" spans="1:14" s="12" customFormat="1">
-      <c r="A5" s="63">
-        <v>44473</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="9">
+      <c r="A5" s="36">
+        <v>46142</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="15">
         <v>100</v>
       </c>
-      <c r="D5" s="30">
-        <v>358</v>
-      </c>
-      <c r="E5" s="19">
+      <c r="D5" s="27">
+        <v>340</v>
+      </c>
+      <c r="E5" s="17">
         <f>C5*D5</f>
-        <v>35800</v>
-      </c>
-      <c r="F5" s="19">
+        <v>34000</v>
+      </c>
+      <c r="F5" s="17">
         <f>E5*0.002</f>
-        <v>71.600000000000009</v>
-      </c>
-      <c r="G5" s="19">
+        <v>68</v>
+      </c>
+      <c r="G5" s="17">
         <f>E5*0.00006</f>
-        <v>2.1480000000000001</v>
-      </c>
-      <c r="H5" s="19">
+        <v>2.04</v>
+      </c>
+      <c r="H5" s="17">
         <f>E5*0.00001</f>
-        <v>0.35800000000000004</v>
-      </c>
-      <c r="I5" s="19">
+        <v>0.34</v>
+      </c>
+      <c r="I5" s="17">
         <f>(F5+G5+H5)*0.07</f>
-        <v>5.1874200000000013</v>
-      </c>
-      <c r="J5" s="19">
+        <v>4.9266000000000014</v>
+      </c>
+      <c r="J5" s="17">
         <f>E5+F5+I5+G5+H5</f>
-        <v>35879.293420000002</v>
+        <v>34075.306599999996</v>
       </c>
       <c r="K5" s="30"/>
       <c r="L5" s="10"/>
       <c r="M5" s="11"/>
     </row>
     <row r="6" spans="1:14" s="59" customFormat="1" ht="21">
-      <c r="A6" s="52"/>
-      <c r="B6" s="72">
+      <c r="A6" s="46"/>
+      <c r="B6" s="71">
         <f>(D5-D4)/D4</f>
-        <v>-3.2432432432432434E-2</v>
-      </c>
-      <c r="C6" s="9">
+        <v>-5.5555555555555552E-2</v>
+      </c>
+      <c r="C6" s="15">
         <f>SUM(C4:C5)</f>
-        <v>300</v>
-      </c>
-      <c r="D6" s="30">
+        <v>400</v>
+      </c>
+      <c r="D6" s="27">
         <f>E6/C6</f>
-        <v>366</v>
-      </c>
-      <c r="E6" s="9">
+        <v>355</v>
+      </c>
+      <c r="E6" s="15">
         <f t="shared" ref="E6:J6" si="1">SUM(E4:E5)</f>
-        <v>109800</v>
-      </c>
-      <c r="F6" s="9">
+        <v>142000</v>
+      </c>
+      <c r="F6" s="15">
         <f t="shared" si="1"/>
-        <v>219.60000000000002</v>
-      </c>
-      <c r="G6" s="9">
+        <v>284</v>
+      </c>
+      <c r="G6" s="15">
         <f t="shared" si="1"/>
-        <v>6.588000000000001</v>
-      </c>
-      <c r="H6" s="9">
+        <v>8.52</v>
+      </c>
+      <c r="H6" s="15">
         <f t="shared" si="1"/>
-        <v>1.0980000000000001</v>
-      </c>
-      <c r="I6" s="9">
+        <v>1.4200000000000002</v>
+      </c>
+      <c r="I6" s="15">
         <f t="shared" si="1"/>
-        <v>15.910020000000001</v>
-      </c>
-      <c r="J6" s="9">
+        <v>20.575800000000001</v>
+      </c>
+      <c r="J6" s="15">
         <f t="shared" si="1"/>
-        <v>110043.19602</v>
+        <v>142314.51579999999</v>
       </c>
       <c r="K6" s="10"/>
       <c r="L6" s="12"/>
@@ -26418,31 +26600,31 @@
         <v>100</v>
       </c>
       <c r="D7" s="30">
-        <v>362</v>
+        <v>330</v>
       </c>
       <c r="E7" s="19">
         <f>C7*D7</f>
-        <v>36200</v>
+        <v>33000</v>
       </c>
       <c r="F7" s="19">
         <f>E7*0.002</f>
-        <v>72.400000000000006</v>
+        <v>66</v>
       </c>
       <c r="G7" s="19">
         <f>E7*0.00006</f>
-        <v>2.1720000000000002</v>
+        <v>1.98</v>
       </c>
       <c r="H7" s="19">
         <f>E7*0.00001</f>
-        <v>0.36200000000000004</v>
+        <v>0.33</v>
       </c>
       <c r="I7" s="19">
         <f>(F7+G7+H7)*0.07</f>
-        <v>5.2453799999999999</v>
+        <v>4.7817000000000007</v>
       </c>
       <c r="J7" s="19">
         <f>E7+F7+I7+G7+H7</f>
-        <v>36280.179380000001</v>
+        <v>33073.091700000004</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="10"/>
@@ -26452,39 +26634,39 @@
       <c r="A8" s="52"/>
       <c r="B8" s="72">
         <f>(D7-D6)/D6</f>
-        <v>-1.092896174863388E-2</v>
+        <v>-7.0422535211267609E-2</v>
       </c>
       <c r="C8" s="9">
         <f>SUM(C6:C7)</f>
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="D8" s="30">
         <f>E8/C8</f>
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E8" s="9">
         <f t="shared" ref="E8:J8" si="2">SUM(E6:E7)</f>
-        <v>146000</v>
+        <v>175000</v>
       </c>
       <c r="F8" s="9">
         <f t="shared" si="2"/>
-        <v>292</v>
+        <v>350</v>
       </c>
       <c r="G8" s="9">
         <f t="shared" si="2"/>
-        <v>8.7600000000000016</v>
+        <v>10.5</v>
       </c>
       <c r="H8" s="9">
         <f t="shared" si="2"/>
-        <v>1.4600000000000002</v>
+        <v>1.7500000000000002</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="2"/>
-        <v>21.1554</v>
+        <v>25.357500000000002</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="2"/>
-        <v>146323.37540000002</v>
+        <v>175387.60749999998</v>
       </c>
       <c r="K8" s="10"/>
       <c r="L8" s="12"/>
@@ -26502,31 +26684,31 @@
         <v>100</v>
       </c>
       <c r="D9" s="30">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="E9" s="19">
         <f>C9*D9</f>
-        <v>35500</v>
+        <v>32000</v>
       </c>
       <c r="F9" s="19">
         <f>E9*0.002</f>
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="G9" s="19">
         <f>E9*0.00006</f>
-        <v>2.13</v>
+        <v>1.9200000000000002</v>
       </c>
       <c r="H9" s="19">
         <f>E9*0.00001</f>
-        <v>0.35500000000000004</v>
+        <v>0.32</v>
       </c>
       <c r="I9" s="19">
         <f>(F9+G9+H9)*0.07</f>
-        <v>5.1439500000000002</v>
+        <v>4.6368</v>
       </c>
       <c r="J9" s="19">
         <f>E9+F9+I9+G9+H9</f>
-        <v>35578.628949999998</v>
+        <v>32070.876799999998</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="10"/>
@@ -26536,39 +26718,39 @@
       <c r="A10" s="52"/>
       <c r="B10" s="72">
         <f>(D9-D8)/D8</f>
-        <v>-2.7397260273972601E-2</v>
+        <v>-8.5714285714285715E-2</v>
       </c>
       <c r="C10" s="9">
         <f>SUM(C8:C9)</f>
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D10" s="30">
         <f>E10/C10</f>
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="E10" s="9">
         <f t="shared" ref="E10:J10" si="3">SUM(E8:E9)</f>
-        <v>181500</v>
+        <v>207000</v>
       </c>
       <c r="F10" s="9">
         <f t="shared" si="3"/>
-        <v>363</v>
+        <v>414</v>
       </c>
       <c r="G10" s="9">
         <f t="shared" si="3"/>
-        <v>10.89</v>
+        <v>12.42</v>
       </c>
       <c r="H10" s="9">
         <f t="shared" si="3"/>
-        <v>1.8150000000000002</v>
+        <v>2.0700000000000003</v>
       </c>
       <c r="I10" s="9">
         <f t="shared" si="3"/>
-        <v>26.29935</v>
+        <v>29.994300000000003</v>
       </c>
       <c r="J10" s="9">
         <f t="shared" si="3"/>
-        <v>181902.00435</v>
+        <v>207458.48429999998</v>
       </c>
       <c r="K10" s="10"/>
       <c r="L10" s="12"/>
@@ -26586,31 +26768,31 @@
         <v>100</v>
       </c>
       <c r="D11" s="30">
-        <v>345</v>
+        <v>310</v>
       </c>
       <c r="E11" s="19">
         <f>C11*D11</f>
-        <v>34500</v>
+        <v>31000</v>
       </c>
       <c r="F11" s="19">
         <f>E11*0.002</f>
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="G11" s="19">
         <f>E11*0.00006</f>
-        <v>2.0699999999999998</v>
+        <v>1.86</v>
       </c>
       <c r="H11" s="19">
         <f>E11*0.00001</f>
-        <v>0.34500000000000003</v>
+        <v>0.31</v>
       </c>
       <c r="I11" s="19">
         <f>(F11+G11+H11)*0.07</f>
-        <v>4.9990499999999995</v>
+        <v>4.4919000000000002</v>
       </c>
       <c r="J11" s="19">
         <f>E11+F11+I11+G11+H11</f>
-        <v>34576.414049999999</v>
+        <v>31068.661900000003</v>
       </c>
       <c r="K11" s="30"/>
       <c r="L11" s="10"/>
@@ -26620,39 +26802,39 @@
       <c r="A12" s="52"/>
       <c r="B12" s="72">
         <f>(D11-D10)/D10</f>
-        <v>-4.9586776859504134E-2</v>
+        <v>-0.10144927536231885</v>
       </c>
       <c r="C12" s="9">
         <f>SUM(C10:C11)</f>
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="D12" s="30">
         <f>E12/C12</f>
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="E12" s="9">
         <f t="shared" ref="E12:J12" si="4">SUM(E10:E11)</f>
-        <v>216000</v>
+        <v>238000</v>
       </c>
       <c r="F12" s="9">
         <f t="shared" si="4"/>
-        <v>432</v>
+        <v>476</v>
       </c>
       <c r="G12" s="9">
         <f t="shared" si="4"/>
-        <v>12.96</v>
+        <v>14.28</v>
       </c>
       <c r="H12" s="9">
         <f t="shared" si="4"/>
-        <v>2.16</v>
+        <v>2.3800000000000003</v>
       </c>
       <c r="I12" s="9">
         <f t="shared" si="4"/>
-        <v>31.298400000000001</v>
+        <v>34.486200000000004</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="4"/>
-        <v>216478.4184</v>
+        <v>238527.14619999999</v>
       </c>
       <c r="K12" s="10"/>
       <c r="L12" s="12"/>
@@ -26660,17 +26842,7 @@
       <c r="N12" s="58"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="C13" s="20">
-        <v>400</v>
-      </c>
-      <c r="D13" s="88">
-        <f>E13/C13</f>
-        <v>355</v>
-      </c>
-      <c r="E13" s="22">
-        <f>E5+E7+E9+E11</f>
-        <v>142000</v>
-      </c>
+      <c r="E13" s="22"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -28418,7 +28590,7 @@
   <sheetData>
     <row r="1" spans="1:14">
       <c r="B1" s="47" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -28856,7 +29028,7 @@
         <v>45871</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2">
         <v>5000</v>
@@ -28979,7 +29151,7 @@
     </row>
     <row r="20" spans="1:10">
       <c r="B20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -29082,7 +29254,7 @@
     </row>
     <row r="24" spans="1:10">
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1841" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25641D0C-D666-4834-B152-240364F62029}"/>
+  <xr:revisionPtr revIDLastSave="1869" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E0E10B-0BF4-4201-A735-6CA004F14504}"/>
   <bookViews>
-    <workbookView xWindow="12120" yWindow="1608" windowWidth="10068" windowHeight="10764" tabRatio="461" firstSheet="27" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12192" yWindow="876" windowWidth="10608" windowHeight="11364" tabRatio="461" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="569" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="570" uniqueCount="44">
   <si>
     <t>BUY</t>
   </si>
@@ -203,15 +203,15 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="165" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="\฿#,##0.000"/>
-    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="169" formatCode="0.0000"/>
-    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="171" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="187" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="190" formatCode="\฿#,##0.000"/>
+    <numFmt numFmtId="191" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="192" formatCode="0.0000"/>
+    <numFmt numFmtId="193" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="194" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="195" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -382,64 +382,64 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="192" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -447,30 +447,30 @@
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -501,10 +501,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27426,80 +27422,143 @@
       <c r="N8" s="58"/>
     </row>
     <row r="9" spans="1:14" s="29" customFormat="1" ht="18.600000000000001">
-      <c r="A9" s="52">
-        <v>45525</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="9">
-        <f>C8</f>
-        <v>17500</v>
-      </c>
-      <c r="D9" s="32">
-        <v>11.1</v>
-      </c>
-      <c r="E9" s="10">
-        <f>C9*D9</f>
-        <v>194250</v>
-      </c>
-      <c r="F9" s="33">
-        <f>E9*0.002</f>
-        <v>388.5</v>
-      </c>
-      <c r="G9" s="32">
-        <f>E9*0.000068</f>
-        <v>13.209</v>
-      </c>
-      <c r="H9" s="32">
-        <f>E9*0.00001</f>
-        <v>1.9425000000000001</v>
-      </c>
-      <c r="I9" s="32">
-        <f>(F9+G9+H9)*0.07</f>
-        <v>28.255605000000003</v>
-      </c>
-      <c r="J9" s="32">
-        <f>E9-F9-G9-H9-I9</f>
-        <v>193818.09289499998</v>
-      </c>
+      <c r="A9" s="52"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="52"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="10">
-        <f>E9-E8</f>
-        <v>8750</v>
-      </c>
-      <c r="F10" s="33"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
-      <c r="J10" s="10">
-        <f>J9-J8</f>
-        <v>7907.2289449999516</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="52"/>
-      <c r="B11" s="12"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="10"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="19"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="J12" s="50"/>
+    <row r="10" spans="1:14" s="18" customFormat="1" ht="15.6">
+      <c r="A10" s="46">
+        <v>46163</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" s="15">
+        <v>900</v>
+      </c>
+      <c r="D10" s="38">
+        <v>11.4</v>
+      </c>
+      <c r="E10" s="17">
+        <f>C10*D10</f>
+        <v>10260</v>
+      </c>
+      <c r="F10" s="17">
+        <f>E10*0.002</f>
+        <v>20.52</v>
+      </c>
+      <c r="G10" s="17">
+        <f>E10*0.00006</f>
+        <v>0.61560000000000004</v>
+      </c>
+      <c r="H10" s="17">
+        <f>E10*0.00001</f>
+        <v>0.10260000000000001</v>
+      </c>
+      <c r="I10" s="17">
+        <f>(F10+G10+H10)*0.07</f>
+        <v>1.4866740000000001</v>
+      </c>
+      <c r="J10" s="17">
+        <f>E10+F10+I10+G10+H10</f>
+        <v>10282.724874</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A11" s="36">
+        <v>46164</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="15">
+        <v>9100</v>
+      </c>
+      <c r="D11" s="16">
+        <v>11.3</v>
+      </c>
+      <c r="E11" s="17">
+        <f>C11*D11</f>
+        <v>102830</v>
+      </c>
+      <c r="F11" s="17">
+        <f>E11*0.002</f>
+        <v>205.66</v>
+      </c>
+      <c r="G11" s="17">
+        <f>E11*0.00006</f>
+        <v>6.1698000000000004</v>
+      </c>
+      <c r="H11" s="17">
+        <f>E11*0.00001</f>
+        <v>1.0283</v>
+      </c>
+      <c r="I11" s="17">
+        <f>(F11+G11+H11)*0.07</f>
+        <v>14.900067000000002</v>
+      </c>
+      <c r="J11" s="17">
+        <f>E11+F11+I11+G11+H11</f>
+        <v>103057.75816700001</v>
+      </c>
+      <c r="K11" s="30"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="11"/>
+      <c r="N11" s="12"/>
+    </row>
+    <row r="12" spans="1:14" s="59" customFormat="1" ht="21">
+      <c r="A12" s="46"/>
+      <c r="B12" s="71">
+        <f>(D11-D10)/D10</f>
+        <v>-8.7719298245613718E-3</v>
+      </c>
+      <c r="C12" s="15">
+        <f>SUM(C10:C11)</f>
+        <v>10000</v>
+      </c>
+      <c r="D12" s="37">
+        <f>E12/C12</f>
+        <v>11.308999999999999</v>
+      </c>
+      <c r="E12" s="15">
+        <f t="shared" ref="E12:J12" si="3">SUM(E10:E11)</f>
+        <v>113090</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="3"/>
+        <v>226.18</v>
+      </c>
+      <c r="G12" s="15">
+        <f t="shared" si="3"/>
+        <v>6.7854000000000001</v>
+      </c>
+      <c r="H12" s="15">
+        <f t="shared" si="3"/>
+        <v>1.1309</v>
+      </c>
+      <c r="I12" s="15">
+        <f t="shared" si="3"/>
+        <v>16.386741000000001</v>
+      </c>
+      <c r="J12" s="15">
+        <f t="shared" si="3"/>
+        <v>113340.483041</v>
+      </c>
+      <c r="K12" s="10"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1869" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0E0E10B-0BF4-4201-A735-6CA004F14504}"/>
+  <xr:revisionPtr revIDLastSave="1873" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D81471AD-E1C6-4791-81DC-D6DF6EB02F25}"/>
   <bookViews>
-    <workbookView xWindow="12192" yWindow="876" windowWidth="10608" windowHeight="11364" tabRatio="461" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9972" yWindow="660" windowWidth="13068" windowHeight="11364" tabRatio="461" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PTTGC" sheetId="42" r:id="rId1"/>
@@ -503,6 +503,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>

--- a/Excel/02-Profit_by_Type.xlsx
+++ b/Excel/02-Profit_by_Type.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1893" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{75909B50-2D8F-4175-B0B2-E5E2FC91BB5E}"/>
+  <xr:revisionPtr revIDLastSave="1896" documentId="13_ncr:1_{952C9640-4145-4BFE-A933-8C66170A3FDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA07ADB7-7B34-436C-8C62-76C1C92FE344}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="684" windowWidth="15840" windowHeight="9672" tabRatio="461" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1188" windowWidth="12516" windowHeight="10764" tabRatio="461" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="226" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="47">
   <si>
     <t>BUY</t>
   </si>
@@ -198,21 +198,30 @@
   <si>
     <t>None</t>
   </si>
+  <si>
+    <t>Buy</t>
+  </si>
+  <si>
+    <t>Qty</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="9">
-    <numFmt numFmtId="187" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="189" formatCode="[$฿-41E]#,##0.00"/>
-    <numFmt numFmtId="190" formatCode="\฿#,##0.000"/>
-    <numFmt numFmtId="191" formatCode="#,##0.0000"/>
-    <numFmt numFmtId="192" formatCode="0.0000"/>
-    <numFmt numFmtId="193" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="194" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="195" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$฿-41E]#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="\฿#,##0.000"/>
+    <numFmt numFmtId="168" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="169" formatCode="0.0000"/>
+    <numFmt numFmtId="170" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="171" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="_-&quot;฿&quot;* #,##0.0000_-;\-&quot;฿&quot;* #,##0.0000_-;_-&quot;฿&quot;* &quot;-&quot;????_-;_-@_-"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -383,64 +392,64 @@
     <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="192" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="192" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -448,30 +457,30 @@
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -502,10 +511,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -856,9 +861,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57FD5FC0-1BDB-4806-B210-A8463FD70908}">
-  <dimension ref="A2:C3"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C1" t="s">
+        <v>45</v>
+      </c>
+    </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>17</v>
